--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EEF039-3374-48C1-9137-2E1B4F2A7934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C977ABCA-1BB2-4D89-9B53-88D4D882D946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="844">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2555,6 +2555,15 @@
   </si>
   <si>
     <t>BAU Cost of Electricity Sector Capital for Power Plants, BAU Cost of Electricity Sector Capital for Other Investments, BAU Cost of Electricity Sector Capital for Distributed Solar Investments</t>
+  </si>
+  <si>
+    <t>CiDESCTY</t>
+  </si>
+  <si>
+    <t>Change in Distributed Electricity Source Capacity This Year</t>
+  </si>
+  <si>
+    <t>You plan on using a policy mandated change in distributed solar capacity additions</t>
   </si>
 </sst>
 </file>
@@ -3366,7 +3375,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G307"/>
+  <dimension ref="A1:G308"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -3609,30 +3618,33 @@
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>165</v>
+        <v>841</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>842</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>14</v>
+        <v>165</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>99</v>
+        <v>166</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -3640,10 +3652,10 @@
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>99</v>
@@ -3654,86 +3666,83 @@
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>163</v>
+        <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>163</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>471</v>
+        <v>30</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>758</v>
+        <v>470</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>759</v>
+        <v>471</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>18</v>
+        <v>758</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>304</v>
+        <v>759</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3741,13 +3750,16 @@
         <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>98</v>
+        <v>31</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3755,16 +3767,13 @@
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>305</v>
+        <v>32</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3772,13 +3781,16 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>98</v>
+        <v>33</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3786,10 +3798,10 @@
         <v>9</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>98</v>
@@ -3800,16 +3812,13 @@
         <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>341</v>
+        <v>22</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>343</v>
+        <v>35</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3817,58 +3826,61 @@
         <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>566</v>
+        <v>341</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>437</v>
+        <v>566</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>839</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+        <v>438</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>492</v>
+        <v>442</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>99</v>
+        <v>443</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -3876,13 +3888,13 @@
         <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>237</v>
+        <v>492</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>252</v>
+        <v>493</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -3890,13 +3902,13 @@
         <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>474</v>
+        <v>237</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>98</v>
+        <v>238</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -3904,200 +3916,195 @@
         <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F36" s="12" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="17" t="s">
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B37" s="17" t="s">
         <v>444</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C37" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17" t="s">
+      <c r="D37" s="17"/>
+      <c r="E37" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="F36" s="19" t="s">
+      <c r="F37" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G36" s="17"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G37" s="17"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>680</v>
+        <v>603</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+        <v>604</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="116" x14ac:dyDescent="0.35">
+        <v>681</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>37</v>
+        <v>684</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>685</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>396</v>
+        <v>37</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>837</v>
+        <v>396</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>838</v>
+        <v>397</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>679</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="17" t="s">
+    <row r="45" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B45" s="17" t="s">
         <v>765</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C45" s="17" t="s">
         <v>686</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F45" s="20" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F46" s="4" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>426</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G46" s="17" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="17" t="s">
-        <v>472</v>
+        <v>170</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
@@ -4105,75 +4112,77 @@
         <v>140</v>
       </c>
       <c r="G47" s="17" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G48" s="17" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>543</v>
+        <v>312</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>544</v>
+        <v>313</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>423</v>
+        <v>543</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>424</v>
+        <v>544</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>329</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>330</v>
+        <v>424</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>331</v>
+        <v>425</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -4181,50 +4190,50 @@
         <v>400</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>245</v>
+        <v>329</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>246</v>
+        <v>330</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>704</v>
+        <v>245</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>705</v>
+        <v>246</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>496</v>
+        <v>704</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>497</v>
+        <v>705</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>498</v>
+        <v>706</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -4232,33 +4241,33 @@
         <v>400</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>260</v>
+        <v>496</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>261</v>
+        <v>497</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>558</v>
+        <v>260</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>559</v>
+        <v>261</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>560</v>
+        <v>499</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -4266,116 +4275,119 @@
         <v>400</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>766</v>
+        <v>558</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>767</v>
+        <v>559</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>176</v>
+        <v>766</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>177</v>
+        <v>767</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>563</v>
+        <v>176</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>565</v>
+        <v>177</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>402</v>
+        <v>563</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+        <v>565</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="F61" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="17" t="s">
-        <v>400</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>452</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>707</v>
-      </c>
-      <c r="E62" s="17"/>
       <c r="F62" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="G62" s="17" t="s">
+      <c r="G62" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>707</v>
+      </c>
+      <c r="E63" s="17"/>
+      <c r="F63" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="G63" s="17" t="s">
         <v>453</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -4383,10 +4395,10 @@
         <v>38</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>197</v>
+        <v>39</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>198</v>
+        <v>41</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>97</v>
@@ -4397,13 +4409,13 @@
         <v>38</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>807</v>
+        <v>197</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>99</v>
+        <v>198</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
@@ -4411,13 +4423,13 @@
         <v>38</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>40</v>
+        <v>807</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>98</v>
+        <v>808</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -4425,46 +4437,46 @@
         <v>38</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>532</v>
+        <v>40</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>533</v>
+        <v>42</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="17" t="s">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C69" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="21" t="s">
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="G68" s="17" t="s">
+      <c r="G69" s="17" t="s">
         <v>374</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
@@ -4472,75 +4484,75 @@
         <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>642</v>
+        <v>773</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>775</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>179</v>
+        <v>642</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>708</v>
+        <v>643</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+        <v>840</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>316</v>
+        <v>179</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>708</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>590</v>
+        <v>316</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>99</v>
+        <v>317</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4548,16 +4560,13 @@
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>670</v>
+        <v>590</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>98</v>
+        <v>589</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4565,33 +4574,33 @@
         <v>43</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>173</v>
+        <v>670</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F76" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+        <v>671</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>581</v>
+        <v>173</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>244</v>
+        <v>172</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -4599,30 +4608,30 @@
         <v>43</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>44</v>
+        <v>581</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>582</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F79" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>310</v>
+        <v>50</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
@@ -4630,89 +4639,92 @@
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>738</v>
+        <v>45</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>739</v>
+        <v>51</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>760</v>
+        <v>738</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>739</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>675</v>
+        <v>760</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+        <v>761</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>199</v>
+        <v>676</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>674</v>
+        <v>661</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>158</v>
+        <v>673</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>159</v>
+        <v>674</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>97</v>
@@ -4723,120 +4735,120 @@
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>644</v>
+        <v>158</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>46</v>
+        <v>644</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>711</v>
+        <v>645</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>712</v>
+        <v>46</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>713</v>
+        <v>52</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>711</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>500</v>
+        <v>712</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+        <v>713</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>776</v>
+        <v>500</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>501</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>714</v>
+        <v>776</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>634</v>
+        <v>714</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>635</v>
+        <v>715</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>748</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>297</v>
+        <v>634</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>98</v>
+        <v>635</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -4844,64 +4856,61 @@
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>727</v>
+        <v>297</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>728</v>
+        <v>298</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>47</v>
+        <v>727</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+        <v>728</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>276</v>
+        <v>47</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>277</v>
+        <v>169</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>689</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>646</v>
+        <v>276</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>647</v>
+        <v>277</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>99</v>
+        <v>278</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4909,33 +4918,33 @@
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>167</v>
+        <v>646</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>168</v>
+        <v>647</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+        <v>716</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>657</v>
+        <v>167</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>658</v>
+        <v>168</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>98</v>
+        <v>434</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -4943,13 +4952,16 @@
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>778</v>
+        <v>657</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>99</v>
+        <v>658</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4957,10 +4969,10 @@
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>717</v>
+        <v>778</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>718</v>
+        <v>779</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>99</v>
@@ -4971,114 +4983,114 @@
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>476</v>
+        <v>717</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>718</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>175</v>
+        <v>476</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+        <v>477</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C105" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="F104" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B105" s="2" t="s">
+      <c r="F105" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B106" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="F105" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F106" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>579</v>
+        <v>719</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>580</v>
+        <v>720</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>97</v>
+        <v>580</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
@@ -5086,10 +5098,10 @@
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>736</v>
+        <v>592</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>737</v>
+        <v>593</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>97</v>
@@ -5100,13 +5112,13 @@
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>583</v>
+        <v>736</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>98</v>
+        <v>737</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
@@ -5114,10 +5126,10 @@
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>648</v>
+        <v>583</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>649</v>
+        <v>584</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>98</v>
@@ -5128,13 +5140,13 @@
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>48</v>
+        <v>648</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>97</v>
+        <v>649</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
@@ -5142,30 +5154,27 @@
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>194</v>
+        <v>48</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>49</v>
+        <v>194</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>311</v>
+        <v>202</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -5173,33 +5182,33 @@
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>741</v>
+        <v>49</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>742</v>
+        <v>54</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>100</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>99</v>
+        <v>742</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5207,41 +5216,44 @@
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>655</v>
+        <v>734</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>656</v>
+        <v>735</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="F118" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+        <v>749</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>184</v>
+        <v>655</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>656</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F119" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>566</v>
+        <v>184</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>567</v>
+        <v>185</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>98</v>
@@ -5252,16 +5264,13 @@
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>199</v>
+        <v>566</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>326</v>
+        <v>567</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5269,75 +5278,78 @@
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>667</v>
+        <v>199</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>668</v>
+        <v>200</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>669</v>
+        <v>201</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D124" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="F123" s="3" t="s">
+      <c r="F124" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="B124" s="2" t="s">
+    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B125" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="F124" s="14" t="s">
+      <c r="F125" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>665</v>
+        <v>439</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F126" s="14" t="s">
-        <v>252</v>
+        <v>440</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5345,13 +5357,13 @@
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>98</v>
+        <v>666</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5359,10 +5371,10 @@
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>98</v>
@@ -5373,27 +5385,27 @@
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>561</v>
+        <v>640</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>562</v>
+        <v>641</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>636</v>
+        <v>561</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>97</v>
+        <v>562</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
@@ -5401,30 +5413,27 @@
         <v>43</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>585</v>
+        <v>636</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>583</v>
+        <v>637</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>722</v>
+        <v>585</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>724</v>
+        <v>586</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>583</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>97</v>
@@ -5435,110 +5444,113 @@
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="F133" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="17" t="s">
+      <c r="F134" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B134" s="17" t="s">
+      <c r="B135" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="C134" s="17" t="s">
+      <c r="C135" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="D134" s="17" t="s">
+      <c r="D135" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="E134" s="17"/>
-      <c r="F134" s="21" t="s">
+      <c r="E135" s="17"/>
+      <c r="F135" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="G134" s="17" t="s">
+      <c r="G135" s="17" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A135" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>618</v>
+        <v>691</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>618</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>405</v>
+        <v>265</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>181</v>
+        <v>405</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>98</v>
+        <v>406</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
@@ -5546,69 +5558,69 @@
         <v>269</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="17" t="s">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A141" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B141" s="17" t="s">
+      <c r="B141" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="B142" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C141" s="17" t="s">
+      <c r="C142" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="D141" s="17"/>
-      <c r="E141" s="17"/>
-      <c r="F141" s="20" t="s">
+      <c r="D142" s="17"/>
+      <c r="E142" s="17"/>
+      <c r="F142" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G141" s="17"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A142" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G142" s="17"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>780</v>
+        <v>458</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+        <v>459</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>99</v>
@@ -5619,10 +5631,10 @@
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>99</v>
@@ -5633,16 +5645,13 @@
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>460</v>
+        <v>782</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F146" s="3" t="s">
-        <v>97</v>
+        <v>785</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
@@ -5650,69 +5659,72 @@
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>367</v>
+        <v>460</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>368</v>
+        <v>461</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>56</v>
+        <v>367</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>262</v>
+        <v>368</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>301</v>
+        <v>56</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>769</v>
+        <v>301</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>770</v>
+        <v>302</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>616</v>
+        <v>769</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>617</v>
+        <v>770</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>99</v>
@@ -5723,13 +5735,10 @@
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>513</v>
+        <v>616</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>514</v>
+        <v>617</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>99</v>
@@ -5740,10 +5749,13 @@
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>786</v>
+        <v>513</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>771</v>
+        <v>787</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>514</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>99</v>
@@ -5754,13 +5766,13 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>530</v>
+        <v>786</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>97</v>
+        <v>771</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
@@ -5768,61 +5780,58 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>594</v>
+        <v>530</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="F155" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>57</v>
+        <v>594</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+        <v>595</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>299</v>
+        <v>57</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>377</v>
+        <v>299</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F158" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>383</v>
+        <v>300</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5830,16 +5839,16 @@
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F159" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5847,129 +5856,132 @@
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F160" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>58</v>
+        <v>379</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>382</v>
+      </c>
+      <c r="F161" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>363</v>
+        <v>58</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>327</v>
+        <v>61</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F162" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C164" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F163" s="3" t="s">
+      <c r="F164" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="164" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="17" t="s">
+    <row r="165" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A165" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B164" s="17" t="s">
+      <c r="B165" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="C164" s="17" t="s">
+      <c r="C165" s="17" t="s">
         <v>429</v>
       </c>
-      <c r="F164" s="22" t="s">
+      <c r="F165" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G164" s="17" t="s">
+      <c r="G165" s="17" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A165" s="2" t="s">
+    <row r="166" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A166" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="B166" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C166" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="D165" s="2" t="s">
+      <c r="D166" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="F165" s="3" t="s">
+      <c r="F166" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="166" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="17" t="s">
+    <row r="167" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="B166" s="17" t="s">
+      <c r="B167" s="17" t="s">
         <v>745</v>
       </c>
-      <c r="C166" s="17" t="s">
+      <c r="C167" s="17" t="s">
         <v>746</v>
       </c>
-      <c r="D166" s="17" t="s">
+      <c r="D167" s="17" t="s">
         <v>747</v>
       </c>
-      <c r="F166" s="19" t="s">
+      <c r="F167" s="19" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A167" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
@@ -5977,13 +5989,13 @@
         <v>344</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F168" s="4" t="s">
-        <v>98</v>
+        <v>353</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
@@ -5991,27 +6003,24 @@
         <v>344</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>98</v>
@@ -6022,95 +6031,98 @@
         <v>344</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F172" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G172" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>357</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F173" s="6" t="s">
         <v>140</v>
       </c>
       <c r="G173" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A174" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G174" s="2" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="17" t="s">
+    <row r="175" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="B174" s="17" t="s">
+      <c r="B175" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="C174" s="17" t="s">
+      <c r="C175" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="D174" s="17"/>
-      <c r="E174" s="17"/>
-      <c r="F174" s="20" t="s">
+      <c r="D175" s="17"/>
+      <c r="E175" s="17"/>
+      <c r="F175" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G174" s="17"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A175" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>99</v>
-      </c>
+      <c r="G175" s="17"/>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="F176" s="16" t="s">
-        <v>291</v>
+        <v>813</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
@@ -6118,10 +6130,10 @@
         <v>63</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="F177" s="16" t="s">
         <v>291</v>
@@ -6132,61 +6144,58 @@
         <v>63</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="F178" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>820</v>
+      </c>
+      <c r="F178" s="16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>795</v>
+        <v>829</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="F180" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>828</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>506</v>
+        <v>795</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>507</v>
+        <v>797</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F181" s="14" t="s">
-        <v>387</v>
+        <v>796</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6194,16 +6203,16 @@
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>650</v>
+        <v>506</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>651</v>
+        <v>507</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F182" s="4" t="s">
-        <v>98</v>
+        <v>508</v>
+      </c>
+      <c r="F182" s="14" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6211,58 +6220,58 @@
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>314</v>
+        <v>650</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+        <v>651</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>484</v>
+        <v>314</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>485</v>
+        <v>315</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>801</v>
+        <v>484</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="F185" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+        <v>485</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>64</v>
+        <v>801</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F186" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G186" s="2" t="s">
-        <v>332</v>
+        <v>802</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -6270,41 +6279,44 @@
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>803</v>
+        <v>64</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="F187" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="F187" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+        <v>804</v>
+      </c>
+      <c r="F188" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="F189" s="14" t="s">
-        <v>252</v>
+        <v>810</v>
+      </c>
+      <c r="F189" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
@@ -6312,47 +6324,47 @@
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>830</v>
+        <v>805</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="F190" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>806</v>
+      </c>
+      <c r="F190" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>798</v>
+        <v>830</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="F191" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G191" s="2" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="192" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>549</v>
+        <v>798</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F192" s="5" t="s">
-        <v>99</v>
+        <v>799</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
@@ -6360,13 +6372,13 @@
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>750</v>
+        <v>549</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="F193" s="4" t="s">
-        <v>98</v>
+        <v>550</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
@@ -6374,106 +6386,106 @@
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="F194" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>503</v>
+        <v>756</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F195" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>757</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>821</v>
+        <v>503</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+        <v>504</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>195</v>
+        <v>821</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>196</v>
+        <v>824</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>825</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F198" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>188</v>
+        <v>65</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F199" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F199" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>554</v>
+        <v>188</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F200" s="5" t="s">
-        <v>99</v>
+        <v>189</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6481,38 +6493,38 @@
         <v>63</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>815</v>
+        <v>554</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="F201" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+        <v>555</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>464</v>
+        <v>815</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>463</v>
+        <v>816</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>98</v>
@@ -6523,13 +6535,13 @@
         <v>63</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>822</v>
+        <v>480</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F204" s="5" t="s">
-        <v>99</v>
+        <v>481</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6537,75 +6549,72 @@
         <v>63</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A206" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C205" s="2" t="s">
+      <c r="C206" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F205" s="4" t="s">
+      <c r="F206" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="17" t="s">
+    <row r="207" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A207" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B206" s="17" t="s">
+      <c r="B207" s="17" t="s">
         <v>832</v>
       </c>
-      <c r="C206" s="17" t="s">
+      <c r="C207" s="17" t="s">
         <v>833</v>
       </c>
-      <c r="D206" s="17"/>
-      <c r="E206" s="17"/>
-      <c r="F206" s="19" t="s">
+      <c r="D207" s="17"/>
+      <c r="E207" s="17"/>
+      <c r="F207" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G206" s="17"/>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A207" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F207" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G207" s="17"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>546</v>
+        <v>788</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>548</v>
+        <v>789</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>697</v>
+        <v>546</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>698</v>
+        <v>547</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>696</v>
+        <v>548</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>97</v>
@@ -6616,10 +6625,13 @@
         <v>407</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>415</v>
+        <v>697</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>416</v>
+        <v>698</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>696</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>97</v>
@@ -6630,10 +6642,10 @@
         <v>407</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>97</v>
@@ -6644,10 +6656,10 @@
         <v>407</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>97</v>
@@ -6658,44 +6670,44 @@
         <v>407</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>600</v>
+        <v>419</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>97</v>
@@ -6706,30 +6718,27 @@
         <v>407</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>517</v>
+        <v>409</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F217" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G217" s="2" t="s">
-        <v>519</v>
+        <v>411</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6737,48 +6746,48 @@
         <v>407</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>467</v>
+        <v>517</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F218" s="3"/>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+        <v>518</v>
+      </c>
+      <c r="F218" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>515</v>
+        <v>467</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F219" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G219" s="2" t="s">
-        <v>520</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F219" s="3"/>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F220" s="3" t="s">
-        <v>97</v>
+        <v>516</v>
+      </c>
+      <c r="F220" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
@@ -6786,13 +6795,16 @@
         <v>407</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F221" s="5" t="s">
-        <v>99</v>
+        <v>491</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
@@ -6800,10 +6812,10 @@
         <v>407</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="F222" s="5" t="s">
         <v>99</v>
@@ -6814,10 +6826,10 @@
         <v>407</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>410</v>
+        <v>454</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>412</v>
+        <v>455</v>
       </c>
       <c r="F223" s="5" t="s">
         <v>99</v>
@@ -6828,10 +6840,10 @@
         <v>407</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>457</v>
+        <v>412</v>
       </c>
       <c r="F224" s="5" t="s">
         <v>99</v>
@@ -6842,106 +6854,106 @@
         <v>407</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>528</v>
+        <v>456</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F225" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>457</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>413</v>
+        <v>528</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F226" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>529</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B227" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F227" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A228" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C227" s="2" t="s">
+      <c r="C228" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="F227" s="19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A228" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="B228" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="C228" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="D228" s="17"/>
-      <c r="E228" s="17"/>
       <c r="F228" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G228" s="17"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A229" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>99</v>
-      </c>
+    </row>
+    <row r="229" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A229" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B229" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="C229" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="D229" s="17"/>
+      <c r="E229" s="17"/>
+      <c r="F229" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G229" s="17"/>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>292</v>
+        <v>203</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F230" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+      <c r="F230" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>205</v>
+        <v>292</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F231" s="5" t="s">
-        <v>99</v>
+        <v>293</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F231" s="12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="232" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6949,30 +6961,30 @@
         <v>91</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F232" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G232" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F233" s="5" t="s">
-        <v>99</v>
+        <v>208</v>
+      </c>
+      <c r="F233" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
@@ -6980,10 +6992,10 @@
         <v>91</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="F234" s="5" t="s">
         <v>99</v>
@@ -6994,128 +7006,128 @@
         <v>91</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>210</v>
+        <v>92</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F235" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B236" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A237" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B237" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C236" s="2" t="s">
+      <c r="C237" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F236" s="12" t="s">
+      <c r="F237" s="12" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A237" s="17" t="s">
+    <row r="238" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A238" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B237" s="17" t="s">
+      <c r="B238" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C237" s="17" t="s">
+      <c r="C238" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D237" s="17"/>
-      <c r="E237" s="17"/>
-      <c r="F237" s="20" t="s">
+      <c r="D238" s="17"/>
+      <c r="E238" s="17"/>
+      <c r="F238" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G237" s="17"/>
-    </row>
-    <row r="238" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A238" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F238" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G238" s="2" t="s">
-        <v>319</v>
-      </c>
+      <c r="G238" s="17"/>
     </row>
     <row r="239" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="F239" s="6" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>731</v>
+        <v>190</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>732</v>
+        <v>192</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>140</v>
       </c>
       <c r="G240" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A241" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="F241" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G241" s="2" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A241" s="17" t="s">
+    <row r="242" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A242" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B241" s="17" t="s">
+      <c r="B242" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="C241" s="17" t="s">
+      <c r="C242" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="D241" s="17"/>
-      <c r="E241" s="17"/>
-      <c r="F241" s="22" t="s">
+      <c r="D242" s="17"/>
+      <c r="E242" s="17"/>
+      <c r="F242" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G241" s="17" t="s">
+      <c r="G242" s="17" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A242" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="F242" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
@@ -7123,13 +7135,13 @@
         <v>71</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>537</v>
+        <v>619</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F243" s="5" t="s">
-        <v>99</v>
+        <v>620</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
@@ -7137,13 +7149,13 @@
         <v>71</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>72</v>
+        <v>537</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F244" s="4" t="s">
-        <v>98</v>
+        <v>538</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
@@ -7151,41 +7163,41 @@
         <v>71</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F245" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>541</v>
+        <v>73</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>542</v>
+        <v>81</v>
       </c>
       <c r="F246" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>398</v>
+        <v>541</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F247" s="4" t="s">
-        <v>98</v>
+        <v>542</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
@@ -7193,10 +7205,10 @@
         <v>71</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>663</v>
+        <v>398</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>664</v>
+        <v>399</v>
       </c>
       <c r="F248" s="4" t="s">
         <v>98</v>
@@ -7207,13 +7219,13 @@
         <v>71</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>539</v>
+        <v>663</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F249" s="5" t="s">
-        <v>99</v>
+        <v>664</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
@@ -7221,13 +7233,13 @@
         <v>71</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>271</v>
+        <v>539</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F250" s="3" t="s">
-        <v>97</v>
+        <v>540</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
@@ -7235,44 +7247,44 @@
         <v>71</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F252" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>790</v>
+        <v>230</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="F253" s="3" t="s">
-        <v>97</v>
+        <v>231</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
@@ -7280,13 +7292,13 @@
         <v>71</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>605</v>
+        <v>790</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F254" s="5" t="s">
-        <v>99</v>
+        <v>791</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
@@ -7294,10 +7306,10 @@
         <v>71</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F255" s="5" t="s">
         <v>99</v>
@@ -7308,10 +7320,10 @@
         <v>71</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>226</v>
+        <v>607</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>227</v>
+        <v>608</v>
       </c>
       <c r="F256" s="5" t="s">
         <v>99</v>
@@ -7322,10 +7334,10 @@
         <v>71</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>99</v>
@@ -7336,13 +7348,10 @@
         <v>71</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>621</v>
+        <v>222</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>623</v>
+        <v>223</v>
       </c>
       <c r="F258" s="5" t="s">
         <v>99</v>
@@ -7353,10 +7362,13 @@
         <v>71</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>610</v>
+        <v>622</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>623</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>99</v>
@@ -7367,13 +7379,13 @@
         <v>71</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>694</v>
+        <v>609</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="F260" s="3" t="s">
-        <v>97</v>
+        <v>610</v>
+      </c>
+      <c r="F260" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
@@ -7381,10 +7393,10 @@
         <v>71</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>624</v>
+        <v>694</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>625</v>
+        <v>695</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>97</v>
@@ -7395,10 +7407,10 @@
         <v>71</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>97</v>
@@ -7409,13 +7421,13 @@
         <v>71</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F263" s="4" t="s">
-        <v>98</v>
+        <v>597</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
@@ -7423,44 +7435,44 @@
         <v>71</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>235</v>
+        <v>576</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>236</v>
+        <v>577</v>
       </c>
       <c r="F264" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F265" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="G265" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>74</v>
+        <v>273</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F266" s="5" t="s">
-        <v>99</v>
+        <v>274</v>
+      </c>
+      <c r="F266" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="G266" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
@@ -7468,10 +7480,10 @@
         <v>71</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F267" s="5" t="s">
         <v>99</v>
@@ -7482,10 +7494,10 @@
         <v>71</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F268" s="5" t="s">
         <v>99</v>
@@ -7496,13 +7508,13 @@
         <v>71</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F269" s="4" t="s">
-        <v>98</v>
+        <v>84</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
@@ -7510,16 +7522,13 @@
         <v>71</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>611</v>
+        <v>77</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F270" s="5" t="s">
-        <v>99</v>
+        <v>85</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
@@ -7527,13 +7536,16 @@
         <v>71</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>435</v>
+        <v>611</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F271" s="4" t="s">
-        <v>98</v>
+        <v>612</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
@@ -7541,41 +7553,41 @@
         <v>71</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="F272" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>626</v>
+        <v>465</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F273" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>725</v>
+        <v>626</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="F274" s="3" t="s">
-        <v>97</v>
+        <v>627</v>
+      </c>
+      <c r="F274" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
@@ -7583,10 +7595,10 @@
         <v>71</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>78</v>
+        <v>725</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>86</v>
+        <v>726</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>97</v>
@@ -7597,30 +7609,27 @@
         <v>71</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F276" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>281</v>
+        <v>535</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F277" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G277" s="2" t="s">
-        <v>323</v>
+        <v>536</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="278" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7628,10 +7637,10 @@
         <v>71</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F278" s="16" t="s">
         <v>291</v>
@@ -7645,10 +7654,10 @@
         <v>71</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="F279" s="16" t="s">
         <v>291</v>
@@ -7657,35 +7666,38 @@
         <v>323</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F280" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+      <c r="F280" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>677</v>
+        <v>224</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F281" s="5" t="s">
-        <v>232</v>
+        <v>225</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7693,58 +7705,58 @@
         <v>71</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>79</v>
+        <v>677</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F282" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+        <v>678</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>729</v>
+        <v>79</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>730</v>
+        <v>87</v>
       </c>
       <c r="F283" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>430</v>
+        <v>729</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F284" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G284" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+        <v>730</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>628</v>
+        <v>430</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="F285" s="5" t="s">
-        <v>99</v>
+        <v>431</v>
+      </c>
+      <c r="F285" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G285" s="2" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
@@ -7752,44 +7764,44 @@
         <v>71</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>494</v>
+        <v>628</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>495</v>
+        <v>629</v>
       </c>
       <c r="F286" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>762</v>
+        <v>494</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="F287" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G287" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+      <c r="F287" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>239</v>
+        <v>762</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F288" s="14" t="s">
-        <v>252</v>
+        <v>763</v>
+      </c>
+      <c r="F288" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G288" s="2" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -7797,13 +7809,13 @@
         <v>71</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F289" s="5" t="s">
-        <v>99</v>
+        <v>240</v>
+      </c>
+      <c r="F289" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -7811,13 +7823,13 @@
         <v>71</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>630</v>
+        <v>286</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F290" s="4" t="s">
-        <v>98</v>
+        <v>285</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -7825,13 +7837,13 @@
         <v>71</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>228</v>
+        <v>630</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F291" s="5" t="s">
-        <v>99</v>
+        <v>631</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
@@ -7839,10 +7851,10 @@
         <v>71</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>614</v>
+        <v>228</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>615</v>
+        <v>229</v>
       </c>
       <c r="F292" s="5" t="s">
         <v>99</v>
@@ -7853,13 +7865,13 @@
         <v>71</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>220</v>
+        <v>614</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F293" s="12" t="s">
-        <v>244</v>
+        <v>615</v>
+      </c>
+      <c r="F293" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.35">
@@ -7867,13 +7879,13 @@
         <v>71</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>511</v>
+        <v>220</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F294" s="14" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="F294" s="12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.35">
@@ -7881,16 +7893,13 @@
         <v>71</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E295" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F295" s="5" t="s">
-        <v>99</v>
+        <v>512</v>
+      </c>
+      <c r="F295" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.35">
@@ -7898,44 +7907,44 @@
         <v>71</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>218</v>
+        <v>509</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>219</v>
+        <v>510</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>632</v>
+        <v>218</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F297" s="20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+      <c r="F297" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>571</v>
+        <v>632</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="F298" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G298" s="2" t="s">
-        <v>574</v>
+        <v>633</v>
+      </c>
+      <c r="F298" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="299" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7943,81 +7952,81 @@
         <v>71</v>
       </c>
       <c r="B299" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G299" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A300" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B300" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="C299" s="2" t="s">
+      <c r="C300" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="F299" s="16" t="s">
+      <c r="F300" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="G299" s="2" t="s">
+      <c r="G300" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A300" s="17" t="s">
+    <row r="301" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A301" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B300" s="17" t="s">
+      <c r="B301" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="C300" s="17" t="s">
+      <c r="C301" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="D300" s="17"/>
-      <c r="E300" s="17"/>
-      <c r="F300" s="20" t="s">
+      <c r="D301" s="17"/>
+      <c r="E301" s="17"/>
+      <c r="F301" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G300" s="17"/>
-    </row>
-    <row r="301" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A301" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F301" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G301" s="17"/>
+    </row>
+    <row r="302" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>390</v>
+        <v>303</v>
       </c>
       <c r="F302" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>243</v>
+        <v>390</v>
       </c>
       <c r="F303" s="5" t="s">
         <v>99</v>
@@ -8028,27 +8037,30 @@
         <v>88</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>792</v>
+        <v>241</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F304" s="25" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F304" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>338</v>
+        <v>792</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F305" s="4" t="s">
-        <v>98</v>
+        <v>793</v>
+      </c>
+      <c r="F305" s="25" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.35">
@@ -8056,36 +8068,50 @@
         <v>88</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>551</v>
+        <v>338</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="D306" s="2" t="s">
-        <v>553</v>
+        <v>339</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A307" s="17" t="s">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A307" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B307" s="17" t="s">
+      <c r="B307" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A308" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B308" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C307" s="17" t="s">
+      <c r="C308" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="D307" s="17" t="s">
+      <c r="D308" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="E307" s="17"/>
-      <c r="F307" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G307" s="17"/>
+      <c r="E308" s="17"/>
+      <c r="F308" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G308" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C977ABCA-1BB2-4D89-9B53-88D4D882D946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B01FBE4-3B6E-4E45-A6AB-63D6C15D47FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="848">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2564,6 +2564,18 @@
   </si>
   <si>
     <t>You plan on using a policy mandated change in distributed solar capacity additions</t>
+  </si>
+  <si>
+    <t>PEAAC</t>
+  </si>
+  <si>
+    <t>Process Emissions Additions and Costs</t>
+  </si>
+  <si>
+    <t>Process Emissions Additions and Costs, Marginal Cost Definitions</t>
+  </si>
+  <si>
+    <t>You want to test the addition rather than the reduction of process emissions for select industries</t>
   </si>
 </sst>
 </file>
@@ -3375,7 +3387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G308"/>
+  <dimension ref="A1:G309"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -6462,44 +6474,50 @@
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>65</v>
+        <v>844</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>67</v>
+        <v>845</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F199" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+        <v>846</v>
+      </c>
+      <c r="F199" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>188</v>
+        <v>65</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F200" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F200" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>554</v>
+        <v>188</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F201" s="5" t="s">
-        <v>99</v>
+        <v>189</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6507,38 +6525,38 @@
         <v>63</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>815</v>
+        <v>554</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="F202" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+        <v>555</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>464</v>
+        <v>815</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>463</v>
+        <v>816</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>98</v>
@@ -6549,13 +6567,13 @@
         <v>63</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>822</v>
+        <v>480</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F205" s="5" t="s">
-        <v>99</v>
+        <v>481</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6563,75 +6581,72 @@
         <v>63</v>
       </c>
       <c r="B206" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A207" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B207" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="C207" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F206" s="4" t="s">
+      <c r="F207" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="17" t="s">
+    <row r="208" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A208" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B207" s="17" t="s">
+      <c r="B208" s="17" t="s">
         <v>832</v>
       </c>
-      <c r="C207" s="17" t="s">
+      <c r="C208" s="17" t="s">
         <v>833</v>
       </c>
-      <c r="D207" s="17"/>
-      <c r="E207" s="17"/>
-      <c r="F207" s="19" t="s">
+      <c r="D208" s="17"/>
+      <c r="E208" s="17"/>
+      <c r="F208" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G207" s="17"/>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A208" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F208" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G208" s="17"/>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>546</v>
+        <v>788</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>548</v>
+        <v>789</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>697</v>
+        <v>546</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>698</v>
+        <v>547</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>696</v>
+        <v>548</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>97</v>
@@ -6642,10 +6657,13 @@
         <v>407</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>415</v>
+        <v>697</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>416</v>
+        <v>698</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>696</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>97</v>
@@ -6656,10 +6674,10 @@
         <v>407</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>97</v>
@@ -6670,10 +6688,10 @@
         <v>407</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>97</v>
@@ -6684,44 +6702,44 @@
         <v>407</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>600</v>
+        <v>419</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>97</v>
@@ -6732,30 +6750,27 @@
         <v>407</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>517</v>
+        <v>409</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F218" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G218" s="2" t="s">
-        <v>519</v>
+        <v>411</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="219" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6763,48 +6778,48 @@
         <v>407</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>467</v>
+        <v>517</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F219" s="3"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+        <v>518</v>
+      </c>
+      <c r="F219" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>515</v>
+        <v>467</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F220" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>520</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F220" s="3"/>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F221" s="3" t="s">
-        <v>97</v>
+        <v>516</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
@@ -6812,13 +6827,16 @@
         <v>407</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F222" s="5" t="s">
-        <v>99</v>
+        <v>491</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
@@ -6826,10 +6844,10 @@
         <v>407</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="F223" s="5" t="s">
         <v>99</v>
@@ -6840,10 +6858,10 @@
         <v>407</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>410</v>
+        <v>454</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>412</v>
+        <v>455</v>
       </c>
       <c r="F224" s="5" t="s">
         <v>99</v>
@@ -6854,10 +6872,10 @@
         <v>407</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>457</v>
+        <v>412</v>
       </c>
       <c r="F225" s="5" t="s">
         <v>99</v>
@@ -6868,106 +6886,106 @@
         <v>407</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>528</v>
+        <v>456</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F226" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>457</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>413</v>
+        <v>528</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F227" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G227" s="2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>529</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F228" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A229" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B229" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C228" s="2" t="s">
+      <c r="C229" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="F228" s="19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A229" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="B229" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="C229" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="D229" s="17"/>
-      <c r="E229" s="17"/>
       <c r="F229" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G229" s="17"/>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A230" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F230" s="5" t="s">
-        <v>99</v>
-      </c>
+    </row>
+    <row r="230" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A230" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B230" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="C230" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="D230" s="17"/>
+      <c r="E230" s="17"/>
+      <c r="F230" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G230" s="17"/>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>292</v>
+        <v>203</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F231" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>205</v>
+        <v>292</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F232" s="5" t="s">
-        <v>99</v>
+        <v>293</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F232" s="12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="233" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6975,30 +6993,30 @@
         <v>91</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F233" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G233" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F234" s="5" t="s">
-        <v>99</v>
+        <v>208</v>
+      </c>
+      <c r="F234" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
@@ -7006,10 +7024,10 @@
         <v>91</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="F235" s="5" t="s">
         <v>99</v>
@@ -7020,128 +7038,128 @@
         <v>91</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>210</v>
+        <v>92</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F236" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B237" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A238" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B238" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C237" s="2" t="s">
+      <c r="C238" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F237" s="12" t="s">
+      <c r="F238" s="12" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A238" s="17" t="s">
+    <row r="239" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A239" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B238" s="17" t="s">
+      <c r="B239" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C238" s="17" t="s">
+      <c r="C239" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D238" s="17"/>
-      <c r="E238" s="17"/>
-      <c r="F238" s="20" t="s">
+      <c r="D239" s="17"/>
+      <c r="E239" s="17"/>
+      <c r="F239" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G238" s="17"/>
-    </row>
-    <row r="239" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A239" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F239" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G239" s="2" t="s">
-        <v>319</v>
-      </c>
+      <c r="G239" s="17"/>
     </row>
     <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="F240" s="6" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>731</v>
+        <v>190</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>732</v>
+        <v>192</v>
       </c>
       <c r="F241" s="6" t="s">
         <v>140</v>
       </c>
       <c r="G241" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A242" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="F242" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G242" s="2" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A242" s="17" t="s">
+    <row r="243" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A243" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B242" s="17" t="s">
+      <c r="B243" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="C242" s="17" t="s">
+      <c r="C243" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="D242" s="17"/>
-      <c r="E242" s="17"/>
-      <c r="F242" s="22" t="s">
+      <c r="D243" s="17"/>
+      <c r="E243" s="17"/>
+      <c r="F243" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G242" s="17" t="s">
+      <c r="G243" s="17" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A243" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="F243" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
@@ -7149,13 +7167,13 @@
         <v>71</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>537</v>
+        <v>619</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F244" s="5" t="s">
-        <v>99</v>
+        <v>620</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
@@ -7163,13 +7181,13 @@
         <v>71</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>72</v>
+        <v>537</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F245" s="4" t="s">
-        <v>98</v>
+        <v>538</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
@@ -7177,41 +7195,41 @@
         <v>71</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F246" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>541</v>
+        <v>73</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>542</v>
+        <v>81</v>
       </c>
       <c r="F247" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>398</v>
+        <v>541</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F248" s="4" t="s">
-        <v>98</v>
+        <v>542</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
@@ -7219,10 +7237,10 @@
         <v>71</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>663</v>
+        <v>398</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>664</v>
+        <v>399</v>
       </c>
       <c r="F249" s="4" t="s">
         <v>98</v>
@@ -7233,13 +7251,13 @@
         <v>71</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>539</v>
+        <v>663</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F250" s="5" t="s">
-        <v>99</v>
+        <v>664</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
@@ -7247,13 +7265,13 @@
         <v>71</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>271</v>
+        <v>539</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F251" s="3" t="s">
-        <v>97</v>
+        <v>540</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
@@ -7261,44 +7279,44 @@
         <v>71</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F253" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>790</v>
+        <v>230</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="F254" s="3" t="s">
-        <v>97</v>
+        <v>231</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
@@ -7306,13 +7324,13 @@
         <v>71</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>605</v>
+        <v>790</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F255" s="5" t="s">
-        <v>99</v>
+        <v>791</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
@@ -7320,10 +7338,10 @@
         <v>71</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F256" s="5" t="s">
         <v>99</v>
@@ -7334,10 +7352,10 @@
         <v>71</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>226</v>
+        <v>607</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>227</v>
+        <v>608</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>99</v>
@@ -7348,10 +7366,10 @@
         <v>71</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F258" s="5" t="s">
         <v>99</v>
@@ -7362,13 +7380,10 @@
         <v>71</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>621</v>
+        <v>222</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>623</v>
+        <v>223</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>99</v>
@@ -7379,10 +7394,13 @@
         <v>71</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>610</v>
+        <v>622</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>623</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>99</v>
@@ -7393,13 +7411,13 @@
         <v>71</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>694</v>
+        <v>609</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="F261" s="3" t="s">
-        <v>97</v>
+        <v>610</v>
+      </c>
+      <c r="F261" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
@@ -7407,10 +7425,10 @@
         <v>71</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>624</v>
+        <v>694</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>625</v>
+        <v>695</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>97</v>
@@ -7421,10 +7439,10 @@
         <v>71</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>97</v>
@@ -7435,13 +7453,13 @@
         <v>71</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F264" s="4" t="s">
-        <v>98</v>
+        <v>597</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -7449,44 +7467,44 @@
         <v>71</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>235</v>
+        <v>576</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>236</v>
+        <v>577</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F266" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="G266" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>74</v>
+        <v>273</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F267" s="5" t="s">
-        <v>99</v>
+        <v>274</v>
+      </c>
+      <c r="F267" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="G267" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
@@ -7494,10 +7512,10 @@
         <v>71</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F268" s="5" t="s">
         <v>99</v>
@@ -7508,10 +7526,10 @@
         <v>71</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F269" s="5" t="s">
         <v>99</v>
@@ -7522,13 +7540,13 @@
         <v>71</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F270" s="4" t="s">
-        <v>98</v>
+        <v>84</v>
+      </c>
+      <c r="F270" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
@@ -7536,16 +7554,13 @@
         <v>71</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>611</v>
+        <v>77</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D271" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>99</v>
+        <v>85</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
@@ -7553,13 +7568,16 @@
         <v>71</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>435</v>
+        <v>611</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F272" s="4" t="s">
-        <v>98</v>
+        <v>612</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
@@ -7567,41 +7585,41 @@
         <v>71</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="F273" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>626</v>
+        <v>465</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F274" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>725</v>
+        <v>626</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="F275" s="3" t="s">
-        <v>97</v>
+        <v>627</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
@@ -7609,10 +7627,10 @@
         <v>71</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>78</v>
+        <v>725</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>86</v>
+        <v>726</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>97</v>
@@ -7623,30 +7641,27 @@
         <v>71</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F277" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>281</v>
+        <v>535</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F278" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G278" s="2" t="s">
-        <v>323</v>
+        <v>536</v>
+      </c>
+      <c r="F278" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7654,10 +7669,10 @@
         <v>71</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F279" s="16" t="s">
         <v>291</v>
@@ -7671,10 +7686,10 @@
         <v>71</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="F280" s="16" t="s">
         <v>291</v>
@@ -7683,35 +7698,38 @@
         <v>323</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F281" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+      <c r="F281" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G281" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>677</v>
+        <v>224</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F282" s="5" t="s">
-        <v>232</v>
+        <v>225</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F282" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7719,58 +7737,58 @@
         <v>71</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>79</v>
+        <v>677</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F283" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+        <v>678</v>
+      </c>
+      <c r="F283" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>729</v>
+        <v>79</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>730</v>
+        <v>87</v>
       </c>
       <c r="F284" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>430</v>
+        <v>729</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F285" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G285" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+        <v>730</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>628</v>
+        <v>430</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="F286" s="5" t="s">
-        <v>99</v>
+        <v>431</v>
+      </c>
+      <c r="F286" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G286" s="2" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -7778,44 +7796,44 @@
         <v>71</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>494</v>
+        <v>628</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>495</v>
+        <v>629</v>
       </c>
       <c r="F287" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>762</v>
+        <v>494</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="F288" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G288" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+      <c r="F288" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>239</v>
+        <v>762</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F289" s="14" t="s">
-        <v>252</v>
+        <v>763</v>
+      </c>
+      <c r="F289" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G289" s="2" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -7823,13 +7841,13 @@
         <v>71</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F290" s="5" t="s">
-        <v>99</v>
+        <v>240</v>
+      </c>
+      <c r="F290" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -7837,13 +7855,13 @@
         <v>71</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>630</v>
+        <v>286</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F291" s="4" t="s">
-        <v>98</v>
+        <v>285</v>
+      </c>
+      <c r="F291" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
@@ -7851,13 +7869,13 @@
         <v>71</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>228</v>
+        <v>630</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F292" s="5" t="s">
-        <v>99</v>
+        <v>631</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.35">
@@ -7865,10 +7883,10 @@
         <v>71</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>614</v>
+        <v>228</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>615</v>
+        <v>229</v>
       </c>
       <c r="F293" s="5" t="s">
         <v>99</v>
@@ -7879,13 +7897,13 @@
         <v>71</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>220</v>
+        <v>614</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F294" s="12" t="s">
-        <v>244</v>
+        <v>615</v>
+      </c>
+      <c r="F294" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.35">
@@ -7893,13 +7911,13 @@
         <v>71</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>511</v>
+        <v>220</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F295" s="14" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="F295" s="12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.35">
@@ -7907,16 +7925,13 @@
         <v>71</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E296" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F296" s="5" t="s">
-        <v>99</v>
+        <v>512</v>
+      </c>
+      <c r="F296" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.35">
@@ -7924,44 +7939,44 @@
         <v>71</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>218</v>
+        <v>509</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>219</v>
+        <v>510</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>632</v>
+        <v>218</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F298" s="20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+      <c r="F298" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>571</v>
+        <v>632</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="F299" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G299" s="2" t="s">
-        <v>574</v>
+        <v>633</v>
+      </c>
+      <c r="F299" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="300" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7969,81 +7984,81 @@
         <v>71</v>
       </c>
       <c r="B300" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G300" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A301" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B301" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="C300" s="2" t="s">
+      <c r="C301" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="F300" s="16" t="s">
+      <c r="F301" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="G300" s="2" t="s">
+      <c r="G301" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A301" s="17" t="s">
+    <row r="302" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A302" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B301" s="17" t="s">
+      <c r="B302" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="C301" s="17" t="s">
+      <c r="C302" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="D301" s="17"/>
-      <c r="E301" s="17"/>
-      <c r="F301" s="20" t="s">
+      <c r="D302" s="17"/>
+      <c r="E302" s="17"/>
+      <c r="F302" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G301" s="17"/>
-    </row>
-    <row r="302" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A302" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D302" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F302" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G302" s="17"/>
+    </row>
+    <row r="303" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>390</v>
+        <v>303</v>
       </c>
       <c r="F303" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="304" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>243</v>
+        <v>390</v>
       </c>
       <c r="F304" s="5" t="s">
         <v>99</v>
@@ -8054,27 +8069,30 @@
         <v>88</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>792</v>
+        <v>241</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F305" s="25" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F305" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>338</v>
+        <v>792</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F306" s="4" t="s">
-        <v>98</v>
+        <v>793</v>
+      </c>
+      <c r="F306" s="25" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.35">
@@ -8082,36 +8100,50 @@
         <v>88</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>551</v>
+        <v>338</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="D307" s="2" t="s">
-        <v>553</v>
+        <v>339</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A308" s="17" t="s">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A308" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B308" s="17" t="s">
+      <c r="B308" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A309" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B309" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C308" s="17" t="s">
+      <c r="C309" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="D308" s="17" t="s">
+      <c r="D309" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="E308" s="17"/>
-      <c r="F308" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G308" s="17"/>
+      <c r="E309" s="17"/>
+      <c r="F309" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G309" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B01FBE4-3B6E-4E45-A6AB-63D6C15D47FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693EE7FF-73B1-464B-8372-BD3A2CB5CA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="850">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2576,6 +2576,12 @@
   </si>
   <si>
     <t>You want to test the addition rather than the reduction of process emissions for select industries</t>
+  </si>
+  <si>
+    <t>BRZSPbMR</t>
+  </si>
+  <si>
+    <t>BAU Required ZEV Sales Perc by Model Region</t>
   </si>
 </sst>
 </file>
@@ -3387,7 +3393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G309"/>
+  <dimension ref="A1:G310"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -7425,10 +7431,10 @@
         <v>71</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>694</v>
+        <v>848</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>695</v>
+        <v>849</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>97</v>
@@ -7439,10 +7445,10 @@
         <v>71</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>624</v>
+        <v>694</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>625</v>
+        <v>695</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>97</v>
@@ -7453,10 +7459,10 @@
         <v>71</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>97</v>
@@ -7467,13 +7473,13 @@
         <v>71</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F265" s="4" t="s">
-        <v>98</v>
+        <v>597</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
@@ -7481,44 +7487,44 @@
         <v>71</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>235</v>
+        <v>576</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>236</v>
+        <v>577</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F267" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="G267" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>74</v>
+        <v>273</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>99</v>
+        <v>274</v>
+      </c>
+      <c r="F268" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
@@ -7526,10 +7532,10 @@
         <v>71</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F269" s="5" t="s">
         <v>99</v>
@@ -7540,10 +7546,10 @@
         <v>71</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F270" s="5" t="s">
         <v>99</v>
@@ -7554,13 +7560,13 @@
         <v>71</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F271" s="4" t="s">
-        <v>98</v>
+        <v>84</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
@@ -7568,16 +7574,13 @@
         <v>71</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>611</v>
+        <v>77</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F272" s="5" t="s">
-        <v>99</v>
+        <v>85</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
@@ -7585,13 +7588,16 @@
         <v>71</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>435</v>
+        <v>611</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F273" s="4" t="s">
-        <v>98</v>
+        <v>612</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F273" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
@@ -7599,41 +7605,41 @@
         <v>71</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="F274" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>626</v>
+        <v>465</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F275" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>725</v>
+        <v>626</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="F276" s="3" t="s">
-        <v>97</v>
+        <v>627</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.35">
@@ -7641,10 +7647,10 @@
         <v>71</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>78</v>
+        <v>725</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>86</v>
+        <v>726</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>97</v>
@@ -7655,30 +7661,27 @@
         <v>71</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F278" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>281</v>
+        <v>535</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F279" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G279" s="2" t="s">
-        <v>323</v>
+        <v>536</v>
+      </c>
+      <c r="F279" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7686,10 +7689,10 @@
         <v>71</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F280" s="16" t="s">
         <v>291</v>
@@ -7703,10 +7706,10 @@
         <v>71</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="F281" s="16" t="s">
         <v>291</v>
@@ -7715,35 +7718,38 @@
         <v>323</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F282" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+      <c r="F282" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>677</v>
+        <v>224</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F283" s="5" t="s">
-        <v>232</v>
+        <v>225</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="284" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7751,58 +7757,58 @@
         <v>71</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>79</v>
+        <v>677</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F284" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+        <v>678</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>729</v>
+        <v>79</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>730</v>
+        <v>87</v>
       </c>
       <c r="F285" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>430</v>
+        <v>729</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F286" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G286" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+        <v>730</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>628</v>
+        <v>430</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="F287" s="5" t="s">
-        <v>99</v>
+        <v>431</v>
+      </c>
+      <c r="F287" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
@@ -7810,44 +7816,44 @@
         <v>71</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>494</v>
+        <v>628</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>495</v>
+        <v>629</v>
       </c>
       <c r="F288" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>762</v>
+        <v>494</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="F289" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G289" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+      <c r="F289" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>239</v>
+        <v>762</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F290" s="14" t="s">
-        <v>252</v>
+        <v>763</v>
+      </c>
+      <c r="F290" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G290" s="2" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -7855,13 +7861,13 @@
         <v>71</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F291" s="5" t="s">
-        <v>99</v>
+        <v>240</v>
+      </c>
+      <c r="F291" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
@@ -7869,13 +7875,13 @@
         <v>71</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>630</v>
+        <v>286</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F292" s="4" t="s">
-        <v>98</v>
+        <v>285</v>
+      </c>
+      <c r="F292" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.35">
@@ -7883,13 +7889,13 @@
         <v>71</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>228</v>
+        <v>630</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F293" s="5" t="s">
-        <v>99</v>
+        <v>631</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.35">
@@ -7897,10 +7903,10 @@
         <v>71</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>614</v>
+        <v>228</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>615</v>
+        <v>229</v>
       </c>
       <c r="F294" s="5" t="s">
         <v>99</v>
@@ -7911,13 +7917,13 @@
         <v>71</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>220</v>
+        <v>614</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F295" s="12" t="s">
-        <v>244</v>
+        <v>615</v>
+      </c>
+      <c r="F295" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.35">
@@ -7925,13 +7931,13 @@
         <v>71</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>511</v>
+        <v>220</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F296" s="14" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="F296" s="12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.35">
@@ -7939,16 +7945,13 @@
         <v>71</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E297" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F297" s="5" t="s">
-        <v>99</v>
+        <v>512</v>
+      </c>
+      <c r="F297" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.35">
@@ -7956,44 +7959,44 @@
         <v>71</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>218</v>
+        <v>509</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>219</v>
+        <v>510</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="F298" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>632</v>
+        <v>218</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F299" s="20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>571</v>
+        <v>632</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="F300" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G300" s="2" t="s">
-        <v>574</v>
+        <v>633</v>
+      </c>
+      <c r="F300" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="301" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -8001,81 +8004,81 @@
         <v>71</v>
       </c>
       <c r="B301" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G301" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A302" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B302" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="C301" s="2" t="s">
+      <c r="C302" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="F301" s="16" t="s">
+      <c r="F302" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="G301" s="2" t="s">
+      <c r="G302" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A302" s="17" t="s">
+    <row r="303" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A303" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B302" s="17" t="s">
+      <c r="B303" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="C302" s="17" t="s">
+      <c r="C303" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="D302" s="17"/>
-      <c r="E302" s="17"/>
-      <c r="F302" s="20" t="s">
+      <c r="D303" s="17"/>
+      <c r="E303" s="17"/>
+      <c r="F303" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G302" s="17"/>
-    </row>
-    <row r="303" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A303" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D303" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F303" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G303" s="17"/>
+    </row>
+    <row r="304" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>390</v>
+        <v>303</v>
       </c>
       <c r="F304" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>243</v>
+        <v>390</v>
       </c>
       <c r="F305" s="5" t="s">
         <v>99</v>
@@ -8086,27 +8089,30 @@
         <v>88</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>792</v>
+        <v>241</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F306" s="25" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F306" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>338</v>
+        <v>792</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F307" s="4" t="s">
-        <v>98</v>
+        <v>793</v>
+      </c>
+      <c r="F307" s="25" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.35">
@@ -8114,36 +8120,50 @@
         <v>88</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>551</v>
+        <v>338</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="D308" s="2" t="s">
-        <v>553</v>
+        <v>339</v>
       </c>
       <c r="F308" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A309" s="17" t="s">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A309" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B309" s="17" t="s">
+      <c r="B309" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A310" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B310" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C309" s="17" t="s">
+      <c r="C310" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="D309" s="17" t="s">
+      <c r="D310" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="E309" s="17"/>
-      <c r="F309" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G309" s="17"/>
+      <c r="E310" s="17"/>
+      <c r="F310" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G310" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693EE7FF-73B1-464B-8372-BD3A2CB5CA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4A654E-745D-4DDC-969B-165E241E15DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="852">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2582,6 +2582,12 @@
   </si>
   <si>
     <t>BAU Required ZEV Sales Perc by Model Region</t>
+  </si>
+  <si>
+    <t>TACFMfPBTY</t>
+  </si>
+  <si>
+    <t>Time Adjusted Capacity Factor Multiplier for Plants Built This Year</t>
   </si>
 </sst>
 </file>
@@ -3063,82 +3069,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>97</v>
       </c>
@@ -3146,32 +3152,32 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
         <v>244</v>
       </c>
@@ -3179,17 +3185,17 @@
         <v>247</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>99</v>
       </c>
@@ -3197,42 +3203,42 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>98</v>
       </c>
@@ -3240,84 +3246,84 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>252</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>140</v>
       </c>
@@ -3325,62 +3331,62 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3393,20 +3399,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G310"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G311"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="67" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.81640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.54296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="54" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.81640625" style="2"/>
+    <col min="8" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -3429,7 +3435,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -3448,7 +3454,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -3465,7 +3471,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -3479,7 +3485,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -3496,7 +3502,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -3510,7 +3516,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>4</v>
       </c>
@@ -3527,7 +3533,7 @@
       </c>
       <c r="G7" s="17"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -3541,7 +3547,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -3555,7 +3561,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -3569,7 +3575,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -3586,7 +3592,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -3600,7 +3606,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -3617,7 +3623,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -3631,7 +3637,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -3648,7 +3654,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
@@ -3665,7 +3671,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
@@ -3679,7 +3685,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
@@ -3693,7 +3699,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -3707,7 +3713,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -3721,7 +3727,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -3735,7 +3741,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -3749,7 +3755,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -3763,7 +3769,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
@@ -3780,7 +3786,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -3794,7 +3800,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
@@ -3811,7 +3817,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
@@ -3825,7 +3831,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
@@ -3839,7 +3845,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -3856,7 +3862,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -3870,7 +3876,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
@@ -3887,7 +3893,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
@@ -3901,7 +3907,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
@@ -3915,7 +3921,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
@@ -3929,7 +3935,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
@@ -3943,7 +3949,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
@@ -3960,7 +3966,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="17" t="s">
         <v>9</v>
       </c>
@@ -3979,7 +3985,7 @@
       </c>
       <c r="G37" s="17"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
@@ -3993,7 +3999,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>36</v>
       </c>
@@ -4010,7 +4016,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
@@ -4024,7 +4030,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="116" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
@@ -4041,7 +4047,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
@@ -4058,7 +4064,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
@@ -4072,7 +4078,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
@@ -4086,7 +4092,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="17" t="s">
         <v>36</v>
       </c>
@@ -4100,7 +4106,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>170</v>
       </c>
@@ -4114,7 +4120,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="17" t="s">
         <v>170</v>
       </c>
@@ -4133,7 +4139,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
         <v>472</v>
       </c>
@@ -4152,7 +4158,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>400</v>
       </c>
@@ -4169,7 +4175,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>400</v>
       </c>
@@ -4186,7 +4192,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>400</v>
       </c>
@@ -4203,7 +4209,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>400</v>
       </c>
@@ -4220,7 +4226,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>400</v>
       </c>
@@ -4237,7 +4243,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>400</v>
       </c>
@@ -4254,7 +4260,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>400</v>
       </c>
@@ -4271,7 +4277,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>400</v>
       </c>
@@ -4288,7 +4294,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>400</v>
       </c>
@@ -4305,7 +4311,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>400</v>
       </c>
@@ -4322,7 +4328,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>400</v>
       </c>
@@ -4339,7 +4345,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>400</v>
       </c>
@@ -4356,7 +4362,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>400</v>
       </c>
@@ -4370,7 +4376,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>400</v>
       </c>
@@ -4387,7 +4393,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:7" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>400</v>
       </c>
@@ -4408,7 +4414,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>38</v>
       </c>
@@ -4422,7 +4428,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>38</v>
       </c>
@@ -4436,7 +4442,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>38</v>
       </c>
@@ -4450,7 +4456,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>38</v>
       </c>
@@ -4464,7 +4470,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>38</v>
       </c>
@@ -4478,7 +4484,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="17" t="s">
         <v>38</v>
       </c>
@@ -4497,7 +4503,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>43</v>
       </c>
@@ -4511,7 +4517,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>43</v>
       </c>
@@ -4525,7 +4531,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>43</v>
       </c>
@@ -4542,7 +4548,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>43</v>
       </c>
@@ -4559,7 +4565,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
@@ -4573,7 +4579,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>43</v>
       </c>
@@ -4587,7 +4593,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>43</v>
       </c>
@@ -4604,7 +4610,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
@@ -4621,7 +4627,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>43</v>
       </c>
@@ -4638,7 +4644,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
@@ -4652,7 +4658,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
@@ -4669,7 +4675,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
@@ -4686,7 +4692,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
@@ -4700,7 +4706,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>43</v>
       </c>
@@ -4714,7 +4720,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>43</v>
       </c>
@@ -4734,7 +4740,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
@@ -4748,7 +4754,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>43</v>
       </c>
@@ -4762,7 +4768,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
@@ -4776,7 +4782,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
@@ -4793,7 +4799,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
@@ -4807,7 +4813,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
@@ -4824,7 +4830,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
@@ -4838,7 +4844,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
@@ -4855,7 +4861,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
@@ -4869,7 +4875,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>43</v>
       </c>
@@ -4883,7 +4889,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
@@ -4897,7 +4903,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
@@ -4914,7 +4920,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
@@ -4931,7 +4937,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
@@ -4948,7 +4954,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
@@ -4965,7 +4971,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>43</v>
       </c>
@@ -4982,7 +4988,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>43</v>
       </c>
@@ -4996,7 +5002,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>43</v>
       </c>
@@ -5010,7 +5016,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
@@ -5027,7 +5033,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
@@ -5044,7 +5050,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
@@ -5058,7 +5064,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B106" s="2" t="s">
         <v>753</v>
       </c>
@@ -5069,7 +5075,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
@@ -5083,7 +5089,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
@@ -5097,7 +5103,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
@@ -5111,7 +5117,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
@@ -5125,7 +5131,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>43</v>
       </c>
@@ -5139,7 +5145,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>43</v>
       </c>
@@ -5153,7 +5159,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>43</v>
       </c>
@@ -5167,7 +5173,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>43</v>
       </c>
@@ -5181,7 +5187,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
@@ -5195,7 +5201,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
@@ -5212,7 +5218,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
@@ -5229,7 +5235,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
@@ -5246,7 +5252,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
@@ -5263,7 +5269,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
@@ -5277,7 +5283,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
@@ -5291,7 +5297,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>43</v>
       </c>
@@ -5308,7 +5314,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>43</v>
       </c>
@@ -5325,7 +5331,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
@@ -5342,7 +5348,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B125" s="2" t="s">
         <v>653</v>
       </c>
@@ -5353,7 +5359,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
@@ -5370,7 +5376,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>43</v>
       </c>
@@ -5384,7 +5390,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>43</v>
       </c>
@@ -5398,7 +5404,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
@@ -5412,7 +5418,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>43</v>
       </c>
@@ -5426,7 +5432,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>43</v>
       </c>
@@ -5440,7 +5446,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
@@ -5457,7 +5463,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
@@ -5474,2242 +5480,2239 @@
         <v>97</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="F134" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="17" t="s">
+      <c r="F135" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B135" s="17" t="s">
+      <c r="B136" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="C135" s="17" t="s">
+      <c r="C136" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="D135" s="17" t="s">
+      <c r="D136" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="E135" s="17"/>
-      <c r="F135" s="21" t="s">
+      <c r="E136" s="17"/>
+      <c r="F136" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="G135" s="17" t="s">
+      <c r="G136" s="17" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A136" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="F136" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>618</v>
+        <v>691</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>618</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>405</v>
+        <v>265</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>181</v>
+        <v>405</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="17" t="s">
+    <row r="142" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B142" s="17" t="s">
+      <c r="B142" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="B143" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C142" s="17" t="s">
+      <c r="C143" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="D142" s="17"/>
-      <c r="E142" s="17"/>
-      <c r="F142" s="20" t="s">
+      <c r="D143" s="17"/>
+      <c r="E143" s="17"/>
+      <c r="F143" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G142" s="17"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A143" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G143" s="17"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>780</v>
+        <v>458</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+        <v>459</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>460</v>
+        <v>782</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+        <v>785</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>367</v>
+        <v>460</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>368</v>
+        <v>461</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>56</v>
+        <v>367</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>262</v>
+        <v>368</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>301</v>
+        <v>56</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>769</v>
+        <v>301</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>770</v>
+        <v>302</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>616</v>
+        <v>769</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>617</v>
+        <v>770</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>513</v>
+        <v>616</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>514</v>
+        <v>617</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>786</v>
+        <v>513</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>771</v>
+        <v>787</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>514</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>530</v>
+        <v>786</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+        <v>771</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>594</v>
+        <v>530</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="F156" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>57</v>
+        <v>594</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F157" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+        <v>595</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>299</v>
+        <v>57</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>377</v>
+        <v>299</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F159" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F160" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F161" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>58</v>
+        <v>379</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>382</v>
+      </c>
+      <c r="F162" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>363</v>
+        <v>58</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>327</v>
+        <v>61</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F163" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C165" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F164" s="3" t="s">
+      <c r="F165" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="165" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="17" t="s">
+    <row r="166" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B165" s="17" t="s">
+      <c r="B166" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="C165" s="17" t="s">
+      <c r="C166" s="17" t="s">
         <v>429</v>
       </c>
-      <c r="F165" s="22" t="s">
+      <c r="F166" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G165" s="17" t="s">
+      <c r="G166" s="17" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A166" s="2" t="s">
+    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="B167" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C167" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="D167" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="F166" s="3" t="s">
+      <c r="F167" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="167" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="17" t="s">
+    <row r="168" spans="1:7" s="17" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="B167" s="17" t="s">
+      <c r="B168" s="17" t="s">
         <v>745</v>
       </c>
-      <c r="C167" s="17" t="s">
+      <c r="C168" s="17" t="s">
         <v>746</v>
       </c>
-      <c r="D167" s="17" t="s">
+      <c r="D168" s="17" t="s">
         <v>747</v>
       </c>
-      <c r="F167" s="19" t="s">
+      <c r="F168" s="19" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A168" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F169" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+        <v>353</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F173" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>357</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>140</v>
       </c>
       <c r="G174" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G175" s="2" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="17" t="s">
+    <row r="176" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="B175" s="17" t="s">
+      <c r="B176" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="C175" s="17" t="s">
+      <c r="C176" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="D175" s="17"/>
-      <c r="E175" s="17"/>
-      <c r="F175" s="20" t="s">
+      <c r="D176" s="17"/>
+      <c r="E176" s="17"/>
+      <c r="F176" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G175" s="17"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A176" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G176" s="17"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="F177" s="16" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="F178" s="16" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>820</v>
+      </c>
+      <c r="F179" s="16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>795</v>
+        <v>829</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="F181" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>828</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>506</v>
+        <v>795</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>507</v>
+        <v>797</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F182" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>796</v>
+      </c>
+      <c r="F182" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>650</v>
+        <v>506</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>651</v>
+        <v>507</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F183" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>508</v>
+      </c>
+      <c r="F183" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>314</v>
+        <v>650</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+        <v>651</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>484</v>
+        <v>314</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>485</v>
+        <v>315</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>801</v>
+        <v>484</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="F186" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+        <v>485</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>64</v>
+        <v>801</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F187" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G187" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+        <v>802</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>803</v>
+        <v>64</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="F188" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="F188" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="F189" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+        <v>804</v>
+      </c>
+      <c r="F189" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="F190" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+        <v>810</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>830</v>
+        <v>805</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="F191" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>806</v>
+      </c>
+      <c r="F191" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>798</v>
+        <v>830</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="F192" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G192" s="2" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="193" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>549</v>
+        <v>798</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+        <v>799</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>750</v>
+        <v>549</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="F194" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+        <v>550</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>503</v>
+        <v>756</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F196" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G196" s="2" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>757</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>821</v>
+        <v>503</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F197" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+        <v>504</v>
+      </c>
+      <c r="F197" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>195</v>
+        <v>821</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>196</v>
+        <v>824</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>825</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>844</v>
+        <v>195</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="F199" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G199" s="2" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>65</v>
+        <v>844</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>67</v>
+        <v>845</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F200" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+        <v>846</v>
+      </c>
+      <c r="F200" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>188</v>
+        <v>65</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F201" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F201" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>554</v>
+        <v>188</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F202" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>815</v>
+        <v>554</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="F203" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+        <v>555</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>464</v>
+        <v>815</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>463</v>
+        <v>816</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>822</v>
+        <v>480</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F206" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>481</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B208" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C207" s="2" t="s">
+      <c r="C208" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F207" s="4" t="s">
+      <c r="F208" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="17" t="s">
+    <row r="209" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B208" s="17" t="s">
+      <c r="B209" s="17" t="s">
         <v>832</v>
       </c>
-      <c r="C208" s="17" t="s">
+      <c r="C209" s="17" t="s">
         <v>833</v>
       </c>
-      <c r="D208" s="17"/>
-      <c r="E208" s="17"/>
-      <c r="F208" s="19" t="s">
+      <c r="D209" s="17"/>
+      <c r="E209" s="17"/>
+      <c r="F209" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G208" s="17"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A209" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G209" s="17"/>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>546</v>
+        <v>788</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>548</v>
+        <v>789</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>697</v>
+        <v>546</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>698</v>
+        <v>547</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>696</v>
+        <v>548</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>415</v>
+        <v>697</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>416</v>
+        <v>698</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>696</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>600</v>
+        <v>419</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>517</v>
+        <v>409</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F219" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G219" s="2" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>411</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>467</v>
+        <v>517</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F220" s="3"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+        <v>518</v>
+      </c>
+      <c r="F220" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>515</v>
+        <v>467</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F221" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G221" s="2" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+        <v>468</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F221" s="3"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F222" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+        <v>516</v>
+      </c>
+      <c r="F222" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F223" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+        <v>491</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="F224" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>410</v>
+        <v>454</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>412</v>
+        <v>455</v>
       </c>
       <c r="F225" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>457</v>
+        <v>412</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>528</v>
+        <v>456</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>457</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>413</v>
+        <v>528</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F228" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G228" s="2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>529</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B229" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F229" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C229" s="2" t="s">
+      <c r="C230" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="F229" s="19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A230" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="B230" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="C230" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="D230" s="17"/>
-      <c r="E230" s="17"/>
       <c r="F230" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G230" s="17"/>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A231" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F231" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="231" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B231" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="C231" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="D231" s="17"/>
+      <c r="E231" s="17"/>
+      <c r="F231" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G231" s="17"/>
+    </row>
+    <row r="232" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>292</v>
+        <v>203</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F232" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>205</v>
+        <v>292</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F233" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F233" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F234" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G234" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+      <c r="F234" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F235" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+      <c r="F235" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="F236" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>210</v>
+        <v>92</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F237" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B238" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C238" s="2" t="s">
+      <c r="C239" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F238" s="12" t="s">
+      <c r="F239" s="12" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A239" s="17" t="s">
+    <row r="240" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B239" s="17" t="s">
+      <c r="B240" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C239" s="17" t="s">
+      <c r="C240" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D239" s="17"/>
-      <c r="E239" s="17"/>
-      <c r="F239" s="20" t="s">
+      <c r="D240" s="17"/>
+      <c r="E240" s="17"/>
+      <c r="F240" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G239" s="17"/>
-    </row>
-    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A240" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F240" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G240" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G240" s="17"/>
+    </row>
+    <row r="241" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>731</v>
+        <v>190</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>732</v>
+        <v>192</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>140</v>
       </c>
       <c r="G242" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="F243" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G243" s="2" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A243" s="17" t="s">
+    <row r="244" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B243" s="17" t="s">
+      <c r="B244" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="C243" s="17" t="s">
+      <c r="C244" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="D243" s="17"/>
-      <c r="E243" s="17"/>
-      <c r="F243" s="22" t="s">
+      <c r="D244" s="17"/>
+      <c r="E244" s="17"/>
+      <c r="F244" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G243" s="17" t="s">
+      <c r="G244" s="17" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A244" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="F244" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>537</v>
+        <v>619</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F245" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+        <v>620</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>72</v>
+        <v>537</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F246" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+        <v>538</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F247" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>541</v>
+        <v>73</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>542</v>
+        <v>81</v>
       </c>
       <c r="F248" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>398</v>
+        <v>541</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F249" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+        <v>542</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>663</v>
+        <v>398</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>664</v>
+        <v>399</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>539</v>
+        <v>663</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F251" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+        <v>664</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>271</v>
+        <v>539</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F252" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+        <v>540</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F254" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>790</v>
+        <v>230</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="F255" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>605</v>
+        <v>790</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F256" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+        <v>791</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>226</v>
+        <v>607</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>227</v>
+        <v>608</v>
       </c>
       <c r="F258" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>621</v>
+        <v>222</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>623</v>
+        <v>223</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>610</v>
+        <v>622</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>623</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>848</v>
+        <v>609</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F262" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+        <v>610</v>
+      </c>
+      <c r="F262" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>694</v>
+        <v>848</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>695</v>
+        <v>849</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>624</v>
+        <v>694</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>625</v>
+        <v>695</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F266" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+        <v>597</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>235</v>
+        <v>576</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>236</v>
+        <v>577</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F268" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="G268" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>74</v>
+        <v>273</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F269" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+      <c r="F269" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="G269" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F270" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F271" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F272" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>611</v>
+        <v>77</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D273" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F273" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>435</v>
+        <v>611</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F274" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+        <v>612</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F274" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="F275" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>626</v>
+        <v>465</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F276" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>725</v>
+        <v>626</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="F277" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+        <v>627</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>78</v>
+        <v>725</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>86</v>
+        <v>726</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F279" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>281</v>
+        <v>535</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F280" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G280" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>536</v>
+      </c>
+      <c r="F280" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F281" s="16" t="s">
         <v>291</v>
@@ -7718,15 +7721,15 @@
         <v>323</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="F282" s="16" t="s">
         <v>291</v>
@@ -7735,435 +7738,452 @@
         <v>323</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E283" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F283" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+      <c r="F283" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>677</v>
+        <v>224</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F284" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>79</v>
+        <v>677</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+        <v>678</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>729</v>
+        <v>79</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>730</v>
+        <v>87</v>
       </c>
       <c r="F286" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>430</v>
+        <v>729</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F287" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G287" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+        <v>730</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>628</v>
+        <v>430</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="F288" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+        <v>431</v>
+      </c>
+      <c r="F288" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G288" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>494</v>
+        <v>628</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>495</v>
+        <v>629</v>
       </c>
       <c r="F289" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>762</v>
+        <v>494</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="F290" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G290" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>239</v>
+        <v>762</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F291" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+        <v>763</v>
+      </c>
+      <c r="F291" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G291" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F292" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="F292" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>630</v>
+        <v>286</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F293" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+      <c r="F293" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>228</v>
+        <v>630</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F294" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+        <v>631</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>614</v>
+        <v>228</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>615</v>
+        <v>229</v>
       </c>
       <c r="F295" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>220</v>
+        <v>614</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F296" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+        <v>615</v>
+      </c>
+      <c r="F296" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>511</v>
+        <v>220</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F297" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+      <c r="F297" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F298" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+        <v>512</v>
+      </c>
+      <c r="F298" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>218</v>
+        <v>509</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>219</v>
+        <v>510</v>
+      </c>
+      <c r="E299" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="F299" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>632</v>
+        <v>218</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F300" s="20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+      <c r="F300" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>571</v>
+        <v>632</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="F301" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G301" s="2" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>633</v>
+      </c>
+      <c r="F301" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B302" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G302" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B303" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="C302" s="2" t="s">
+      <c r="C303" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="F302" s="16" t="s">
+      <c r="F303" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="G302" s="2" t="s">
+      <c r="G303" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A303" s="17" t="s">
+    <row r="304" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A304" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B303" s="17" t="s">
+      <c r="B304" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="C303" s="17" t="s">
+      <c r="C304" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="D303" s="17"/>
-      <c r="E303" s="17"/>
-      <c r="F303" s="20" t="s">
+      <c r="D304" s="17"/>
+      <c r="E304" s="17"/>
+      <c r="F304" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G303" s="17"/>
-    </row>
-    <row r="304" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A304" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D304" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F304" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G304" s="17"/>
+    </row>
+    <row r="305" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>390</v>
+        <v>303</v>
       </c>
       <c r="F305" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>243</v>
+        <v>390</v>
       </c>
       <c r="F306" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>792</v>
+        <v>241</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F307" s="25" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F307" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>338</v>
+        <v>792</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F308" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+        <v>793</v>
+      </c>
+      <c r="F308" s="25" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>551</v>
+        <v>338</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="D309" s="2" t="s">
-        <v>553</v>
+        <v>339</v>
       </c>
       <c r="F309" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A310" s="17" t="s">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A310" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B310" s="17" t="s">
+      <c r="B310" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A311" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B311" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C310" s="17" t="s">
+      <c r="C311" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="D310" s="17" t="s">
+      <c r="D311" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="E310" s="17"/>
-      <c r="F310" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G310" s="17"/>
+      <c r="E311" s="17"/>
+      <c r="F311" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G311" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8174,13 +8194,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="52.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8188,7 +8208,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -8196,7 +8216,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -8204,7 +8224,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -8212,7 +8232,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -8220,7 +8240,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>400</v>
       </c>
@@ -8228,7 +8248,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>472</v>
       </c>
@@ -8236,7 +8256,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -8244,7 +8264,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -8252,7 +8272,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>269</v>
       </c>
@@ -8260,7 +8280,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -8268,7 +8288,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>391</v>
       </c>
@@ -8276,7 +8296,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>344</v>
       </c>
@@ -8284,7 +8304,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -8292,7 +8312,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>407</v>
       </c>
@@ -8300,7 +8320,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>91</v>
       </c>
@@ -8308,7 +8328,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -8316,7 +8336,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -8324,7 +8344,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>88</v>
       </c>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4A654E-745D-4DDC-969B-165E241E15DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA14AFB-0DA1-476E-B275-10CEAF1CFFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29595" yWindow="3060" windowWidth="26655" windowHeight="13965" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="850">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -1490,12 +1490,6 @@
   </si>
   <si>
     <t>Elasticities of Demand for Industrial Products</t>
-  </si>
-  <si>
-    <t>SoHPCCbRIC</t>
-  </si>
-  <si>
-    <t>Share of Hydrogen Production Capital Costs by Recipient ISIC Code</t>
   </si>
   <si>
     <t>HSR</t>
@@ -3069,82 +3063,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>97</v>
       </c>
@@ -3152,32 +3146,32 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>244</v>
       </c>
@@ -3185,17 +3179,17 @@
         <v>247</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>99</v>
       </c>
@@ -3203,42 +3197,42 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>98</v>
       </c>
@@ -3246,84 +3240,84 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="15" t="s">
         <v>252</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="11" t="s">
         <v>140</v>
       </c>
@@ -3331,62 +3325,62 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3399,20 +3393,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G311"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G310"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.1796875" style="2" customWidth="1"/>
     <col min="4" max="4" width="67" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="2" customWidth="1"/>
     <col min="7" max="7" width="54" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="2"/>
+    <col min="8" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -3435,15 +3429,15 @@
         <v>306</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -3451,27 +3445,27 @@
         <v>97</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -3485,24 +3479,24 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>140</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -3516,7 +3510,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="17" t="s">
         <v>4</v>
       </c>
@@ -3533,7 +3527,7 @@
       </c>
       <c r="G7" s="17"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -3547,7 +3541,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -3561,21 +3555,21 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -3592,21 +3586,21 @@
         <v>304</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -3623,7 +3617,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -3637,24 +3631,24 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
@@ -3671,7 +3665,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
@@ -3685,7 +3679,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
@@ -3699,7 +3693,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -3713,7 +3707,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -3727,7 +3721,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -3741,7 +3735,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -3755,21 +3749,21 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
@@ -3786,7 +3780,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -3800,7 +3794,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
@@ -3817,7 +3811,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
@@ -3831,7 +3825,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
@@ -3845,7 +3839,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -3862,21 +3856,21 @@
         <v>343</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
@@ -3893,7 +3887,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
@@ -3907,21 +3901,21 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
@@ -3935,7 +3929,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
@@ -3949,7 +3943,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
@@ -3966,7 +3960,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="17" t="s">
         <v>9</v>
       </c>
@@ -3985,52 +3979,52 @@
       </c>
       <c r="G37" s="17"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>682</v>
-      </c>
       <c r="F39" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
@@ -4041,13 +4035,13 @@
         <v>404</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
@@ -4058,55 +4052,55 @@
         <v>397</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F45" s="20" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>170</v>
       </c>
@@ -4120,7 +4114,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="17" t="s">
         <v>170</v>
       </c>
@@ -4139,7 +4133,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="17" t="s">
         <v>472</v>
       </c>
@@ -4155,10 +4149,10 @@
         <v>140</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>400</v>
       </c>
@@ -4175,24 +4169,24 @@
         <v>318</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>400</v>
       </c>
@@ -4209,7 +4203,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>400</v>
       </c>
@@ -4226,7 +4220,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>400</v>
       </c>
@@ -4243,41 +4237,41 @@
         <v>321</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>400</v>
       </c>
@@ -4291,44 +4285,44 @@
         <v>178</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>400</v>
       </c>
@@ -4345,24 +4339,24 @@
         <v>320</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>400</v>
       </c>
@@ -4376,24 +4370,24 @@
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="F62" s="22" t="s">
         <v>178</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="17" t="s">
         <v>400</v>
       </c>
@@ -4404,7 +4398,7 @@
         <v>452</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E63" s="17"/>
       <c r="F63" s="22" t="s">
@@ -4414,7 +4408,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>38</v>
       </c>
@@ -4428,7 +4422,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>38</v>
       </c>
@@ -4442,21 +4436,21 @@
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>38</v>
       </c>
@@ -4470,21 +4464,21 @@
         <v>98</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="17" t="s">
         <v>38</v>
       </c>
@@ -4503,52 +4497,52 @@
         <v>374</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>774</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>773</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>43</v>
       </c>
@@ -4556,16 +4550,16 @@
         <v>179</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
@@ -4579,38 +4573,38 @@
         <v>97</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
@@ -4627,24 +4621,24 @@
         <v>308</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
@@ -4658,7 +4652,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
@@ -4675,63 +4669,63 @@
         <v>310</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="F81" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>199</v>
@@ -4740,21 +4734,21 @@
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>43</v>
       </c>
@@ -4768,21 +4762,21 @@
         <v>97</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
@@ -4793,89 +4787,89 @@
         <v>52</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>100</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>43</v>
       </c>
@@ -4889,21 +4883,21 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
@@ -4914,13 +4908,13 @@
         <v>169</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
@@ -4937,24 +4931,24 @@
         <v>98</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
@@ -4971,52 +4965,52 @@
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
@@ -5027,13 +5021,13 @@
         <v>477</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
@@ -5050,130 +5044,130 @@
         <v>309</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>754</v>
-      </c>
       <c r="F105" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B106" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>755</v>
-      </c>
       <c r="F106" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>43</v>
       </c>
@@ -5187,7 +5181,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
@@ -5201,7 +5195,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
@@ -5218,58 +5212,58 @@
         <v>311</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>100</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="F119" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
@@ -5283,21 +5277,21 @@
         <v>98</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>43</v>
       </c>
@@ -5314,52 +5308,52 @@
         <v>326</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>669</v>
-      </c>
       <c r="F123" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B125" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F125" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
@@ -5376,139 +5370,139 @@
         <v>98</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F127" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D133" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>724</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="17" t="s">
         <v>43</v>
       </c>
@@ -5529,7 +5523,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>269</v>
       </c>
@@ -5540,13 +5534,13 @@
         <v>264</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>269</v>
       </c>
@@ -5557,13 +5551,13 @@
         <v>268</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>269</v>
       </c>
@@ -5577,7 +5571,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>269</v>
       </c>
@@ -5591,7 +5585,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>269</v>
       </c>
@@ -5605,7 +5599,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>269</v>
       </c>
@@ -5619,7 +5613,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="17" t="s">
         <v>269</v>
       </c>
@@ -5636,7 +5630,7 @@
       </c>
       <c r="G143" s="17"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>55</v>
       </c>
@@ -5650,49 +5644,49 @@
         <v>97</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>55</v>
       </c>
@@ -5709,7 +5703,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>55</v>
       </c>
@@ -5723,7 +5717,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
@@ -5740,7 +5734,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
@@ -5754,94 +5748,94 @@
         <v>99</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
@@ -5858,7 +5852,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
@@ -5872,7 +5866,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
@@ -5889,7 +5883,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
@@ -5906,7 +5900,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
@@ -5923,7 +5917,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
@@ -5940,7 +5934,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
@@ -5957,7 +5951,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>55</v>
       </c>
@@ -5971,7 +5965,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="166" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="17" t="s">
         <v>55</v>
       </c>
@@ -5988,7 +5982,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>391</v>
       </c>
@@ -6005,24 +5999,24 @@
         <v>97</v>
       </c>
     </row>
-    <row r="168" spans="1:7" s="17" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="17" t="s">
+        <v>742</v>
+      </c>
+      <c r="B168" s="17" t="s">
+        <v>743</v>
+      </c>
+      <c r="C168" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="B168" s="17" t="s">
+      <c r="D168" s="17" t="s">
         <v>745</v>
-      </c>
-      <c r="C168" s="17" t="s">
-        <v>746</v>
-      </c>
-      <c r="D168" s="17" t="s">
-        <v>747</v>
       </c>
       <c r="F168" s="19" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>344</v>
       </c>
@@ -6036,7 +6030,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>344</v>
       </c>
@@ -6050,7 +6044,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>344</v>
       </c>
@@ -6064,7 +6058,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>344</v>
       </c>
@@ -6081,7 +6075,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>344</v>
       </c>
@@ -6095,7 +6089,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>344</v>
       </c>
@@ -6112,58 +6106,55 @@
         <v>361</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A175" s="2" t="s">
+    <row r="175" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="B175" s="2" t="s">
+      <c r="B175" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="C175" s="2" t="s">
+      <c r="C175" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="F175" s="6" t="s">
+      <c r="F175" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G175" s="2" t="s">
+      <c r="G175" s="17" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="17" t="s">
-        <v>344</v>
-      </c>
-      <c r="B176" s="17" t="s">
-        <v>486</v>
-      </c>
-      <c r="C176" s="17" t="s">
-        <v>487</v>
-      </c>
-      <c r="D176" s="17"/>
-      <c r="E176" s="17"/>
-      <c r="F176" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G176" s="17"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A176" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+      <c r="F177" s="16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>63</v>
       </c>
@@ -6177,1189 +6168,1189 @@
         <v>291</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="F179" s="16" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>826</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>827</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>829</v>
+        <v>793</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+        <v>795</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>795</v>
+        <v>504</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>797</v>
+        <v>505</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="F182" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="F182" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>506</v>
+        <v>648</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>507</v>
+        <v>649</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F183" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>650</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>650</v>
+        <v>314</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F184" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>314</v>
+        <v>484</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>315</v>
+        <v>485</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>484</v>
+        <v>799</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>800</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>801</v>
+        <v>64</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="F187" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="F187" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>64</v>
+        <v>801</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F188" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G188" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>802</v>
+      </c>
+      <c r="F188" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="F189" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>808</v>
+      </c>
+      <c r="F189" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="F190" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+        <v>804</v>
+      </c>
+      <c r="F190" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>805</v>
+        <v>828</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="F191" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+        <v>829</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>830</v>
+        <v>796</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>831</v>
+        <v>797</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>809</v>
       </c>
       <c r="F192" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="G192" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>798</v>
+        <v>547</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="F193" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>549</v>
+        <v>748</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F194" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>756</v>
+        <v>501</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>502</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>503</v>
+        <v>819</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F197" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G197" s="2" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>821</v>
+        <v>195</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>825</v>
+        <v>196</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>195</v>
+        <v>842</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F199" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>843</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F199" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>844</v>
+        <v>65</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>845</v>
+        <v>67</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="F200" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G200" s="2" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="F200" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F201" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>188</v>
+        <v>552</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F202" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>554</v>
+        <v>813</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F203" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>814</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>815</v>
+        <v>464</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>816</v>
+        <v>463</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>480</v>
+        <v>820</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="F206" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>821</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>822</v>
+        <v>482</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F207" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A208" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A208" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B208" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F208" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B209" s="17" t="s">
-        <v>832</v>
-      </c>
-      <c r="C209" s="17" t="s">
-        <v>833</v>
-      </c>
-      <c r="D209" s="17"/>
-      <c r="E209" s="17"/>
-      <c r="F209" s="19" t="s">
+      <c r="B208" s="17" t="s">
+        <v>830</v>
+      </c>
+      <c r="C208" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="D208" s="17"/>
+      <c r="E208" s="17"/>
+      <c r="F208" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G209" s="17"/>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G208" s="17"/>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A209" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>788</v>
+        <v>544</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>789</v>
+        <v>545</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>546</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>546</v>
+        <v>695</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>547</v>
+        <v>696</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>548</v>
+        <v>694</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>697</v>
+        <v>415</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>696</v>
+        <v>416</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>418</v>
+        <v>389</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>419</v>
+        <v>598</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>420</v>
+        <v>600</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>600</v>
+        <v>421</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D217" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>409</v>
+        <v>515</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+      <c r="F219" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>517</v>
+        <v>467</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F220" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>468</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F220" s="3"/>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>467</v>
+        <v>513</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F221" s="3"/>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>515</v>
+        <v>488</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F222" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G222" s="2" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F223" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>488</v>
+        <v>454</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>489</v>
+        <v>455</v>
       </c>
       <c r="F224" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>454</v>
+        <v>410</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>455</v>
+        <v>412</v>
       </c>
       <c r="F225" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>410</v>
+        <v>456</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>456</v>
+        <v>526</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="F227" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>528</v>
+        <v>413</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F228" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+      <c r="F228" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>413</v>
+        <v>554</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F229" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G229" s="2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F229" s="19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A230" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>557</v>
-      </c>
+      <c r="B230" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="C230" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="D230" s="17"/>
+      <c r="E230" s="17"/>
       <c r="F230" s="19" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="B231" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="C231" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="D231" s="17"/>
-      <c r="E231" s="17"/>
-      <c r="F231" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="G231" s="17"/>
-    </row>
-    <row r="232" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G230" s="17"/>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A231" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>203</v>
+        <v>292</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F232" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F232" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F233" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F234" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="F234" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F235" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G235" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>214</v>
+        <v>95</v>
       </c>
       <c r="F236" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>92</v>
+        <v>210</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F238" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A239" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F238" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A239" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B239" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F239" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B240" s="17" t="s">
+      <c r="B239" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C240" s="17" t="s">
+      <c r="C239" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D240" s="17"/>
-      <c r="E240" s="17"/>
-      <c r="F240" s="20" t="s">
+      <c r="D239" s="17"/>
+      <c r="E239" s="17"/>
+      <c r="F239" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G240" s="17"/>
-    </row>
-    <row r="241" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G239" s="17"/>
+    </row>
+    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A240" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F240" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>190</v>
+        <v>729</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>192</v>
+        <v>730</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>140</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A243" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A243" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B243" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="F243" s="6" t="s">
+      <c r="B243" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="C243" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="D243" s="17"/>
+      <c r="E243" s="17"/>
+      <c r="F243" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G243" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B244" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="C244" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D244" s="17"/>
-      <c r="E244" s="17"/>
-      <c r="F244" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G244" s="17" t="s">
+      <c r="G243" s="17" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A244" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>619</v>
+        <v>535</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="F245" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>537</v>
+        <v>72</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F246" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F247" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>73</v>
+        <v>539</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>81</v>
+        <v>540</v>
       </c>
       <c r="F248" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>541</v>
+        <v>398</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F249" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>398</v>
+        <v>661</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>399</v>
+        <v>662</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>663</v>
+        <v>537</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="F251" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>539</v>
+        <v>271</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F252" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F254" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>230</v>
+        <v>788</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F255" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+        <v>789</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>790</v>
+        <v>603</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="F256" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+      <c r="F256" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>71</v>
       </c>
@@ -7373,346 +7364,349 @@
         <v>99</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>607</v>
+        <v>226</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>608</v>
+        <v>227</v>
       </c>
       <c r="F258" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>222</v>
+        <v>619</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>223</v>
+        <v>620</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>621</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="D261" s="2" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>609</v>
+        <v>846</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="F262" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+        <v>847</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>848</v>
+        <v>692</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>849</v>
+        <v>693</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>694</v>
+        <v>622</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>695</v>
+        <v>623</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>624</v>
+        <v>594</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>625</v>
+        <v>595</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="F266" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+        <v>575</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>576</v>
+        <v>235</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>577</v>
+        <v>236</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F268" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="F268" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>273</v>
+        <v>74</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F269" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="G269" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F270" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F271" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F272" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>77</v>
+        <v>609</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F273" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>610</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F273" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>611</v>
+        <v>435</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F274" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+        <v>436</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="F275" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>465</v>
+        <v>624</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F276" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>625</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>626</v>
+        <v>723</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F277" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>725</v>
+        <v>78</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>726</v>
+        <v>86</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F279" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+      <c r="F279" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>535</v>
+        <v>281</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F280" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+      <c r="F280" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F281" s="16" t="s">
         <v>291</v>
@@ -7721,15 +7715,15 @@
         <v>323</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>283</v>
+        <v>233</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>284</v>
+        <v>234</v>
       </c>
       <c r="F282" s="16" t="s">
         <v>291</v>
@@ -7738,452 +7732,435 @@
         <v>323</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F283" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G283" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>224</v>
+        <v>675</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E284" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F284" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>676</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>677</v>
+        <v>79</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F285" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>79</v>
+        <v>727</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>87</v>
+        <v>728</v>
       </c>
       <c r="F286" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>729</v>
+        <v>430</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F287" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+      <c r="F287" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>430</v>
+        <v>626</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F288" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G288" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+      <c r="F288" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>628</v>
+        <v>492</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>629</v>
+        <v>493</v>
       </c>
       <c r="F289" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>494</v>
+        <v>760</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="F290" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>761</v>
+      </c>
+      <c r="F290" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G290" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>762</v>
+        <v>239</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="F291" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G291" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="F291" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>239</v>
+        <v>286</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F292" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="F292" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>286</v>
+        <v>628</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F293" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+        <v>629</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>630</v>
+        <v>228</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F294" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="F294" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>228</v>
+        <v>612</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>229</v>
+        <v>613</v>
       </c>
       <c r="F295" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>614</v>
+        <v>220</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F296" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+      <c r="F296" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>220</v>
+        <v>509</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F297" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="F297" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F298" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F298" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>509</v>
+        <v>218</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E299" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F299" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>218</v>
+        <v>630</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F300" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>631</v>
+      </c>
+      <c r="F300" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>632</v>
+        <v>569</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F301" s="20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G301" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="F302" s="3" t="s">
-        <v>97</v>
+      <c r="F302" s="16" t="s">
+        <v>291</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A303" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A303" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B303" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F303" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G303" s="2" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A304" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B304" s="17" t="s">
+      <c r="B303" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="C304" s="17" t="s">
+      <c r="C303" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="D304" s="17"/>
-      <c r="E304" s="17"/>
-      <c r="F304" s="20" t="s">
+      <c r="D303" s="17"/>
+      <c r="E303" s="17"/>
+      <c r="F303" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G304" s="17"/>
-    </row>
-    <row r="305" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="G303" s="17"/>
+    </row>
+    <row r="304" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A304" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F304" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>89</v>
+        <v>216</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>90</v>
+        <v>215</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>303</v>
+        <v>390</v>
       </c>
       <c r="F305" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>390</v>
+        <v>243</v>
       </c>
       <c r="F306" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>241</v>
+        <v>790</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D307" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F307" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>791</v>
+      </c>
+      <c r="F307" s="25" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>792</v>
+        <v>338</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F308" s="25" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>338</v>
+        <v>549</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>339</v>
+        <v>550</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>551</v>
       </c>
       <c r="F309" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A310" s="2" t="s">
+    <row r="310" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A310" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B310" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="D310" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F310" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B311" s="17" t="s">
+      <c r="B310" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C311" s="17" t="s">
+      <c r="C310" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="D311" s="17" t="s">
+      <c r="D310" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="E311" s="17"/>
-      <c r="F311" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G311" s="17"/>
+      <c r="E310" s="17"/>
+      <c r="F310" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G310" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8194,13 +8171,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="52.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8208,7 +8185,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -8216,7 +8193,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -8224,7 +8201,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -8232,7 +8209,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -8240,7 +8217,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>400</v>
       </c>
@@ -8248,7 +8225,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>472</v>
       </c>
@@ -8256,7 +8233,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -8264,7 +8241,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -8272,7 +8249,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>269</v>
       </c>
@@ -8280,7 +8257,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -8288,7 +8265,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>391</v>
       </c>
@@ -8296,7 +8273,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>344</v>
       </c>
@@ -8304,7 +8281,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -8312,7 +8289,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>407</v>
       </c>
@@ -8320,7 +8297,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>91</v>
       </c>
@@ -8328,7 +8305,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -8336,7 +8313,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -8344,7 +8321,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>88</v>
       </c>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA14AFB-0DA1-476E-B275-10CEAF1CFFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606D8603-F01D-4DB3-99F3-85E8BA982B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29595" yWindow="3060" windowWidth="26655" windowHeight="13965" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="59235" yWindow="3345" windowWidth="21900" windowHeight="12420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="854">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2582,6 +2582,18 @@
   </si>
   <si>
     <t>Time Adjusted Capacity Factor Multiplier for Plants Built This Year</t>
+  </si>
+  <si>
+    <t>BSfGBP</t>
+  </si>
+  <si>
+    <t>BAU Subsidy for Grid Battery Production</t>
+  </si>
+  <si>
+    <t>FoGBPD</t>
+  </si>
+  <si>
+    <t>Fraction of Grid Batteries Produced Domestically</t>
   </si>
 </sst>
 </file>
@@ -3393,7 +3405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G310"/>
+  <dimension ref="A1:G312"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -4734,29 +4746,29 @@
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>671</v>
+        <v>850</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>672</v>
+        <v>851</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>158</v>
+        <v>671</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>159</v>
+        <v>672</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>97</v>
@@ -4767,120 +4779,120 @@
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>642</v>
+        <v>158</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>46</v>
+        <v>642</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>709</v>
+        <v>643</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>710</v>
+        <v>46</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>711</v>
+        <v>52</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>709</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>498</v>
+        <v>710</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+        <v>711</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>774</v>
+        <v>498</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>499</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>712</v>
+        <v>774</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>746</v>
+        <v>775</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>632</v>
+        <v>712</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>633</v>
+        <v>713</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>746</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>297</v>
+        <v>632</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>98</v>
+        <v>633</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -4888,64 +4900,61 @@
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>725</v>
+        <v>297</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>726</v>
+        <v>298</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>47</v>
+        <v>725</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+        <v>726</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>276</v>
+        <v>47</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>277</v>
+        <v>169</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>687</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>644</v>
+        <v>276</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>645</v>
+        <v>277</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>99</v>
+        <v>278</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4953,33 +4962,33 @@
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>167</v>
+        <v>644</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>168</v>
+        <v>645</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+        <v>714</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>655</v>
+        <v>167</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>656</v>
+        <v>168</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>98</v>
+        <v>434</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4987,13 +4996,16 @@
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>776</v>
+        <v>655</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>99</v>
+        <v>656</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -5001,10 +5013,10 @@
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>715</v>
+        <v>776</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>716</v>
+        <v>777</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>99</v>
@@ -5015,33 +5027,27 @@
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>476</v>
+        <v>852</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>688</v>
+        <v>853</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>175</v>
+        <v>715</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>309</v>
+        <v>716</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
@@ -5049,52 +5055,58 @@
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>750</v>
+        <v>476</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+        <v>477</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B106" s="2" t="s">
-        <v>751</v>
+        <v>175</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>697</v>
+        <v>750</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>98</v>
+        <v>752</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="B108" s="2" t="s">
-        <v>717</v>
+        <v>751</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>98</v>
+        <v>753</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5102,10 +5114,10 @@
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>577</v>
+        <v>697</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>578</v>
+        <v>698</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>98</v>
@@ -5116,27 +5128,27 @@
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>590</v>
+        <v>717</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+        <v>718</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>734</v>
+        <v>577</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>97</v>
+        <v>578</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
@@ -5144,13 +5156,13 @@
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>98</v>
+        <v>591</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
@@ -5158,13 +5170,13 @@
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>646</v>
+        <v>734</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>98</v>
+        <v>735</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
@@ -5172,13 +5184,13 @@
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>48</v>
+        <v>581</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>97</v>
+        <v>582</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
@@ -5186,95 +5198,92 @@
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>194</v>
+        <v>646</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>202</v>
+        <v>647</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>739</v>
+        <v>194</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>732</v>
+        <v>49</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>653</v>
+        <v>739</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="F119" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+        <v>740</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>184</v>
+        <v>732</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>98</v>
+        <v>733</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5282,30 +5291,30 @@
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>564</v>
+        <v>653</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>654</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="F121" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>326</v>
+        <v>185</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5313,86 +5322,89 @@
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>665</v>
+        <v>564</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+        <v>565</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>585</v>
+        <v>199</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>586</v>
+        <v>200</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>97</v>
+        <v>201</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A125" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B125" s="2" t="s">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F125" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>666</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>439</v>
+        <v>585</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>440</v>
+        <v>586</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>98</v>
+        <v>589</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A127" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="B127" s="2" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="F127" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>636</v>
+        <v>439</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>637</v>
+        <v>440</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>441</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>98</v>
@@ -5403,13 +5415,13 @@
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>98</v>
+        <v>664</v>
+      </c>
+      <c r="F129" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5417,75 +5429,72 @@
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>559</v>
+        <v>636</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>560</v>
+        <v>637</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+        <v>639</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>583</v>
+        <v>559</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>560</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>720</v>
+        <v>634</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>722</v>
+        <v>635</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>848</v>
+        <v>583</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>98</v>
+        <v>584</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5493,68 +5502,65 @@
         <v>43</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A137" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C137" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="F135" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="17" t="s">
+      <c r="F137" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B136" s="17" t="s">
+      <c r="B138" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="C136" s="17" t="s">
+      <c r="C138" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="D136" s="17" t="s">
+      <c r="D138" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="E136" s="17"/>
-      <c r="F136" s="21" t="s">
+      <c r="E138" s="17"/>
+      <c r="F138" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="G136" s="17" t="s">
+      <c r="G138" s="17" t="s">
         <v>337</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A137" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A138" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
@@ -5562,10 +5568,13 @@
         <v>269</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>689</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>98</v>
@@ -5576,13 +5585,16 @@
         <v>269</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>405</v>
+        <v>267</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>99</v>
+        <v>268</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
@@ -5590,97 +5602,97 @@
         <v>269</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>181</v>
+        <v>265</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>180</v>
+        <v>266</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>182</v>
+        <v>405</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F142" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A143" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F143" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="B143" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="C143" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="D143" s="17"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G143" s="17"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>55</v>
+        <v>269</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>458</v>
+        <v>182</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A145" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>99</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="B145" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C145" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D145" s="17"/>
+      <c r="E145" s="17"/>
+      <c r="F145" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G145" s="17"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>779</v>
+        <v>458</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+        <v>459</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>99</v>
@@ -5691,16 +5703,13 @@
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>460</v>
+        <v>779</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F148" s="3" t="s">
-        <v>97</v>
+        <v>782</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
@@ -5708,27 +5717,27 @@
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>367</v>
+        <v>780</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>783</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>56</v>
+        <v>460</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>59</v>
+        <v>461</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>262</v>
+        <v>462</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>97</v>
@@ -5739,13 +5748,13 @@
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>301</v>
+        <v>367</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>99</v>
+        <v>368</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5753,13 +5762,16 @@
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>767</v>
+        <v>56</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>99</v>
+        <v>59</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
@@ -5767,27 +5779,24 @@
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>614</v>
+        <v>301</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>615</v>
+        <v>302</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>511</v>
+        <v>767</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>512</v>
+        <v>768</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>99</v>
@@ -5798,10 +5807,10 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>784</v>
+        <v>614</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>769</v>
+        <v>615</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>99</v>
@@ -5812,13 +5821,16 @@
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>97</v>
+        <v>785</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -5826,30 +5838,27 @@
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>592</v>
+        <v>784</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F157" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>769</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>57</v>
+        <v>528</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>325</v>
+        <v>529</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
@@ -5857,13 +5866,13 @@
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>299</v>
+        <v>592</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>99</v>
+        <v>593</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5871,33 +5880,30 @@
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>377</v>
+        <v>57</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F160" s="16" t="s">
-        <v>291</v>
+        <v>60</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>378</v>
+        <v>299</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F161" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>384</v>
+        <v>300</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5905,143 +5911,149 @@
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F162" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>58</v>
+        <v>378</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>381</v>
+      </c>
+      <c r="F163" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>382</v>
+      </c>
+      <c r="F164" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>375</v>
+        <v>58</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>376</v>
+        <v>61</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="166" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="17" t="s">
+    <row r="166" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A166" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B166" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="C166" s="17" t="s">
-        <v>429</v>
-      </c>
-      <c r="F166" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G166" s="17" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B166" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
-        <v>391</v>
+        <v>55</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="168" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B168" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="C168" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="F168" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G168" s="17" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A169" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A170" s="17" t="s">
         <v>742</v>
       </c>
-      <c r="B168" s="17" t="s">
+      <c r="B170" s="17" t="s">
         <v>743</v>
       </c>
-      <c r="C168" s="17" t="s">
+      <c r="C170" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="D168" s="17" t="s">
+      <c r="D170" s="17" t="s">
         <v>745</v>
       </c>
-      <c r="F168" s="19" t="s">
+      <c r="F170" s="19" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A169" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A170" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F170" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
@@ -6049,109 +6061,106 @@
         <v>344</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F171" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>353</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A175" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B175" s="17" t="s">
-        <v>352</v>
-      </c>
-      <c r="C175" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="F175" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G175" s="17" t="s">
-        <v>362</v>
+      <c r="B175" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
-        <v>63</v>
+        <v>344</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>810</v>
+        <v>351</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A177" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="F177" s="16" t="s">
-        <v>291</v>
+        <v>358</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A177" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="B177" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="C177" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="F177" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G177" s="17" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
@@ -6159,13 +6168,16 @@
         <v>63</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="F178" s="16" t="s">
-        <v>291</v>
+        <v>811</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
@@ -6173,27 +6185,27 @@
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+      <c r="F179" s="16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>97</v>
+        <v>818</v>
+      </c>
+      <c r="F180" s="16" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
@@ -6201,16 +6213,13 @@
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>793</v>
+        <v>824</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="F181" s="12" t="s">
-        <v>244</v>
+        <v>825</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6218,33 +6227,30 @@
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>504</v>
+        <v>827</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="F182" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>826</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>648</v>
+        <v>793</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>649</v>
+        <v>795</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="F183" s="4" t="s">
-        <v>98</v>
+        <v>794</v>
+      </c>
+      <c r="F183" s="12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6252,27 +6258,33 @@
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>314</v>
+        <v>504</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+        <v>505</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="F184" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>484</v>
+        <v>648</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>99</v>
+        <v>649</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6280,13 +6292,13 @@
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>799</v>
+        <v>314</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="F186" s="4" t="s">
-        <v>98</v>
+        <v>315</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -6294,44 +6306,44 @@
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>64</v>
+        <v>484</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F187" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G187" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+        <v>485</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="F188" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>800</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>807</v>
+        <v>64</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="F189" s="5" t="s">
-        <v>99</v>
+        <v>66</v>
+      </c>
+      <c r="F189" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
@@ -6339,47 +6351,41 @@
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="F190" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="F191" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>808</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="F192" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G192" s="2" t="s">
-        <v>798</v>
+        <v>804</v>
+      </c>
+      <c r="F192" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
@@ -6387,27 +6393,33 @@
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>547</v>
+        <v>828</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+        <v>829</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>748</v>
+        <v>796</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>749</v>
+        <v>797</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>809</v>
       </c>
       <c r="F194" s="4" t="s">
         <v>98</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
@@ -6415,61 +6427,58 @@
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>754</v>
+        <v>547</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="F195" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>548</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>501</v>
+        <v>748</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F196" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G196" s="2" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>749</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>819</v>
+        <v>754</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>823</v>
+        <v>755</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>195</v>
+        <v>501</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F198" s="4" t="s">
-        <v>98</v>
+        <v>502</v>
+      </c>
+      <c r="F198" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6477,50 +6486,50 @@
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>843</v>
+        <v>822</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="F199" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G199" s="2" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>823</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F200" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>188</v>
+        <v>842</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F201" s="4" t="s">
-        <v>98</v>
+        <v>843</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F201" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>845</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6528,41 +6537,44 @@
         <v>63</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>552</v>
+        <v>65</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F202" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F202" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>813</v>
+        <v>188</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>814</v>
+        <v>189</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>464</v>
+        <v>552</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F204" s="4" t="s">
-        <v>98</v>
+        <v>553</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6570,27 +6582,27 @@
         <v>63</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>480</v>
+        <v>813</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>481</v>
+        <v>814</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>820</v>
+        <v>464</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F206" s="5" t="s">
-        <v>99</v>
+        <v>463</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6598,89 +6610,86 @@
         <v>63</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="17" t="s">
+    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A208" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B208" s="17" t="s">
+      <c r="B208" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A209" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A210" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B210" s="17" t="s">
         <v>830</v>
       </c>
-      <c r="C208" s="17" t="s">
+      <c r="C210" s="17" t="s">
         <v>831</v>
       </c>
-      <c r="D208" s="17"/>
-      <c r="E208" s="17"/>
-      <c r="F208" s="19" t="s">
+      <c r="D210" s="17"/>
+      <c r="E210" s="17"/>
+      <c r="F210" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G208" s="17"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A209" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A210" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="F210" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="G210" s="17"/>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>695</v>
+        <v>786</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>694</v>
+        <v>787</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>415</v>
+        <v>544</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>416</v>
+        <v>545</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>546</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>97</v>
@@ -6691,10 +6700,13 @@
         <v>407</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>417</v>
+        <v>695</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>418</v>
+        <v>696</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>694</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>97</v>
@@ -6705,10 +6717,10 @@
         <v>407</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>97</v>
@@ -6719,30 +6731,24 @@
         <v>407</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>598</v>
+        <v>388</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>97</v>
@@ -6753,107 +6759,110 @@
         <v>407</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>409</v>
+        <v>598</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>411</v>
+        <v>600</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>515</v>
+        <v>421</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F219" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G219" s="2" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>467</v>
+        <v>409</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F220" s="3"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+        <v>411</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F221" s="6" t="s">
-        <v>140</v>
+        <v>516</v>
+      </c>
+      <c r="F221" s="16" t="s">
+        <v>291</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F222" s="3" t="s">
-        <v>97</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F222" s="3"/>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F223" s="5" t="s">
-        <v>99</v>
+        <v>514</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
@@ -6861,13 +6870,16 @@
         <v>407</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="F224" s="5" t="s">
-        <v>99</v>
+        <v>489</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
@@ -6875,10 +6887,10 @@
         <v>407</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>410</v>
+        <v>486</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
       <c r="F225" s="5" t="s">
         <v>99</v>
@@ -6889,10 +6901,10 @@
         <v>407</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>99</v>
@@ -6903,151 +6915,151 @@
         <v>407</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>526</v>
+        <v>410</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>412</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>413</v>
+        <v>456</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F228" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G228" s="2" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>457</v>
+      </c>
+      <c r="F228" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B229" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A230" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F230" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A231" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="C229" s="2" t="s">
+      <c r="C231" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="F229" s="19" t="s">
+      <c r="F231" s="19" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A230" s="17" t="s">
+    <row r="232" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A232" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="B230" s="17" t="s">
+      <c r="B232" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="C230" s="17" t="s">
+      <c r="C232" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="D230" s="17"/>
-      <c r="E230" s="17"/>
-      <c r="F230" s="19" t="s">
+      <c r="D232" s="17"/>
+      <c r="E232" s="17"/>
+      <c r="F232" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G230" s="17"/>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A231" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F231" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A232" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F232" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G232" s="17"/>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F233" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F234" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G234" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F234" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F235" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F236" s="5" t="s">
-        <v>99</v>
+        <v>208</v>
+      </c>
+      <c r="F236" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -7055,142 +7067,142 @@
         <v>91</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F237" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>212</v>
+        <v>92</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F238" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A239" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A239" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B239" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C239" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D239" s="17"/>
-      <c r="E239" s="17"/>
-      <c r="F239" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G239" s="17"/>
+      <c r="B239" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>69</v>
+        <v>212</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F240" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G240" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A241" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F241" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G241" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+      <c r="F240" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A241" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B241" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C241" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D241" s="17"/>
+      <c r="E241" s="17"/>
+      <c r="F241" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G241" s="17"/>
+    </row>
+    <row r="242" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>729</v>
+        <v>69</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>730</v>
+        <v>70</v>
       </c>
       <c r="F242" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A243" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F243" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G242" s="2" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A243" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B243" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="C243" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D243" s="17"/>
-      <c r="E243" s="17"/>
-      <c r="F243" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G243" s="17" t="s">
-        <v>324</v>
+      <c r="G243" s="2" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>617</v>
+        <v>729</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="F244" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A245" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F245" s="5" t="s">
-        <v>99</v>
+        <v>730</v>
+      </c>
+      <c r="F244" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A245" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B245" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="C245" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="D245" s="17"/>
+      <c r="E245" s="17"/>
+      <c r="F245" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G245" s="17" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
@@ -7198,10 +7210,10 @@
         <v>71</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>72</v>
+        <v>617</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>80</v>
+        <v>618</v>
       </c>
       <c r="F246" s="4" t="s">
         <v>98</v>
@@ -7212,27 +7224,27 @@
         <v>71</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>73</v>
+        <v>535</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>81</v>
+        <v>536</v>
       </c>
       <c r="F247" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>539</v>
+        <v>72</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F248" s="5" t="s">
-        <v>99</v>
+        <v>80</v>
+      </c>
+      <c r="F248" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
@@ -7240,27 +7252,27 @@
         <v>71</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>398</v>
+        <v>73</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F249" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>661</v>
+        <v>539</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F250" s="4" t="s">
-        <v>98</v>
+        <v>540</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
@@ -7268,13 +7280,13 @@
         <v>71</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>537</v>
+        <v>398</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F251" s="5" t="s">
-        <v>99</v>
+        <v>399</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
@@ -7282,13 +7294,13 @@
         <v>71</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>271</v>
+        <v>661</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F252" s="3" t="s">
-        <v>97</v>
+        <v>662</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
@@ -7296,30 +7308,27 @@
         <v>71</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>250</v>
+        <v>537</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F253" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>538</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F254" s="5" t="s">
-        <v>99</v>
+        <v>272</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
@@ -7327,24 +7336,27 @@
         <v>71</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>788</v>
+        <v>250</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>789</v>
+        <v>251</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>603</v>
+        <v>230</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>604</v>
+        <v>231</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="F256" s="5" t="s">
         <v>99</v>
@@ -7355,13 +7367,13 @@
         <v>71</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>605</v>
+        <v>788</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F257" s="5" t="s">
-        <v>99</v>
+        <v>789</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
@@ -7369,10 +7381,10 @@
         <v>71</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>226</v>
+        <v>603</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>227</v>
+        <v>604</v>
       </c>
       <c r="F258" s="5" t="s">
         <v>99</v>
@@ -7383,10 +7395,10 @@
         <v>71</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>222</v>
+        <v>605</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>223</v>
+        <v>606</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>99</v>
@@ -7397,13 +7409,10 @@
         <v>71</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>619</v>
+        <v>226</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>621</v>
+        <v>227</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>99</v>
@@ -7414,10 +7423,10 @@
         <v>71</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>607</v>
+        <v>222</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>608</v>
+        <v>223</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>99</v>
@@ -7428,13 +7437,16 @@
         <v>71</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>846</v>
+        <v>619</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="F262" s="3" t="s">
-        <v>97</v>
+        <v>620</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="F262" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
@@ -7442,13 +7454,13 @@
         <v>71</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>692</v>
+        <v>607</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="F263" s="3" t="s">
-        <v>97</v>
+        <v>608</v>
+      </c>
+      <c r="F263" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
@@ -7456,10 +7468,10 @@
         <v>71</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>622</v>
+        <v>846</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>623</v>
+        <v>847</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>97</v>
@@ -7470,10 +7482,10 @@
         <v>71</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>594</v>
+        <v>692</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>595</v>
+        <v>693</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>97</v>
@@ -7484,13 +7496,13 @@
         <v>71</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>574</v>
+        <v>622</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F266" s="4" t="s">
-        <v>98</v>
+        <v>623</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
@@ -7498,30 +7510,27 @@
         <v>71</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>235</v>
+        <v>594</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F267" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>595</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>273</v>
+        <v>574</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F268" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="G268" s="2" t="s">
-        <v>322</v>
+        <v>575</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
@@ -7529,27 +7538,30 @@
         <v>71</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F269" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F270" s="5" t="s">
-        <v>99</v>
+        <v>274</v>
+      </c>
+      <c r="F270" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
@@ -7557,10 +7569,10 @@
         <v>71</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F271" s="5" t="s">
         <v>99</v>
@@ -7571,13 +7583,13 @@
         <v>71</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F272" s="4" t="s">
-        <v>98</v>
+        <v>83</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
@@ -7585,13 +7597,10 @@
         <v>71</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>609</v>
+        <v>76</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="D273" s="2" t="s">
-        <v>611</v>
+        <v>84</v>
       </c>
       <c r="F273" s="5" t="s">
         <v>99</v>
@@ -7602,10 +7611,10 @@
         <v>71</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>435</v>
+        <v>77</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>436</v>
+        <v>85</v>
       </c>
       <c r="F274" s="4" t="s">
         <v>98</v>
@@ -7616,27 +7625,30 @@
         <v>71</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>465</v>
+        <v>609</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F275" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>610</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>624</v>
+        <v>435</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F276" s="5" t="s">
-        <v>99</v>
+        <v>436</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.35">
@@ -7644,27 +7656,27 @@
         <v>71</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>723</v>
+        <v>465</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="F277" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>78</v>
+        <v>624</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F278" s="3" t="s">
-        <v>97</v>
+        <v>625</v>
+      </c>
+      <c r="F278" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
@@ -7672,47 +7684,41 @@
         <v>71</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>533</v>
+        <v>723</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F279" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>724</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>281</v>
+        <v>78</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F280" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G280" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>283</v>
+        <v>533</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F281" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G281" s="2" t="s">
-        <v>323</v>
+        <v>534</v>
+      </c>
+      <c r="F281" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7720,10 +7726,10 @@
         <v>71</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="F282" s="16" t="s">
         <v>291</v>
@@ -7732,80 +7738,83 @@
         <v>323</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E283" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F283" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+      <c r="F283" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>675</v>
+        <v>233</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="F284" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+      <c r="F284" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G284" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>79</v>
+        <v>224</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>87</v>
+        <v>225</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="F285" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>727</v>
+        <v>675</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="F286" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>676</v>
+      </c>
+      <c r="F286" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>430</v>
+        <v>79</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F287" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G287" s="2" t="s">
-        <v>364</v>
+        <v>87</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
@@ -7813,44 +7822,44 @@
         <v>71</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>626</v>
+        <v>727</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F288" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+        <v>728</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>492</v>
+        <v>430</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F289" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>431</v>
+      </c>
+      <c r="F289" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G289" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>760</v>
+        <v>626</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="F290" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G290" s="2" t="s">
-        <v>762</v>
+        <v>627</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -7858,27 +7867,30 @@
         <v>71</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>239</v>
+        <v>492</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F291" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+        <v>493</v>
+      </c>
+      <c r="F291" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>286</v>
+        <v>760</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F292" s="5" t="s">
-        <v>99</v>
+        <v>761</v>
+      </c>
+      <c r="F292" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G292" s="2" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.35">
@@ -7886,13 +7898,13 @@
         <v>71</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>628</v>
+        <v>239</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="F293" s="4" t="s">
-        <v>98</v>
+        <v>240</v>
+      </c>
+      <c r="F293" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.35">
@@ -7900,10 +7912,10 @@
         <v>71</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>228</v>
+        <v>286</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>229</v>
+        <v>285</v>
       </c>
       <c r="F294" s="5" t="s">
         <v>99</v>
@@ -7914,13 +7926,13 @@
         <v>71</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F295" s="5" t="s">
-        <v>99</v>
+        <v>629</v>
+      </c>
+      <c r="F295" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.35">
@@ -7928,13 +7940,13 @@
         <v>71</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F296" s="12" t="s">
-        <v>244</v>
+        <v>229</v>
+      </c>
+      <c r="F296" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.35">
@@ -7942,13 +7954,13 @@
         <v>71</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>509</v>
+        <v>612</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="F297" s="14" t="s">
-        <v>252</v>
+        <v>613</v>
+      </c>
+      <c r="F297" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.35">
@@ -7956,16 +7968,13 @@
         <v>71</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>507</v>
+        <v>220</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F298" s="5" t="s">
-        <v>99</v>
+        <v>221</v>
+      </c>
+      <c r="F298" s="12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.35">
@@ -7973,194 +7982,225 @@
         <v>71</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>218</v>
+        <v>509</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F299" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>510</v>
+      </c>
+      <c r="F299" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>630</v>
+        <v>507</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F300" s="20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>508</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F300" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>569</v>
+        <v>218</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="F301" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G301" s="2" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+      <c r="F301" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B302" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F302" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A303" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G303" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A304" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B304" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="C302" s="2" t="s">
+      <c r="C304" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="F302" s="16" t="s">
+      <c r="F304" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="G302" s="2" t="s">
+      <c r="G304" s="2" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A303" s="17" t="s">
+    <row r="305" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A305" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B303" s="17" t="s">
+      <c r="B305" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="C303" s="17" t="s">
+      <c r="C305" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="D303" s="17"/>
-      <c r="E303" s="17"/>
-      <c r="F303" s="20" t="s">
+      <c r="D305" s="17"/>
+      <c r="E305" s="17"/>
+      <c r="F305" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G303" s="17"/>
-    </row>
-    <row r="304" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A304" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D304" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F304" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A305" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D305" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F305" s="5" t="s">
-        <v>99</v>
-      </c>
+      <c r="G305" s="17"/>
     </row>
     <row r="306" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>241</v>
+        <v>89</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>242</v>
+        <v>90</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="F306" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>790</v>
+        <v>216</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="F307" s="25" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F307" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>338</v>
+        <v>241</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F308" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F308" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B309" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="F309" s="25" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A310" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A311" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B311" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="C309" s="2" t="s">
+      <c r="C311" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="D309" s="2" t="s">
+      <c r="D311" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="F309" s="4" t="s">
+      <c r="F311" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A310" s="17" t="s">
+    <row r="312" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A312" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B310" s="17" t="s">
+      <c r="B312" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C310" s="17" t="s">
+      <c r="C312" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="D310" s="17" t="s">
+      <c r="D312" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="E310" s="17"/>
-      <c r="F310" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G310" s="17"/>
+      <c r="E312" s="17"/>
+      <c r="F312" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G312" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606D8603-F01D-4DB3-99F3-85E8BA982B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E448F18-0DCE-4DF2-A042-1AAB7EF5E9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59235" yWindow="3345" windowWidth="21900" windowHeight="12420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1350" yWindow="3750" windowWidth="25275" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="863">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2594,6 +2594,33 @@
   </si>
   <si>
     <t>Fraction of Grid Batteries Produced Domestically</t>
+  </si>
+  <si>
+    <t>NBICS</t>
+  </si>
+  <si>
+    <t>Non BAU Industry CCS Subsidy</t>
+  </si>
+  <si>
+    <t>You plan on using the non-BAU CCS subsidy boolean lever</t>
+  </si>
+  <si>
+    <t>CECRCbI</t>
+  </si>
+  <si>
+    <t>Cost Effective CCS Retrofit Capacity by Industry</t>
+  </si>
+  <si>
+    <t>SoCECRCSiaY</t>
+  </si>
+  <si>
+    <t>Share of Cost Effective CCS Retrofit Construction Started in a Year</t>
+  </si>
+  <si>
+    <t>CRDT</t>
+  </si>
+  <si>
+    <t>CCS Retrofit Deployment Time</t>
   </si>
 </sst>
 </file>
@@ -3075,82 +3102,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>97</v>
       </c>
@@ -3158,32 +3185,32 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
         <v>244</v>
       </c>
@@ -3191,17 +3218,17 @@
         <v>247</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>99</v>
       </c>
@@ -3209,42 +3236,42 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>98</v>
       </c>
@@ -3252,84 +3279,84 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>252</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>140</v>
       </c>
@@ -3337,62 +3364,62 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3405,20 +3432,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G312"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G316"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="67" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.81640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.54296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="54" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.81640625" style="2"/>
+    <col min="8" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -3441,7 +3468,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -3460,7 +3487,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -3477,7 +3504,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -3491,7 +3518,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -3508,7 +3535,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -3522,7 +3549,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>4</v>
       </c>
@@ -3539,7 +3566,7 @@
       </c>
       <c r="G7" s="17"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -3553,7 +3580,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -3567,7 +3594,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -3581,7 +3608,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -3598,7 +3625,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -3612,7 +3639,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -3629,7 +3656,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -3643,7 +3670,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -3660,7 +3687,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
@@ -3677,7 +3704,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
@@ -3691,7 +3718,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
@@ -3705,7 +3732,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -3719,7 +3746,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -3733,7 +3760,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -3747,7 +3774,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -3761,7 +3788,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -3775,7 +3802,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
@@ -3792,7 +3819,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -3806,7 +3833,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
@@ -3823,7 +3850,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
@@ -3837,7 +3864,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
@@ -3851,7 +3878,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -3868,7 +3895,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -3882,7 +3909,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
@@ -3899,7 +3926,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
@@ -3913,7 +3940,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
@@ -3927,7 +3954,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
@@ -3941,7 +3968,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
@@ -3955,7 +3982,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
@@ -3972,7 +3999,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="17" t="s">
         <v>9</v>
       </c>
@@ -3991,7 +4018,7 @@
       </c>
       <c r="G37" s="17"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
@@ -4005,7 +4032,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>36</v>
       </c>
@@ -4022,7 +4049,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
@@ -4036,7 +4063,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="116" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
@@ -4053,7 +4080,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
@@ -4070,7 +4097,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
@@ -4084,4123 +4111,4182 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F48" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="17" t="s">
+    <row r="49" spans="1:7" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B49" s="17" t="s">
         <v>763</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C49" s="17" t="s">
         <v>684</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="F49" s="20" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F50" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="17" t="s">
+    <row r="51" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B51" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C51" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="22" t="s">
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G47" s="17" t="s">
+      <c r="G51" s="17" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="17" t="s">
+    <row r="52" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B52" s="17" t="s">
         <v>432</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C52" s="17" t="s">
         <v>433</v>
       </c>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="22" t="s">
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G48" s="17" t="s">
+      <c r="G52" s="17" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A49" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>702</v>
+        <v>541</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>703</v>
+        <v>542</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>494</v>
+        <v>423</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>495</v>
+        <v>424</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>261</v>
+        <v>330</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>556</v>
+        <v>245</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>557</v>
+        <v>246</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>764</v>
+        <v>702</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>765</v>
+        <v>703</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>176</v>
+        <v>494</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>177</v>
+        <v>495</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>561</v>
+        <v>260</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>563</v>
+        <v>261</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>402</v>
+        <v>556</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+        <v>557</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="F62" s="22" t="s">
+      <c r="F66" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="17" t="s">
+    <row r="67" spans="1:7" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="B63" s="17" t="s">
+      <c r="B67" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C67" s="17" t="s">
         <v>452</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D67" s="17" t="s">
         <v>705</v>
       </c>
-      <c r="E63" s="17"/>
-      <c r="F63" s="22" t="s">
+      <c r="E67" s="17"/>
+      <c r="F67" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="G67" s="17" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>530</v>
+        <v>39</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B69" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="C69" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="D69" s="17"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="G69" s="17" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B69" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>770</v>
+        <v>805</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+        <v>806</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>771</v>
+        <v>40</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>773</v>
+        <v>42</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>640</v>
+        <v>530</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A73" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="F73" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="D73" s="17"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="G73" s="17" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>316</v>
+        <v>770</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>772</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>588</v>
+        <v>771</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>773</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>668</v>
+        <v>640</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>669</v>
+        <v>641</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>838</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F77" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+        <v>706</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>579</v>
+        <v>316</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+        <v>317</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>44</v>
+        <v>588</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>587</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>45</v>
+        <v>668</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F80" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>669</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>736</v>
+        <v>173</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>737</v>
+        <v>172</v>
       </c>
       <c r="F81" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>758</v>
+        <v>579</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>580</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>673</v>
+        <v>44</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>674</v>
+        <v>50</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>658</v>
+        <v>45</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="F84" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>850</v>
+        <v>736</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>737</v>
+      </c>
+      <c r="F85" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>671</v>
+        <v>758</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>158</v>
+        <v>673</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>159</v>
+        <v>674</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>659</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>46</v>
+        <v>850</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>851</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>710</v>
+        <v>671</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>672</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>498</v>
+        <v>158</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>774</v>
+        <v>642</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>775</v>
+        <v>643</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>712</v>
+        <v>46</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>713</v>
+        <v>52</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>746</v>
+        <v>709</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>632</v>
+        <v>710</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>633</v>
+        <v>711</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>297</v>
+        <v>498</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+        <v>499</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>725</v>
+        <v>774</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>775</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>47</v>
+        <v>712</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>169</v>
+        <v>713</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+        <v>746</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>276</v>
+        <v>632</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>633</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>644</v>
+        <v>297</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>298</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>167</v>
+        <v>725</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+        <v>726</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>655</v>
+        <v>47</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>656</v>
+        <v>169</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+        <v>687</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>776</v>
+        <v>276</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>852</v>
+        <v>644</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+        <v>645</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>715</v>
+        <v>167</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>476</v>
+        <v>655</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>477</v>
+        <v>656</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>657</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>175</v>
+        <v>776</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+        <v>777</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>750</v>
+        <v>852</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+        <v>853</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B108" s="2" t="s">
-        <v>751</v>
+        <v>715</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>753</v>
+        <v>716</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>697</v>
+        <v>476</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+        <v>477</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>717</v>
+        <v>175</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>577</v>
+        <v>750</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>752</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B112" s="2" t="s">
-        <v>590</v>
+        <v>751</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+        <v>753</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>734</v>
+        <v>697</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+        <v>698</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>581</v>
+        <v>717</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>582</v>
+        <v>718</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>646</v>
+        <v>577</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>647</v>
+        <v>578</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>48</v>
+        <v>590</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>53</v>
+        <v>591</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>194</v>
+        <v>734</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>735</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>49</v>
+        <v>581</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>582</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>739</v>
+        <v>646</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G119" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>647</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>732</v>
+        <v>48</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>653</v>
+        <v>194</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="F121" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>564</v>
+        <v>739</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>740</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>199</v>
+        <v>732</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>200</v>
+        <v>733</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>201</v>
+        <v>747</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+        <v>719</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>585</v>
+        <v>184</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B127" s="2" t="s">
-        <v>651</v>
+        <v>564</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F127" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>565</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>439</v>
+        <v>199</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="F129" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>666</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>636</v>
+        <v>585</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A131" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B131" s="2" t="s">
-        <v>638</v>
+        <v>651</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>652</v>
+      </c>
+      <c r="F131" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>559</v>
+        <v>439</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>560</v>
+        <v>440</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>441</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>634</v>
+        <v>663</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F133" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+        <v>664</v>
+      </c>
+      <c r="F133" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>583</v>
+        <v>636</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>637</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>720</v>
+        <v>638</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="F135" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>639</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>848</v>
+        <v>559</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>849</v>
+        <v>560</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>690</v>
+        <v>634</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B138" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="C138" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="D138" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="E138" s="17"/>
-      <c r="F138" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="G138" s="17" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B138" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>269</v>
+        <v>43</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>263</v>
+        <v>720</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>264</v>
+        <v>721</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>722</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>269</v>
+        <v>43</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>267</v>
+        <v>848</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>616</v>
+        <v>849</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>269</v>
+        <v>43</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>265</v>
+        <v>690</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A142" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+        <v>691</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="C142" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="D142" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="E142" s="17"/>
+      <c r="F142" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="G142" s="17" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>180</v>
+        <v>264</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>689</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>182</v>
+        <v>267</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>183</v>
+        <v>268</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>616</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="17" t="s">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B145" s="17" t="s">
+      <c r="B145" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="B149" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C145" s="17" t="s">
+      <c r="C149" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="D145" s="17"/>
-      <c r="E145" s="17"/>
-      <c r="F145" s="20" t="s">
+      <c r="D149" s="17"/>
+      <c r="E149" s="17"/>
+      <c r="F149" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G145" s="17"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A146" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F146" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A147" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A148" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A149" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G149" s="17"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>367</v>
+        <v>778</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>781</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>56</v>
+        <v>779</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+        <v>782</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>301</v>
+        <v>780</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>302</v>
+        <v>783</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>767</v>
+        <v>460</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+        <v>461</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>614</v>
+        <v>367</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+        <v>368</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>511</v>
+        <v>56</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>784</v>
+        <v>301</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>769</v>
+        <v>302</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>528</v>
+        <v>767</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F158" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+        <v>768</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>592</v>
+        <v>614</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F159" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>615</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>57</v>
+        <v>511</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+        <v>785</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>299</v>
+        <v>784</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>300</v>
+        <v>769</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>377</v>
+        <v>528</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F162" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G162" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>529</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>378</v>
+        <v>592</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F163" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>593</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>379</v>
+        <v>57</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="F164" s="16" t="s">
-        <v>291</v>
+        <v>60</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>58</v>
+        <v>299</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F166" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>380</v>
+      </c>
+      <c r="F166" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="F167" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B168" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="C168" s="17" t="s">
-        <v>429</v>
-      </c>
-      <c r="F168" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G168" s="17" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B168" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F168" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>391</v>
+        <v>55</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>393</v>
+        <v>58</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>394</v>
+        <v>61</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>395</v>
+        <v>62</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="170" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="17" t="s">
+    <row r="170" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B172" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="C172" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="F172" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G172" s="17" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" s="17" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="17" t="s">
         <v>742</v>
       </c>
-      <c r="B170" s="17" t="s">
+      <c r="B174" s="17" t="s">
         <v>743</v>
       </c>
-      <c r="C170" s="17" t="s">
+      <c r="C174" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="D170" s="17" t="s">
+      <c r="D174" s="17" t="s">
         <v>745</v>
       </c>
-      <c r="F170" s="19" t="s">
+      <c r="F174" s="19" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A171" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A172" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F172" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A173" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F173" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A174" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F174" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F175" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+        <v>353</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B180" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C176" s="2" t="s">
+      <c r="C180" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="F176" s="6" t="s">
+      <c r="F180" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G176" s="2" t="s">
+      <c r="G180" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="177" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="17" t="s">
+    <row r="181" spans="1:7" s="17" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="B177" s="17" t="s">
+      <c r="B181" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="C177" s="17" t="s">
+      <c r="C181" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="F177" s="22" t="s">
+      <c r="F181" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G177" s="17" t="s">
+      <c r="G181" s="17" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A178" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A179" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="F179" s="16" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A180" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="F180" s="16" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A181" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>827</v>
+        <v>810</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="F182" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+        <v>811</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>793</v>
+        <v>815</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="F183" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+      <c r="F183" s="16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>504</v>
+        <v>817</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="F184" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>818</v>
+      </c>
+      <c r="F184" s="16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>648</v>
+        <v>824</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="F185" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>825</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>314</v>
+        <v>827</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+        <v>826</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>484</v>
+        <v>793</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>795</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="F187" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>799</v>
+        <v>504</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="F188" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+        <v>505</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="F188" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>64</v>
+        <v>648</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F189" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+        <v>649</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>801</v>
+        <v>314</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="F190" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>807</v>
+        <v>484</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>808</v>
+        <v>485</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="F192" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+        <v>800</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>828</v>
+        <v>64</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="F193" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="F193" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="F194" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G194" s="2" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+        <v>802</v>
+      </c>
+      <c r="F194" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>547</v>
+        <v>807</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>548</v>
+        <v>808</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>748</v>
+        <v>803</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+        <v>804</v>
+      </c>
+      <c r="F196" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>754</v>
+        <v>828</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>755</v>
+        <v>829</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>501</v>
+        <v>796</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F198" s="6" t="s">
-        <v>100</v>
+        <v>797</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>819</v>
+        <v>547</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F199" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+        <v>548</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>195</v>
+        <v>748</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>196</v>
+        <v>749</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>842</v>
+        <v>754</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="F201" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G201" s="2" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>755</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>65</v>
+        <v>501</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F202" s="14" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+      <c r="F202" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>188</v>
+        <v>819</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>189</v>
+        <v>822</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>823</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>552</v>
+        <v>195</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F204" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>813</v>
+        <v>842</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F205" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+        <v>843</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F205" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>464</v>
+        <v>65</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F206" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F206" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>480</v>
+        <v>188</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>481</v>
+        <v>189</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>820</v>
+        <v>552</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>821</v>
+        <v>553</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>482</v>
+        <v>813</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>483</v>
+        <v>814</v>
       </c>
       <c r="F209" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A210" s="17" t="s">
+    <row r="210" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B210" s="17" t="s">
+      <c r="B210" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B214" s="17" t="s">
         <v>830</v>
       </c>
-      <c r="C210" s="17" t="s">
+      <c r="C214" s="17" t="s">
         <v>831</v>
       </c>
-      <c r="D210" s="17"/>
-      <c r="E210" s="17"/>
-      <c r="F210" s="19" t="s">
+      <c r="D214" s="17"/>
+      <c r="E214" s="17"/>
+      <c r="F214" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G210" s="17"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A211" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A212" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="F212" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A213" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="F213" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A214" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G214" s="17"/>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>417</v>
+        <v>786</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>418</v>
+        <v>787</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>388</v>
+        <v>544</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>389</v>
+        <v>545</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>546</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>419</v>
+        <v>695</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>420</v>
+        <v>696</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>694</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>598</v>
+        <v>415</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>515</v>
+        <v>419</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F221" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G221" s="2" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>467</v>
+        <v>598</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>468</v>
+        <v>600</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F222" s="3"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+        <v>599</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>513</v>
+        <v>421</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F223" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G223" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>486</v>
+        <v>515</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F225" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+        <v>516</v>
+      </c>
+      <c r="F225" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="F226" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+        <v>468</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F226" s="3"/>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>410</v>
+        <v>513</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F227" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+      <c r="F227" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="F228" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+        <v>489</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>526</v>
+        <v>486</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F229" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>487</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F230" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G230" s="2" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>455</v>
+      </c>
+      <c r="F230" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B231" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F234" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B235" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="C231" s="2" t="s">
+      <c r="C235" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="F231" s="19" t="s">
+      <c r="F235" s="19" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A232" s="17" t="s">
+    <row r="236" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="B232" s="17" t="s">
+      <c r="B236" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="C232" s="17" t="s">
+      <c r="C236" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="D232" s="17"/>
-      <c r="E232" s="17"/>
-      <c r="F232" s="19" t="s">
+      <c r="D236" s="17"/>
+      <c r="E236" s="17"/>
+      <c r="F236" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G232" s="17"/>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A233" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F233" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A234" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F234" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A235" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F235" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A236" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F236" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G236" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G236" s="17"/>
+    </row>
+    <row r="237" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="F237" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>92</v>
+        <v>292</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F238" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F238" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F239" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B240" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F240" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B244" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C240" s="2" t="s">
+      <c r="C244" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F240" s="12" t="s">
+      <c r="F244" s="12" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A241" s="17" t="s">
+    <row r="245" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B241" s="17" t="s">
+      <c r="B245" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C241" s="17" t="s">
+      <c r="C245" s="17" t="s">
         <v>94</v>
-      </c>
-      <c r="D241" s="17"/>
-      <c r="E241" s="17"/>
-      <c r="F241" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G241" s="17"/>
-    </row>
-    <row r="242" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A242" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F242" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G242" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A243" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F243" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G243" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A244" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F244" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G244" s="2" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A245" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B245" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="C245" s="17" t="s">
-        <v>193</v>
       </c>
       <c r="D245" s="17"/>
       <c r="E245" s="17"/>
-      <c r="F245" s="22" t="s">
+      <c r="F245" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G245" s="17"/>
+    </row>
+    <row r="246" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F246" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F247" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G245" s="17" t="s">
+      <c r="G247" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="F248" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B249" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="C249" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="D249" s="17"/>
+      <c r="E249" s="17"/>
+      <c r="F249" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G249" s="17" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A246" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="F246" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A247" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F247" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A248" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F248" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A249" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F249" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>539</v>
+        <v>617</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F250" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+        <v>618</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>398</v>
+        <v>535</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F251" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+        <v>536</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>661</v>
+        <v>72</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>662</v>
+        <v>80</v>
       </c>
       <c r="F252" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>537</v>
+        <v>73</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>538</v>
+        <v>81</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>271</v>
+        <v>539</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F254" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+        <v>540</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>250</v>
+        <v>398</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F255" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>399</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>230</v>
+        <v>661</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F256" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+        <v>662</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>788</v>
+        <v>537</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F257" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+        <v>538</v>
+      </c>
+      <c r="F257" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>603</v>
+        <v>271</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F258" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>605</v>
+        <v>250</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F259" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>222</v>
+        <v>788</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F261" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+        <v>789</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="D262" s="2" t="s">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>846</v>
+        <v>226</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="F264" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>692</v>
+        <v>222</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="F265" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F266" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+        <v>620</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="F266" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>594</v>
+        <v>607</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="F267" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+        <v>608</v>
+      </c>
+      <c r="F267" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>574</v>
+        <v>846</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F268" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+        <v>847</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>235</v>
+        <v>692</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F269" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>693</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>273</v>
+        <v>622</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F270" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="G270" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+        <v>623</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>74</v>
+        <v>594</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+        <v>595</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>75</v>
+        <v>574</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F272" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+        <v>575</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F273" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F274" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+      <c r="F274" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="G274" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>609</v>
+        <v>74</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="F275" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>435</v>
+        <v>75</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F276" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>465</v>
+        <v>76</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F277" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>624</v>
+        <v>77</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F278" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>723</v>
+        <v>609</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="F279" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+        <v>610</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F279" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>78</v>
+        <v>435</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F280" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+        <v>436</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>533</v>
+        <v>465</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F281" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>281</v>
+        <v>624</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F282" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G282" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>625</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>283</v>
+        <v>723</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F283" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G283" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>724</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F284" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G284" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>224</v>
+        <v>533</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E285" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>534</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>675</v>
+        <v>281</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="F286" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+      <c r="F286" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G286" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F287" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+      <c r="F287" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>727</v>
+        <v>233</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="F288" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+      <c r="F288" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G288" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>430</v>
+        <v>224</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F289" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G289" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>626</v>
+        <v>675</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>627</v>
+        <v>676</v>
       </c>
       <c r="F290" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>492</v>
+        <v>79</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F291" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="F292" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G292" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
+        <v>728</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>239</v>
+        <v>430</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F293" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+        <v>431</v>
+      </c>
+      <c r="F293" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>286</v>
+        <v>626</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>285</v>
+        <v>627</v>
       </c>
       <c r="F294" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>628</v>
+        <v>492</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="F295" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+        <v>493</v>
+      </c>
+      <c r="F295" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>228</v>
+        <v>760</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F296" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+        <v>761</v>
+      </c>
+      <c r="F296" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G296" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>612</v>
+        <v>239</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F297" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="F297" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F298" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+      <c r="F298" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>509</v>
+        <v>628</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="F299" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+        <v>629</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>507</v>
+        <v>228</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="F300" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>218</v>
+        <v>612</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>219</v>
+        <v>613</v>
       </c>
       <c r="F301" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>630</v>
+        <v>220</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F302" s="20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+      <c r="F302" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>569</v>
+        <v>509</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="F303" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G303" s="2" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>510</v>
+      </c>
+      <c r="F303" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B304" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F304" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F305" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A306" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F306" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A307" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G307" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A308" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B308" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="C304" s="2" t="s">
+      <c r="C308" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="F304" s="16" t="s">
+      <c r="F308" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="G304" s="2" t="s">
+      <c r="G308" s="2" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A305" s="17" t="s">
+    <row r="309" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A309" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B305" s="17" t="s">
+      <c r="B309" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="C305" s="17" t="s">
+      <c r="C309" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="D305" s="17"/>
-      <c r="E305" s="17"/>
-      <c r="F305" s="20" t="s">
+      <c r="D309" s="17"/>
+      <c r="E309" s="17"/>
+      <c r="F309" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G305" s="17"/>
-    </row>
-    <row r="306" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A306" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D306" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F306" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A307" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D307" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F307" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A308" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D308" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F308" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A309" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="F309" s="25" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G309" s="17"/>
+    </row>
+    <row r="310" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>338</v>
+        <v>89</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F310" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F310" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B311" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F311" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A312" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F312" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A313" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="F313" s="25" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A314" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B315" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="C311" s="2" t="s">
+      <c r="C315" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="D311" s="2" t="s">
+      <c r="D315" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="F311" s="4" t="s">
+      <c r="F315" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A312" s="17" t="s">
+    <row r="316" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A316" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B312" s="17" t="s">
+      <c r="B316" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C312" s="17" t="s">
+      <c r="C316" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="D312" s="17" t="s">
+      <c r="D316" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="E312" s="17"/>
-      <c r="F312" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G312" s="17"/>
+      <c r="E316" s="17"/>
+      <c r="F316" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G316" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8211,13 +8297,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="52.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8225,7 +8311,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -8233,7 +8319,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -8241,7 +8327,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -8249,7 +8335,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -8257,7 +8343,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>400</v>
       </c>
@@ -8265,7 +8351,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>472</v>
       </c>
@@ -8273,7 +8359,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -8281,7 +8367,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -8289,7 +8375,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>269</v>
       </c>
@@ -8297,7 +8383,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -8305,7 +8391,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>391</v>
       </c>
@@ -8313,7 +8399,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>344</v>
       </c>
@@ -8321,7 +8407,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -8329,7 +8415,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>407</v>
       </c>
@@ -8337,7 +8423,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>91</v>
       </c>
@@ -8345,7 +8431,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -8353,7 +8439,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -8361,7 +8447,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>88</v>
       </c>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F111D967-3D7B-478C-9335-239EEBFA5AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8260A84B-734B-418D-B415-453762BCD744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59580" yWindow="1425" windowWidth="21600" windowHeight="15210" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="836">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2531,6 +2531,15 @@
   </si>
   <si>
     <t>BAU Subsidy for Grid Battery Production</t>
+  </si>
+  <si>
+    <t>BEEEfEPS</t>
+  </si>
+  <si>
+    <t>Boolean Exclude Electricity Exports from Elec Portfolio Stds</t>
+  </si>
+  <si>
+    <t>You wish to change the default behavior or whether electricity exports are included or excluded in RPS and CES policies.</t>
   </si>
 </sst>
 </file>
@@ -3342,7 +3351,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G302"/>
+  <dimension ref="A1:G303"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -4158,21 +4167,21 @@
         <v>438</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>342</v>
+        <v>833</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>343</v>
+        <v>834</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>344</v>
+        <v>835</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -4180,50 +4189,50 @@
         <v>413</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>251</v>
+        <v>342</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>252</v>
+        <v>343</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>720</v>
+        <v>251</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>721</v>
+        <v>252</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>509</v>
+        <v>720</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>510</v>
+        <v>721</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>511</v>
+        <v>722</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -4231,33 +4240,33 @@
         <v>413</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>266</v>
+        <v>509</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>267</v>
+        <v>510</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>571</v>
+        <v>266</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>572</v>
+        <v>267</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>573</v>
+        <v>512</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -4265,99 +4274,102 @@
         <v>413</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>782</v>
+        <v>571</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>783</v>
+        <v>572</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>178</v>
+        <v>782</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>179</v>
+        <v>783</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>576</v>
+        <v>178</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>578</v>
+        <v>179</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="17" t="s">
+      <c r="F62" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B63" s="17" t="s">
         <v>464</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C63" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D63" s="17" t="s">
         <v>723</v>
       </c>
-      <c r="E62" s="17"/>
-      <c r="F62" s="22" t="s">
+      <c r="E63" s="17"/>
+      <c r="F63" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="G62" s="17" t="s">
+      <c r="G63" s="17" t="s">
         <v>466</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -4365,10 +4377,10 @@
         <v>38</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>201</v>
+        <v>39</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>202</v>
+        <v>41</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>99</v>
@@ -4379,13 +4391,13 @@
         <v>38</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>100</v>
+        <v>202</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
@@ -4393,46 +4405,46 @@
         <v>38</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>545</v>
+        <v>40</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>546</v>
+        <v>42</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="17" t="s">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C68" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="21" t="s">
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="G67" s="17" t="s">
+      <c r="G68" s="17" t="s">
         <v>387</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
@@ -4440,30 +4452,27 @@
         <v>43</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>655</v>
+        <v>789</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>101</v>
+        <v>791</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4471,44 +4480,47 @@
         <v>43</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>181</v>
+        <v>655</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>724</v>
+        <v>656</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+        <v>657</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>328</v>
+        <v>181</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>724</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>603</v>
+        <v>328</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>101</v>
+        <v>329</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4516,16 +4528,13 @@
         <v>43</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>684</v>
+        <v>603</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>100</v>
+        <v>602</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4533,33 +4542,33 @@
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>175</v>
+        <v>684</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F75" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+        <v>685</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>594</v>
+        <v>175</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>250</v>
+        <v>174</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
@@ -4567,30 +4576,30 @@
         <v>43</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>44</v>
+        <v>594</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>595</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F78" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>322</v>
+        <v>50</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
@@ -4598,61 +4607,58 @@
         <v>43</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>754</v>
+        <v>45</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>755</v>
+        <v>51</v>
       </c>
       <c r="F79" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>776</v>
+        <v>754</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>755</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>691</v>
+        <v>776</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+        <v>777</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>203</v>
+        <v>692</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>99</v>
@@ -4663,38 +4669,44 @@
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>831</v>
+        <v>674</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>832</v>
+        <v>675</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>689</v>
+        <v>831</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>690</v>
+        <v>832</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>160</v>
+        <v>689</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>161</v>
+        <v>690</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>99</v>
@@ -4705,120 +4717,120 @@
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>658</v>
+        <v>160</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>46</v>
+        <v>658</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>727</v>
+        <v>659</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>728</v>
+        <v>46</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>729</v>
+        <v>52</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>727</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>513</v>
+        <v>728</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+        <v>729</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>792</v>
+        <v>513</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>730</v>
+        <v>792</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>647</v>
+        <v>730</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>648</v>
+        <v>731</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>764</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>309</v>
+        <v>647</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>100</v>
+        <v>648</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -4826,64 +4838,61 @@
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>743</v>
+        <v>309</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>744</v>
+        <v>310</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>47</v>
+        <v>743</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+        <v>744</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>288</v>
+        <v>47</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>660</v>
+        <v>288</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>661</v>
+        <v>289</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>101</v>
+        <v>290</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4891,33 +4900,33 @@
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>169</v>
+        <v>660</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>170</v>
+        <v>661</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+        <v>732</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>671</v>
+        <v>169</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>672</v>
+        <v>170</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>100</v>
+        <v>447</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -4925,13 +4934,16 @@
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>794</v>
+        <v>671</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>101</v>
+        <v>672</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4939,13 +4951,13 @@
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>829</v>
+        <v>794</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>99</v>
+        <v>795</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -4953,13 +4965,13 @@
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>733</v>
+        <v>829</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>101</v>
+        <v>830</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
@@ -4967,114 +4979,114 @@
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>489</v>
+        <v>733</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>734</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>177</v>
+        <v>489</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="F105" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B106" s="2" t="s">
+      <c r="F106" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B107" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C107" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F107" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>735</v>
+        <v>715</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>592</v>
+        <v>735</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>593</v>
+        <v>736</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>99</v>
+        <v>593</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
@@ -5082,10 +5094,10 @@
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>752</v>
+        <v>605</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>753</v>
+        <v>606</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>99</v>
@@ -5096,13 +5108,13 @@
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>596</v>
+        <v>752</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>100</v>
+        <v>753</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
@@ -5110,10 +5122,10 @@
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>662</v>
+        <v>596</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>663</v>
+        <v>597</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>100</v>
@@ -5124,13 +5136,13 @@
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>48</v>
+        <v>662</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>99</v>
+        <v>663</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
@@ -5138,30 +5150,27 @@
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>196</v>
+        <v>48</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>49</v>
+        <v>196</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>323</v>
+        <v>208</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -5169,33 +5178,33 @@
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>757</v>
+        <v>49</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>758</v>
+        <v>54</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>101</v>
+        <v>758</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>759</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5203,41 +5212,44 @@
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>669</v>
+        <v>750</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>670</v>
+        <v>751</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="F119" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+        <v>765</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>186</v>
+        <v>669</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>670</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>579</v>
+        <v>186</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>580</v>
+        <v>187</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>100</v>
@@ -5248,16 +5260,13 @@
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>203</v>
+        <v>579</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>338</v>
+        <v>580</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5265,75 +5274,78 @@
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>681</v>
+        <v>203</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>682</v>
+        <v>204</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>683</v>
+        <v>205</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F125" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="B125" s="2" t="s">
+    <row r="126" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B126" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C126" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="F125" s="14" t="s">
+      <c r="F126" s="14" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>679</v>
+        <v>452</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="F127" s="14" t="s">
-        <v>258</v>
+        <v>453</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5341,13 +5353,13 @@
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>651</v>
+        <v>679</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>100</v>
+        <v>680</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5355,10 +5367,10 @@
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>100</v>
@@ -5369,27 +5381,27 @@
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>574</v>
+        <v>653</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>575</v>
+        <v>654</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>649</v>
+        <v>574</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>99</v>
+        <v>575</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
@@ -5397,30 +5409,27 @@
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>598</v>
+        <v>649</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>596</v>
+        <v>650</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>738</v>
+        <v>598</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>740</v>
+        <v>599</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>596</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>99</v>
@@ -5431,13 +5440,16 @@
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>827</v>
+        <v>738</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>100</v>
+        <v>739</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5445,110 +5457,110 @@
         <v>43</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C136" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="F135" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="17" t="s">
+      <c r="F136" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B136" s="17" t="s">
+      <c r="B137" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="C136" s="17" t="s">
+      <c r="C137" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D136" s="17" t="s">
+      <c r="D137" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="E136" s="17"/>
-      <c r="F136" s="21" t="s">
+      <c r="E137" s="17"/>
+      <c r="F137" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="G136" s="17" t="s">
+      <c r="G137" s="17" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A137" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>631</v>
+        <v>707</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>631</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>418</v>
+        <v>271</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>183</v>
+        <v>418</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>100</v>
+        <v>419</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
@@ -5556,69 +5568,69 @@
         <v>275</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="17" t="s">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A143" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B143" s="17" t="s">
+      <c r="B143" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="B144" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C143" s="17" t="s">
+      <c r="C144" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="D143" s="17"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="20" t="s">
+      <c r="D144" s="17"/>
+      <c r="E144" s="17"/>
+      <c r="F144" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G143" s="17"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A144" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G144" s="17"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>796</v>
+        <v>471</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+        <v>472</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>101</v>
@@ -5629,10 +5641,10 @@
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>101</v>
@@ -5643,16 +5655,13 @@
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>473</v>
+        <v>798</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F148" s="3" t="s">
-        <v>99</v>
+        <v>801</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
@@ -5660,69 +5669,72 @@
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>380</v>
+        <v>473</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>381</v>
+        <v>474</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>475</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>56</v>
+        <v>380</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>268</v>
+        <v>381</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>313</v>
+        <v>56</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>785</v>
+        <v>313</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>786</v>
+        <v>314</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>629</v>
+        <v>785</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>630</v>
+        <v>786</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>101</v>
@@ -5733,13 +5745,10 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>526</v>
+        <v>629</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>527</v>
+        <v>630</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>101</v>
@@ -5750,10 +5759,13 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>802</v>
+        <v>526</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>787</v>
+        <v>803</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>101</v>
@@ -5764,13 +5776,13 @@
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>543</v>
+        <v>802</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>99</v>
+        <v>787</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -5778,61 +5790,58 @@
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>607</v>
+        <v>543</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F157" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>544</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>57</v>
+        <v>607</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+        <v>608</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>311</v>
+        <v>57</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>390</v>
+        <v>311</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F160" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>396</v>
+        <v>312</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5840,16 +5849,16 @@
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F161" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5857,129 +5866,132 @@
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F162" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>58</v>
+        <v>392</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+      <c r="F163" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>376</v>
+        <v>58</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>340</v>
+        <v>61</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B166" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C166" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="F165" s="3" t="s">
+      <c r="F166" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="166" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="17" t="s">
+    <row r="167" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B166" s="17" t="s">
+      <c r="B167" s="17" t="s">
         <v>441</v>
       </c>
-      <c r="C166" s="17" t="s">
+      <c r="C167" s="17" t="s">
         <v>442</v>
       </c>
-      <c r="F166" s="22" t="s">
+      <c r="F167" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G166" s="17" t="s">
+      <c r="G167" s="17" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A167" s="2" t="s">
+    <row r="168" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A168" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B168" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C168" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="D168" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="F167" s="3" t="s">
+      <c r="F168" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="168" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="17" t="s">
+    <row r="169" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A169" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="B168" s="17" t="s">
+      <c r="B169" s="17" t="s">
         <v>761</v>
       </c>
-      <c r="C168" s="17" t="s">
+      <c r="C169" s="17" t="s">
         <v>762</v>
       </c>
-      <c r="D168" s="17" t="s">
+      <c r="D169" s="17" t="s">
         <v>763</v>
       </c>
-      <c r="F168" s="19" t="s">
+      <c r="F169" s="19" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A169" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
@@ -5987,13 +5999,13 @@
         <v>357</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F170" s="4" t="s">
-        <v>100</v>
+        <v>366</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
@@ -6001,27 +6013,24 @@
         <v>357</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>100</v>
@@ -6032,45 +6041,47 @@
         <v>357</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>370</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>818</v>
+        <v>364</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="F175" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="G175" s="2" t="s">
-        <v>820</v>
+        <v>374</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6078,64 +6089,62 @@
         <v>357</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F176" s="6"/>
+      <c r="G176" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A177" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C176" s="2" t="s">
+      <c r="C177" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="F176" s="6" t="s">
+      <c r="F177" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G176" s="2" t="s">
+      <c r="G177" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="17" t="s">
+    <row r="178" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A178" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B177" s="17" t="s">
+      <c r="B178" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="C177" s="17" t="s">
+      <c r="C178" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="D177" s="17"/>
-      <c r="E177" s="17"/>
-      <c r="F177" s="20" t="s">
+      <c r="D178" s="17"/>
+      <c r="E178" s="17"/>
+      <c r="F178" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G177" s="17"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A178" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F178" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G178" s="17"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>519</v>
+        <v>206</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F179" s="14" t="s">
-        <v>400</v>
+        <v>207</v>
+      </c>
+      <c r="F179" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6143,16 +6152,16 @@
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>664</v>
+        <v>519</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>665</v>
+        <v>520</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F180" s="4" t="s">
-        <v>100</v>
+        <v>521</v>
+      </c>
+      <c r="F180" s="14" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6160,19 +6169,16 @@
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>197</v>
+        <v>664</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F181" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G181" s="2" t="s">
-        <v>339</v>
+        <v>665</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6180,13 +6186,19 @@
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>326</v>
+        <v>197</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>101</v>
+        <v>198</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F182" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6194,27 +6206,27 @@
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>64</v>
+        <v>326</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F183" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+        <v>327</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>497</v>
+        <v>64</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>101</v>
+        <v>67</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6222,16 +6234,13 @@
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>65</v>
+        <v>497</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F185" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G185" s="2" t="s">
-        <v>345</v>
+        <v>498</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
@@ -6239,13 +6248,16 @@
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>562</v>
+        <v>65</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>101</v>
+        <v>68</v>
+      </c>
+      <c r="F186" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -6253,13 +6265,13 @@
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>766</v>
+        <v>562</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="F187" s="4" t="s">
-        <v>100</v>
+        <v>563</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
@@ -6267,64 +6279,58 @@
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="F188" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>516</v>
+        <v>772</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F189" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+        <v>773</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>199</v>
+        <v>516</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F190" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>517</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>821</v>
+        <v>199</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F191" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G191" s="2" t="s">
-        <v>824</v>
+        <v>200</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6332,44 +6338,50 @@
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>66</v>
+        <v>821</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>69</v>
+        <v>822</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F192" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+        <v>823</v>
+      </c>
+      <c r="F192" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F193" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F193" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>277</v>
+        <v>190</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F194" s="5" t="s">
-        <v>101</v>
+        <v>191</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6377,10 +6389,10 @@
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>101</v>
@@ -6391,13 +6403,13 @@
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>100</v>
+        <v>281</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6405,103 +6417,100 @@
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>567</v>
+        <v>279</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F197" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>477</v>
+        <v>567</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="F198" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="17" t="s">
+    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A200" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B200" s="17" t="s">
+      <c r="B200" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A201" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B201" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="C200" s="17" t="s">
+      <c r="C201" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="D200" s="17"/>
-      <c r="E200" s="17"/>
-      <c r="F200" s="20" t="s">
+      <c r="D201" s="17"/>
+      <c r="E201" s="17"/>
+      <c r="F201" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G200" s="17"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A201" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G201" s="17"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>559</v>
+        <v>804</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>561</v>
+        <v>805</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>713</v>
+        <v>559</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>714</v>
+        <v>560</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>712</v>
+        <v>561</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>99</v>
@@ -6512,10 +6521,13 @@
         <v>420</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>428</v>
+        <v>713</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>429</v>
+        <v>714</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>712</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>99</v>
@@ -6526,10 +6538,10 @@
         <v>420</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>99</v>
@@ -6540,10 +6552,10 @@
         <v>420</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>99</v>
@@ -6554,44 +6566,44 @@
         <v>420</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>613</v>
+        <v>432</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>99</v>
@@ -6602,30 +6614,27 @@
         <v>420</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>530</v>
+        <v>422</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F211" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G211" s="2" t="s">
-        <v>532</v>
+        <v>424</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6633,48 +6642,48 @@
         <v>420</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>480</v>
+        <v>530</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F212" s="3"/>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+      <c r="F212" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>528</v>
+        <v>480</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F213" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G213" s="2" t="s">
-        <v>533</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F213" s="3"/>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>99</v>
+        <v>529</v>
+      </c>
+      <c r="F214" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
@@ -6682,13 +6691,16 @@
         <v>420</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F215" s="5" t="s">
-        <v>101</v>
+        <v>504</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
@@ -6696,10 +6708,10 @@
         <v>420</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>101</v>
@@ -6710,10 +6722,10 @@
         <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>425</v>
+        <v>468</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>101</v>
@@ -6724,10 +6736,10 @@
         <v>420</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>469</v>
+        <v>423</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>470</v>
+        <v>425</v>
       </c>
       <c r="F218" s="5" t="s">
         <v>101</v>
@@ -6738,106 +6750,106 @@
         <v>420</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>541</v>
+        <v>469</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>470</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>426</v>
+        <v>541</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F220" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>542</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B221" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F221" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A222" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B222" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="C221" s="2" t="s">
+      <c r="C222" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="F221" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="B222" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="C222" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="D222" s="17"/>
-      <c r="E222" s="17"/>
       <c r="F222" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="G222" s="17"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A223" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F223" s="5" t="s">
-        <v>101</v>
-      </c>
+    </row>
+    <row r="223" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A223" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B223" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="C223" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="D223" s="17"/>
+      <c r="E223" s="17"/>
+      <c r="F223" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G223" s="17"/>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>304</v>
+        <v>209</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F224" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>211</v>
+        <v>304</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F225" s="5" t="s">
-        <v>101</v>
+        <v>305</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F225" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6845,30 +6857,30 @@
         <v>93</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F226" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F227" s="5" t="s">
-        <v>101</v>
+        <v>214</v>
+      </c>
+      <c r="F227" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
@@ -6876,10 +6888,10 @@
         <v>93</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>101</v>
@@ -6890,128 +6902,128 @@
         <v>93</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>216</v>
+        <v>94</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F229" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B230" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A231" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="C231" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F230" s="12" t="s">
+      <c r="F231" s="12" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A231" s="17" t="s">
+    <row r="232" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A232" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B231" s="17" t="s">
+      <c r="B232" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C231" s="17" t="s">
+      <c r="C232" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D231" s="17"/>
-      <c r="E231" s="17"/>
-      <c r="F231" s="20" t="s">
+      <c r="D232" s="17"/>
+      <c r="E232" s="17"/>
+      <c r="F232" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G231" s="17"/>
-    </row>
-    <row r="232" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A232" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F232" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G232" s="2" t="s">
-        <v>331</v>
-      </c>
+      <c r="G232" s="17"/>
     </row>
     <row r="233" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>192</v>
+        <v>71</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>747</v>
+        <v>192</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>748</v>
+        <v>194</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G234" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A235" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="F235" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G235" s="2" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A235" s="17" t="s">
+    <row r="236" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A236" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B235" s="17" t="s">
+      <c r="B236" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C235" s="17" t="s">
+      <c r="C236" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="D235" s="17"/>
-      <c r="E235" s="17"/>
-      <c r="F235" s="22" t="s">
+      <c r="D236" s="17"/>
+      <c r="E236" s="17"/>
+      <c r="F236" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G235" s="17" t="s">
+      <c r="G236" s="17" t="s">
         <v>336</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A236" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F236" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -7019,13 +7031,13 @@
         <v>73</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>550</v>
+        <v>632</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>101</v>
+        <v>633</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -7033,13 +7045,13 @@
         <v>73</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>74</v>
+        <v>550</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F238" s="4" t="s">
-        <v>100</v>
+        <v>551</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
@@ -7047,41 +7059,41 @@
         <v>73</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F239" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>554</v>
+        <v>75</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>555</v>
+        <v>83</v>
       </c>
       <c r="F240" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>411</v>
+        <v>554</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F241" s="4" t="s">
-        <v>100</v>
+        <v>555</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
@@ -7089,10 +7101,10 @@
         <v>73</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>677</v>
+        <v>411</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>678</v>
+        <v>412</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>100</v>
@@ -7103,13 +7115,13 @@
         <v>73</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>552</v>
+        <v>677</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F243" s="5" t="s">
-        <v>101</v>
+        <v>678</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
@@ -7117,13 +7129,13 @@
         <v>73</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>283</v>
+        <v>552</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F244" s="3" t="s">
-        <v>99</v>
+        <v>553</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
@@ -7131,44 +7143,44 @@
         <v>73</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F246" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>806</v>
+        <v>236</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="F247" s="3" t="s">
-        <v>99</v>
+        <v>237</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
@@ -7176,13 +7188,13 @@
         <v>73</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>618</v>
+        <v>806</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F248" s="5" t="s">
-        <v>101</v>
+        <v>807</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
@@ -7190,10 +7202,10 @@
         <v>73</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>101</v>
@@ -7204,10 +7216,10 @@
         <v>73</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>232</v>
+        <v>620</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>233</v>
+        <v>621</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>101</v>
@@ -7218,10 +7230,10 @@
         <v>73</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>101</v>
@@ -7232,13 +7244,10 @@
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>634</v>
+        <v>228</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>636</v>
+        <v>229</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>101</v>
@@ -7249,10 +7258,13 @@
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>623</v>
+        <v>635</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>636</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>101</v>
@@ -7263,13 +7275,13 @@
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>825</v>
+        <v>622</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="F254" s="3" t="s">
-        <v>99</v>
+        <v>623</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
@@ -7277,10 +7289,10 @@
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>710</v>
+        <v>825</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>711</v>
+        <v>826</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>99</v>
@@ -7291,10 +7303,10 @@
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>637</v>
+        <v>710</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>638</v>
+        <v>711</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>99</v>
@@ -7305,10 +7317,10 @@
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>99</v>
@@ -7319,13 +7331,13 @@
         <v>73</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="F258" s="4" t="s">
-        <v>100</v>
+        <v>610</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
@@ -7333,44 +7345,44 @@
         <v>73</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>241</v>
+        <v>589</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>242</v>
+        <v>590</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F260" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>76</v>
+        <v>285</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F261" s="5" t="s">
-        <v>101</v>
+        <v>286</v>
+      </c>
+      <c r="F261" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
@@ -7378,10 +7390,10 @@
         <v>73</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>101</v>
@@ -7392,10 +7404,10 @@
         <v>73</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>101</v>
@@ -7406,13 +7418,13 @@
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F264" s="4" t="s">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -7420,16 +7432,13 @@
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>624</v>
+        <v>79</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="F265" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
@@ -7437,13 +7446,16 @@
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>448</v>
+        <v>624</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="F266" s="4" t="s">
-        <v>100</v>
+        <v>625</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="F266" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
@@ -7451,41 +7463,41 @@
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>639</v>
+        <v>478</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+        <v>479</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>741</v>
+        <v>639</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="F269" s="3" t="s">
-        <v>99</v>
+        <v>640</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
@@ -7493,10 +7505,10 @@
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>80</v>
+        <v>741</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>88</v>
+        <v>742</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>99</v>
@@ -7507,30 +7519,27 @@
         <v>73</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>548</v>
+        <v>80</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>293</v>
+        <v>548</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F272" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G272" s="2" t="s">
-        <v>335</v>
+        <v>549</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7538,10 +7547,10 @@
         <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F273" s="16" t="s">
         <v>303</v>
@@ -7555,10 +7564,10 @@
         <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>239</v>
+        <v>295</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="F274" s="16" t="s">
         <v>303</v>
@@ -7567,35 +7576,38 @@
         <v>335</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F275" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="F275" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>693</v>
+        <v>230</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="F276" s="5" t="s">
-        <v>238</v>
+        <v>231</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7603,58 +7615,58 @@
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>81</v>
+        <v>693</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F277" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+        <v>694</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>745</v>
+        <v>81</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>746</v>
+        <v>89</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>443</v>
+        <v>745</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F279" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G279" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+        <v>746</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>641</v>
+        <v>443</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="F280" s="5" t="s">
-        <v>101</v>
+        <v>444</v>
+      </c>
+      <c r="F280" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
@@ -7662,44 +7674,44 @@
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>507</v>
+        <v>641</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>508</v>
+        <v>642</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>778</v>
+        <v>507</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="F282" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G282" s="2" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+        <v>508</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>245</v>
+        <v>778</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F283" s="14" t="s">
-        <v>258</v>
+        <v>779</v>
+      </c>
+      <c r="F283" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
@@ -7707,13 +7719,13 @@
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F284" s="5" t="s">
-        <v>101</v>
+        <v>246</v>
+      </c>
+      <c r="F284" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
@@ -7721,13 +7733,13 @@
         <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>643</v>
+        <v>298</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>100</v>
+        <v>297</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
@@ -7735,13 +7747,13 @@
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>234</v>
+        <v>643</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F286" s="5" t="s">
-        <v>101</v>
+        <v>644</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -7749,10 +7761,10 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>627</v>
+        <v>234</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>628</v>
+        <v>235</v>
       </c>
       <c r="F287" s="5" t="s">
         <v>101</v>
@@ -7763,13 +7775,13 @@
         <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>226</v>
+        <v>627</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F288" s="12" t="s">
-        <v>250</v>
+        <v>628</v>
+      </c>
+      <c r="F288" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -7777,13 +7789,13 @@
         <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>524</v>
+        <v>226</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F289" s="14" t="s">
-        <v>258</v>
+        <v>227</v>
+      </c>
+      <c r="F289" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -7791,16 +7803,13 @@
         <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F290" s="5" t="s">
-        <v>101</v>
+        <v>525</v>
+      </c>
+      <c r="F290" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -7808,44 +7817,44 @@
         <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>224</v>
+        <v>522</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>225</v>
+        <v>523</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="F291" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>645</v>
+        <v>224</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="F292" s="20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="F292" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>584</v>
+        <v>645</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G293" s="2" t="s">
-        <v>587</v>
+        <v>646</v>
+      </c>
+      <c r="F293" s="20" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7853,81 +7862,81 @@
         <v>73</v>
       </c>
       <c r="B294" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G294" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A295" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="C295" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="F294" s="16" t="s">
+      <c r="F295" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="G294" s="2" t="s">
+      <c r="G295" s="2" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A295" s="17" t="s">
+    <row r="296" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A296" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B295" s="17" t="s">
+      <c r="B296" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C295" s="17" t="s">
+      <c r="C296" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D295" s="17"/>
-      <c r="E295" s="17"/>
-      <c r="F295" s="20" t="s">
+      <c r="D296" s="17"/>
+      <c r="E296" s="17"/>
+      <c r="F296" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G295" s="17"/>
-    </row>
-    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A296" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F296" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G296" s="17"/>
+    </row>
+    <row r="297" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>221</v>
+        <v>92</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>403</v>
+        <v>315</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>249</v>
+        <v>403</v>
       </c>
       <c r="F298" s="5" t="s">
         <v>101</v>
@@ -7938,27 +7947,30 @@
         <v>90</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>808</v>
+        <v>247</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="F299" s="25" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>351</v>
+        <v>808</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>100</v>
+        <v>809</v>
+      </c>
+      <c r="F300" s="25" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
@@ -7966,36 +7978,50 @@
         <v>90</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>564</v>
+        <v>351</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>566</v>
+        <v>352</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A302" s="17" t="s">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A302" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B302" s="17" t="s">
+      <c r="B302" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A303" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B303" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C302" s="17" t="s">
+      <c r="C303" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D302" s="17" t="s">
+      <c r="D303" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E302" s="17"/>
-      <c r="F302" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G302" s="17"/>
+      <c r="E303" s="17"/>
+      <c r="F303" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G303" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8260A84B-734B-418D-B415-453762BCD744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23259964-C2C7-4073-BFAA-8518DEBC6B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="834">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2099,12 +2099,6 @@
   </si>
   <si>
     <t>CCS Transportation and Storage Cost</t>
-  </si>
-  <si>
-    <t>BSpUESttGbGB</t>
-  </si>
-  <si>
-    <t>BAU Subsidy per Unit Electricity Supplied to the Grid by Grid Batteries</t>
   </si>
   <si>
     <t>BPSpUGBCD</t>
@@ -3351,7 +3345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G303"/>
+  <dimension ref="A1:G302"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -3518,10 +3512,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>99</v>
@@ -3594,16 +3588,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3712,10 +3706,10 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>101</v>
@@ -3942,13 +3936,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>101</v>
@@ -3959,10 +3953,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>100</v>
@@ -3979,7 +3973,7 @@
         <v>417</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>101</v>
@@ -3996,7 +3990,7 @@
         <v>410</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>101</v>
@@ -4021,19 +4015,19 @@
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>814</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>816</v>
       </c>
       <c r="F43" s="21" t="s">
         <v>303</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4041,10 +4035,10 @@
         <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>100</v>
@@ -4055,10 +4049,10 @@
         <v>36</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F45" s="20" t="s">
         <v>100</v>
@@ -4113,7 +4107,7 @@
         <v>142</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -4172,16 +4166,16 @@
         <v>413</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -4223,16 +4217,16 @@
         <v>413</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -4291,16 +4285,16 @@
         <v>413</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4362,7 +4356,7 @@
         <v>465</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E63" s="17"/>
       <c r="F63" s="22" t="s">
@@ -4452,10 +4446,10 @@
         <v>43</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>100</v>
@@ -4466,10 +4460,10 @@
         <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>100</v>
@@ -4500,10 +4494,10 @@
         <v>181</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>100</v>
@@ -4582,7 +4576,7 @@
         <v>595</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>250</v>
@@ -4624,16 +4618,16 @@
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
@@ -4641,10 +4635,10 @@
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>101</v>
@@ -4655,10 +4649,10 @@
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>99</v>
@@ -4689,24 +4683,24 @@
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>689</v>
+        <v>160</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>690</v>
+        <v>161</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>99</v>
@@ -4717,120 +4711,120 @@
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>160</v>
+        <v>658</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+        <v>659</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>658</v>
+        <v>46</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>659</v>
+        <v>52</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>725</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>46</v>
+        <v>726</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D88" s="2" t="s">
         <v>727</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>728</v>
+        <v>513</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>513</v>
+        <v>790</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+        <v>791</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>792</v>
+        <v>728</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>793</v>
+        <v>729</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>762</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>730</v>
+        <v>647</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>764</v>
+        <v>648</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>647</v>
+        <v>309</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>101</v>
+        <v>310</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -4838,61 +4832,64 @@
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>309</v>
+        <v>741</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>310</v>
+        <v>742</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>743</v>
+        <v>47</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>47</v>
+        <v>288</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>171</v>
+        <v>289</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+        <v>290</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>288</v>
+        <v>660</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>289</v>
+        <v>661</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>100</v>
+        <v>730</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4900,33 +4897,33 @@
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>660</v>
+        <v>169</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>661</v>
+        <v>170</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>447</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>169</v>
+        <v>671</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>170</v>
+        <v>672</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>99</v>
+        <v>673</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -4934,16 +4931,13 @@
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>671</v>
+        <v>792</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>100</v>
+        <v>793</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4951,13 +4945,13 @@
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>794</v>
+        <v>827</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>101</v>
+        <v>828</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -4965,13 +4959,13 @@
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>829</v>
+        <v>731</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>99</v>
+        <v>732</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
@@ -4979,114 +4973,114 @@
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>733</v>
+        <v>489</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>489</v>
+        <v>177</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>177</v>
+        <v>766</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>321</v>
+        <v>768</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A106" s="2" t="s">
+      <c r="B106" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B107" s="2" t="s">
-        <v>769</v>
+        <v>713</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>714</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>715</v>
+        <v>733</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>716</v>
+        <v>734</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>735</v>
+        <v>592</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>736</v>
+        <v>593</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>100</v>
+        <v>606</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
@@ -5094,10 +5088,10 @@
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>605</v>
+        <v>750</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>606</v>
+        <v>751</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>99</v>
@@ -5108,13 +5102,13 @@
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>752</v>
+        <v>596</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>99</v>
+        <v>597</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
@@ -5122,10 +5116,10 @@
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>596</v>
+        <v>662</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>597</v>
+        <v>663</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>100</v>
@@ -5136,13 +5130,13 @@
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>662</v>
+        <v>48</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>100</v>
+        <v>53</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
@@ -5150,27 +5144,30 @@
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>48</v>
+        <v>196</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>196</v>
+        <v>49</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>100</v>
+        <v>54</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -5178,33 +5175,33 @@
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>49</v>
+        <v>755</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>54</v>
+        <v>756</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>759</v>
+        <v>749</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5212,44 +5209,41 @@
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>750</v>
+        <v>669</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>751</v>
+        <v>670</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>735</v>
+      </c>
+      <c r="F119" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>669</v>
+        <v>186</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="F120" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>186</v>
+        <v>579</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>187</v>
+        <v>580</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>100</v>
@@ -5260,13 +5254,16 @@
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>579</v>
+        <v>203</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>100</v>
+        <v>204</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5274,78 +5271,75 @@
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>203</v>
+        <v>681</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>204</v>
+        <v>682</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>205</v>
+        <v>683</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>681</v>
+        <v>600</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>682</v>
+        <v>601</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A125" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B125" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>667</v>
+        <v>452</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="F126" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>453</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>452</v>
+        <v>679</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>100</v>
+        <v>680</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5353,13 +5347,13 @@
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>679</v>
+        <v>651</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="F128" s="14" t="s">
-        <v>258</v>
+        <v>652</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5367,10 +5361,10 @@
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>100</v>
@@ -5381,27 +5375,27 @@
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>653</v>
+        <v>574</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>654</v>
+        <v>575</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>574</v>
+        <v>649</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>100</v>
+        <v>650</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
@@ -5409,27 +5403,30 @@
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>649</v>
+        <v>598</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>650</v>
+        <v>599</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>596</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>598</v>
+        <v>736</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>596</v>
+        <v>737</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>738</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>99</v>
@@ -5440,16 +5437,13 @@
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>738</v>
+        <v>825</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>99</v>
+        <v>826</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5457,110 +5451,110 @@
         <v>43</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>827</v>
+        <v>706</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="F135" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B136" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C136" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="D136" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="E136" s="17"/>
+      <c r="F136" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G136" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A137" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="F137" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B137" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="C137" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="D137" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="E137" s="17"/>
-      <c r="F137" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G137" s="17" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>707</v>
+        <v>631</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>631</v>
+        <v>272</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>271</v>
+        <v>418</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>418</v>
+        <v>183</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>101</v>
+        <v>182</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
@@ -5568,69 +5562,69 @@
         <v>275</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A143" s="2" t="s">
+    <row r="143" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F143" s="4" t="s">
+      <c r="B143" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C143" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D143" s="17"/>
+      <c r="E143" s="17"/>
+      <c r="F143" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="B144" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="C144" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="D144" s="17"/>
-      <c r="E144" s="17"/>
-      <c r="F144" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G144" s="17"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G143" s="17"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A144" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>471</v>
+        <v>794</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>797</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>101</v>
@@ -5641,10 +5635,10 @@
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>101</v>
@@ -5655,13 +5649,16 @@
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>798</v>
+        <v>473</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>101</v>
+        <v>474</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
@@ -5669,72 +5666,69 @@
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>473</v>
+        <v>380</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>380</v>
+        <v>56</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>381</v>
+        <v>59</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>268</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>56</v>
+        <v>313</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>313</v>
+        <v>783</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>314</v>
+        <v>784</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>785</v>
+        <v>629</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>786</v>
+        <v>630</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>101</v>
@@ -5745,10 +5739,13 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>629</v>
+        <v>526</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>630</v>
+        <v>801</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>101</v>
@@ -5759,13 +5756,10 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>526</v>
+        <v>800</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>527</v>
+        <v>785</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>101</v>
@@ -5776,13 +5770,13 @@
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>802</v>
+        <v>543</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>101</v>
+        <v>544</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -5790,58 +5784,61 @@
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>543</v>
+        <v>607</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+        <v>608</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>607</v>
+        <v>57</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F158" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>57</v>
+        <v>311</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>311</v>
+        <v>390</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>101</v>
+        <v>393</v>
+      </c>
+      <c r="F160" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5849,16 +5846,16 @@
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F161" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5866,132 +5863,129 @@
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F162" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>392</v>
+        <v>58</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F163" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>58</v>
+        <v>376</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>61</v>
+        <v>340</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F164" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>341</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F165" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F166" s="3" t="s">
+      <c r="B166" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="C166" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="F166" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="G166" s="17" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A167" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F167" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="167" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B167" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="C167" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="F167" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G167" s="17" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A168" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F168" s="3" t="s">
+    <row r="168" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A168" s="17" t="s">
+        <v>758</v>
+      </c>
+      <c r="B168" s="17" t="s">
+        <v>759</v>
+      </c>
+      <c r="C168" s="17" t="s">
+        <v>760</v>
+      </c>
+      <c r="D168" s="17" t="s">
+        <v>761</v>
+      </c>
+      <c r="F168" s="19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="169" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="17" t="s">
-        <v>760</v>
-      </c>
-      <c r="B169" s="17" t="s">
-        <v>761</v>
-      </c>
-      <c r="C169" s="17" t="s">
-        <v>762</v>
-      </c>
-      <c r="D169" s="17" t="s">
-        <v>763</v>
-      </c>
-      <c r="F169" s="19" t="s">
-        <v>99</v>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A169" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
@@ -5999,13 +5993,13 @@
         <v>357</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>101</v>
+        <v>367</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
@@ -6013,24 +6007,27 @@
         <v>357</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>100</v>
@@ -6041,47 +6038,45 @@
         <v>357</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F174" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+        <v>371</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>364</v>
+        <v>816</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F175" s="6" t="s">
-        <v>142</v>
-      </c>
+        <v>817</v>
+      </c>
+      <c r="F175" s="6"/>
       <c r="G175" s="2" t="s">
-        <v>374</v>
+        <v>818</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6089,62 +6084,64 @@
         <v>357</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>818</v>
+        <v>365</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="F176" s="6"/>
+        <v>372</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="G176" s="2" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A177" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A177" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F177" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G177" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="B178" s="17" t="s">
+      <c r="B177" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="C178" s="17" t="s">
+      <c r="C177" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="D178" s="17"/>
-      <c r="E178" s="17"/>
-      <c r="F178" s="20" t="s">
+      <c r="D177" s="17"/>
+      <c r="E177" s="17"/>
+      <c r="F177" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G178" s="17"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G177" s="17"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A178" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>206</v>
+        <v>519</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F179" s="12" t="s">
-        <v>250</v>
+        <v>520</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F179" s="14" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6152,16 +6149,16 @@
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>519</v>
+        <v>664</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>520</v>
+        <v>665</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F180" s="14" t="s">
-        <v>400</v>
+        <v>666</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6169,16 +6166,19 @@
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>664</v>
+        <v>197</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F181" s="4" t="s">
-        <v>100</v>
+        <v>198</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F181" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6186,19 +6186,13 @@
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>197</v>
+        <v>326</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F182" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>339</v>
+        <v>327</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6206,27 +6200,27 @@
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>326</v>
+        <v>64</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>64</v>
+        <v>497</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F184" s="4" t="s">
-        <v>100</v>
+        <v>498</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6234,13 +6228,16 @@
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>497</v>
+        <v>65</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>101</v>
+        <v>68</v>
+      </c>
+      <c r="F185" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
@@ -6248,16 +6245,13 @@
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>65</v>
+        <v>562</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F186" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G186" s="2" t="s">
-        <v>345</v>
+        <v>563</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -6265,13 +6259,13 @@
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>562</v>
+        <v>764</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>101</v>
+        <v>765</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
@@ -6279,58 +6273,64 @@
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="F188" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>772</v>
+        <v>516</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F189" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>517</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>516</v>
+        <v>199</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F190" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G190" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>199</v>
+        <v>819</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F191" s="4" t="s">
-        <v>100</v>
+        <v>820</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="F191" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6338,50 +6338,44 @@
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>821</v>
+        <v>66</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>822</v>
+        <v>69</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F192" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G192" s="2" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>399</v>
+      </c>
+      <c r="F192" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F193" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>190</v>
+        <v>277</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F194" s="4" t="s">
-        <v>100</v>
+        <v>280</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6389,10 +6383,10 @@
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>101</v>
@@ -6403,13 +6397,13 @@
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F196" s="5" t="s">
-        <v>101</v>
+        <v>282</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6417,100 +6411,103 @@
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>279</v>
+        <v>567</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F197" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>567</v>
+        <v>477</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F198" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+        <v>476</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A200" s="2" t="s">
+    <row r="200" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A200" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F200" s="4" t="s">
+      <c r="B200" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="C200" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="D200" s="17"/>
+      <c r="E200" s="17"/>
+      <c r="F200" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B201" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="C201" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="D201" s="17"/>
-      <c r="E201" s="17"/>
-      <c r="F201" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G201" s="17"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G200" s="17"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A201" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>804</v>
+        <v>559</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>805</v>
+        <v>560</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>561</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>559</v>
+        <v>711</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>560</v>
+        <v>712</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>561</v>
+        <v>710</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>99</v>
@@ -6521,13 +6518,10 @@
         <v>420</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>713</v>
+        <v>428</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>712</v>
+        <v>429</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>99</v>
@@ -6538,10 +6532,10 @@
         <v>420</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>99</v>
@@ -6552,10 +6546,10 @@
         <v>420</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>430</v>
+        <v>401</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>431</v>
+        <v>402</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>99</v>
@@ -6566,44 +6560,44 @@
         <v>420</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>432</v>
+        <v>613</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>433</v>
+        <v>615</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>434</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>613</v>
+        <v>434</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>99</v>
@@ -6614,27 +6608,30 @@
         <v>420</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>422</v>
+        <v>530</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>99</v>
+        <v>531</v>
+      </c>
+      <c r="F211" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6642,48 +6639,48 @@
         <v>420</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>530</v>
+        <v>480</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F212" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G212" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>481</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F212" s="3"/>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>480</v>
+        <v>528</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F213" s="3"/>
+        <v>529</v>
+      </c>
+      <c r="F213" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>533</v>
+      </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>528</v>
+        <v>503</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F214" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G214" s="2" t="s">
-        <v>533</v>
+        <v>504</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
@@ -6691,16 +6688,13 @@
         <v>420</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F215" s="3" t="s">
-        <v>99</v>
+        <v>502</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
@@ -6708,10 +6702,10 @@
         <v>420</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>502</v>
+        <v>468</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>101</v>
@@ -6722,10 +6716,10 @@
         <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>467</v>
+        <v>423</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>468</v>
+        <v>425</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>101</v>
@@ -6736,10 +6730,10 @@
         <v>420</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>423</v>
+        <v>469</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>425</v>
+        <v>470</v>
       </c>
       <c r="F218" s="5" t="s">
         <v>101</v>
@@ -6750,106 +6744,106 @@
         <v>420</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F219" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+        <v>542</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>541</v>
+        <v>426</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F220" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>427</v>
+      </c>
+      <c r="F220" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>426</v>
+        <v>569</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F221" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G221" s="2" t="s">
-        <v>534</v>
+        <v>570</v>
+      </c>
+      <c r="F221" s="19" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="2" t="s">
+      <c r="A222" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="B222" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>570</v>
-      </c>
+      <c r="B222" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="C222" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="D222" s="17"/>
+      <c r="E222" s="17"/>
       <c r="F222" s="19" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="B223" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="C223" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="D223" s="17"/>
-      <c r="E223" s="17"/>
-      <c r="F223" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="G223" s="17"/>
+      <c r="G222" s="17"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A223" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F224" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F224" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>304</v>
+        <v>211</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F225" s="12" t="s">
-        <v>250</v>
+        <v>212</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6857,30 +6851,30 @@
         <v>93</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F226" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+      <c r="F226" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F227" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G227" s="2" t="s">
-        <v>346</v>
+        <v>220</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
@@ -6888,10 +6882,10 @@
         <v>93</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>215</v>
+        <v>94</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>101</v>
@@ -6902,128 +6896,128 @@
         <v>93</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F230" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A231" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F230" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A231" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B231" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F231" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A232" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B232" s="17" t="s">
+      <c r="B231" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C232" s="17" t="s">
+      <c r="C231" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D232" s="17"/>
-      <c r="E232" s="17"/>
-      <c r="F232" s="20" t="s">
+      <c r="D231" s="17"/>
+      <c r="E231" s="17"/>
+      <c r="F231" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G232" s="17"/>
+      <c r="G231" s="17"/>
+    </row>
+    <row r="232" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A232" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="233" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>192</v>
+        <v>745</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>194</v>
+        <v>746</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A235" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A235" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B235" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="F235" s="6" t="s">
+      <c r="B235" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C235" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D235" s="17"/>
+      <c r="E235" s="17"/>
+      <c r="F235" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G235" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A236" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B236" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C236" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="D236" s="17"/>
-      <c r="E236" s="17"/>
-      <c r="F236" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G236" s="17" t="s">
+      <c r="G235" s="17" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A236" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -7031,13 +7025,13 @@
         <v>73</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>632</v>
+        <v>550</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F237" s="4" t="s">
-        <v>100</v>
+        <v>551</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -7045,13 +7039,13 @@
         <v>73</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>550</v>
+        <v>74</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F238" s="5" t="s">
-        <v>101</v>
+        <v>82</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
@@ -7059,41 +7053,41 @@
         <v>73</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F239" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>75</v>
+        <v>554</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>83</v>
+        <v>555</v>
       </c>
       <c r="F240" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>554</v>
+        <v>411</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F241" s="5" t="s">
-        <v>101</v>
+        <v>412</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
@@ -7101,10 +7095,10 @@
         <v>73</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>411</v>
+        <v>677</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>412</v>
+        <v>678</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>100</v>
@@ -7115,13 +7109,13 @@
         <v>73</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>677</v>
+        <v>552</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F243" s="4" t="s">
-        <v>100</v>
+        <v>553</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
@@ -7129,13 +7123,13 @@
         <v>73</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>552</v>
+        <v>283</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F244" s="5" t="s">
-        <v>101</v>
+        <v>284</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
@@ -7143,44 +7137,44 @@
         <v>73</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F246" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>236</v>
+        <v>804</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F247" s="5" t="s">
-        <v>101</v>
+        <v>805</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
@@ -7188,13 +7182,13 @@
         <v>73</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>806</v>
+        <v>618</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="F248" s="3" t="s">
-        <v>99</v>
+        <v>619</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
@@ -7202,10 +7196,10 @@
         <v>73</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>101</v>
@@ -7216,10 +7210,10 @@
         <v>73</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>620</v>
+        <v>232</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>621</v>
+        <v>233</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>101</v>
@@ -7230,10 +7224,10 @@
         <v>73</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>101</v>
@@ -7244,10 +7238,13 @@
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>228</v>
+        <v>634</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>229</v>
+        <v>635</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>636</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>101</v>
@@ -7258,13 +7255,10 @@
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>101</v>
@@ -7275,13 +7269,13 @@
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>622</v>
+        <v>823</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F254" s="5" t="s">
-        <v>101</v>
+        <v>824</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
@@ -7289,10 +7283,10 @@
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>825</v>
+        <v>708</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>826</v>
+        <v>709</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>99</v>
@@ -7303,10 +7297,10 @@
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>710</v>
+        <v>637</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>711</v>
+        <v>638</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>99</v>
@@ -7317,10 +7311,10 @@
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>638</v>
+        <v>610</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>99</v>
@@ -7331,13 +7325,13 @@
         <v>73</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>99</v>
+        <v>590</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
@@ -7345,44 +7339,44 @@
         <v>73</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>589</v>
+        <v>241</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>590</v>
+        <v>242</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F260" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="F260" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F261" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G261" s="2" t="s">
-        <v>334</v>
+        <v>84</v>
+      </c>
+      <c r="F261" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
@@ -7390,10 +7384,10 @@
         <v>73</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>101</v>
@@ -7404,10 +7398,10 @@
         <v>73</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>101</v>
@@ -7418,13 +7412,13 @@
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F264" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -7432,13 +7426,16 @@
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>79</v>
+        <v>624</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F265" s="4" t="s">
-        <v>100</v>
+        <v>625</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
@@ -7446,16 +7443,13 @@
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>624</v>
+        <v>448</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="F266" s="5" t="s">
-        <v>101</v>
+        <v>449</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
@@ -7463,41 +7457,41 @@
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>478</v>
+        <v>639</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="F268" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>640</v>
+      </c>
+      <c r="F268" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>639</v>
+        <v>739</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="F269" s="5" t="s">
-        <v>101</v>
+        <v>740</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
@@ -7505,10 +7499,10 @@
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>741</v>
+        <v>80</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>742</v>
+        <v>88</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>99</v>
@@ -7519,27 +7513,30 @@
         <v>73</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>80</v>
+        <v>548</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F271" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+        <v>549</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>548</v>
+        <v>293</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F272" s="5" t="s">
-        <v>101</v>
+        <v>294</v>
+      </c>
+      <c r="F272" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G272" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7547,10 +7544,10 @@
         <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F273" s="16" t="s">
         <v>303</v>
@@ -7564,10 +7561,10 @@
         <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="F274" s="16" t="s">
         <v>303</v>
@@ -7576,38 +7573,35 @@
         <v>335</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F275" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G275" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>230</v>
+        <v>691</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F276" s="4" t="s">
-        <v>100</v>
+        <v>692</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7615,58 +7609,58 @@
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>693</v>
+        <v>81</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="F277" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>81</v>
+        <v>743</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>89</v>
+        <v>744</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>745</v>
+        <v>443</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="F279" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>444</v>
+      </c>
+      <c r="F279" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>443</v>
+        <v>641</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F280" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G280" s="2" t="s">
-        <v>377</v>
+        <v>642</v>
+      </c>
+      <c r="F280" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
@@ -7674,44 +7668,44 @@
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>641</v>
+        <v>507</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>642</v>
+        <v>508</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>507</v>
+        <v>776</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F282" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>777</v>
+      </c>
+      <c r="F282" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>778</v>
+        <v>245</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="F283" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G283" s="2" t="s">
-        <v>780</v>
+        <v>246</v>
+      </c>
+      <c r="F283" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
@@ -7719,13 +7713,13 @@
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>245</v>
+        <v>298</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F284" s="14" t="s">
-        <v>258</v>
+        <v>297</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
@@ -7733,13 +7727,13 @@
         <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>298</v>
+        <v>643</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F285" s="5" t="s">
-        <v>101</v>
+        <v>644</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
@@ -7747,13 +7741,13 @@
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>643</v>
+        <v>234</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F286" s="4" t="s">
-        <v>100</v>
+        <v>235</v>
+      </c>
+      <c r="F286" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -7761,10 +7755,10 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>234</v>
+        <v>627</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>235</v>
+        <v>628</v>
       </c>
       <c r="F287" s="5" t="s">
         <v>101</v>
@@ -7775,13 +7769,13 @@
         <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>627</v>
+        <v>226</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="F288" s="5" t="s">
-        <v>101</v>
+        <v>227</v>
+      </c>
+      <c r="F288" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -7789,13 +7783,13 @@
         <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>226</v>
+        <v>524</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F289" s="12" t="s">
-        <v>250</v>
+        <v>525</v>
+      </c>
+      <c r="F289" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -7803,13 +7797,16 @@
         <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F290" s="14" t="s">
-        <v>258</v>
+        <v>523</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -7817,44 +7814,44 @@
         <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>522</v>
+        <v>224</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F291" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>224</v>
+        <v>645</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F292" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>646</v>
+      </c>
+      <c r="F292" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>645</v>
+        <v>584</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="F293" s="20" t="s">
-        <v>100</v>
+        <v>586</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7862,81 +7859,81 @@
         <v>73</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F294" s="3" t="s">
-        <v>99</v>
+        <v>588</v>
+      </c>
+      <c r="F294" s="16" t="s">
+        <v>303</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A295" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A295" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B295" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F295" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G295" s="2" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A296" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B296" s="17" t="s">
+      <c r="B295" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C296" s="17" t="s">
+      <c r="C295" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D296" s="17"/>
-      <c r="E296" s="17"/>
-      <c r="F296" s="20" t="s">
+      <c r="D295" s="17"/>
+      <c r="E295" s="17"/>
+      <c r="F295" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G296" s="17"/>
-    </row>
-    <row r="297" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G295" s="17"/>
+    </row>
+    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A296" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F296" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>91</v>
+        <v>222</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>315</v>
+        <v>403</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>403</v>
+        <v>249</v>
       </c>
       <c r="F298" s="5" t="s">
         <v>101</v>
@@ -7947,30 +7944,27 @@
         <v>90</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>247</v>
+        <v>806</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D299" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F299" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>807</v>
+      </c>
+      <c r="F299" s="25" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>808</v>
+        <v>351</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="F300" s="25" t="s">
-        <v>810</v>
+        <v>352</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
@@ -7978,50 +7972,36 @@
         <v>90</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>351</v>
+        <v>564</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>352</v>
+        <v>565</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>566</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A302" s="2" t="s">
+    <row r="302" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A302" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B302" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D302" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F302" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A303" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B303" s="17" t="s">
+      <c r="B302" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C303" s="17" t="s">
+      <c r="C302" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D303" s="17" t="s">
+      <c r="D302" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E303" s="17"/>
-      <c r="F303" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G303" s="17"/>
+      <c r="E302" s="17"/>
+      <c r="F302" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G302" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23259964-C2C7-4073-BFAA-8518DEBC6B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B03495-367A-425A-B8FF-BA60D751B3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="837">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2534,6 +2534,15 @@
   </si>
   <si>
     <t>You wish to change the default behavior or whether electricity exports are included or excluded in RPS and CES policies.</t>
+  </si>
+  <si>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>Modeled Vintages</t>
+  </si>
+  <si>
+    <t>You are using a different model start year than the US EPS (this file should note which vintages are for historical years rather than modeled years)</t>
   </si>
 </sst>
 </file>
@@ -2642,7 +2651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2703,6 +2712,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3345,7 +3360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G302"/>
+  <dimension ref="A1:G303"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -4345,39 +4360,43 @@
         <v>101</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="17" t="s">
+    <row r="63" spans="1:7" s="26" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="26" t="s">
         <v>413</v>
       </c>
-      <c r="B63" s="17" t="s">
+      <c r="B63" s="26" t="s">
         <v>464</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="26" t="s">
         <v>465</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="26" t="s">
         <v>721</v>
       </c>
-      <c r="E63" s="17"/>
-      <c r="F63" s="22" t="s">
+      <c r="F63" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="G63" s="26" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>99</v>
+    <row r="64" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>834</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G64" s="17" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
@@ -4385,10 +4404,10 @@
         <v>38</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>201</v>
+        <v>39</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>202</v>
+        <v>41</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>99</v>
@@ -4399,13 +4418,13 @@
         <v>38</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>100</v>
+        <v>202</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -4413,46 +4432,46 @@
         <v>38</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>545</v>
+        <v>40</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>546</v>
+        <v>42</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="17" t="s">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C69" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="21" t="s">
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="G68" s="17" t="s">
+      <c r="G69" s="17" t="s">
         <v>387</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
@@ -4460,30 +4479,27 @@
         <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>655</v>
+        <v>787</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>101</v>
+        <v>789</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4491,44 +4507,47 @@
         <v>43</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>181</v>
+        <v>655</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>722</v>
+        <v>656</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+        <v>657</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>328</v>
+        <v>181</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>722</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>603</v>
+        <v>328</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>101</v>
+        <v>329</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4536,16 +4555,13 @@
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>684</v>
+        <v>603</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>100</v>
+        <v>602</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4553,33 +4569,33 @@
         <v>43</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>175</v>
+        <v>684</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F76" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+        <v>685</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>594</v>
+        <v>175</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>250</v>
+        <v>174</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -4587,30 +4603,30 @@
         <v>43</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>44</v>
+        <v>594</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>595</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F79" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>322</v>
+        <v>50</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
@@ -4618,61 +4634,58 @@
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>752</v>
+        <v>45</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>753</v>
+        <v>51</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>774</v>
+        <v>752</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>753</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>689</v>
+        <v>774</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+        <v>775</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>203</v>
+        <v>690</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>99</v>
@@ -4683,10 +4696,16 @@
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>829</v>
+        <v>674</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>830</v>
+        <v>675</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>99</v>
@@ -4697,10 +4716,10 @@
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>160</v>
+        <v>829</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>161</v>
+        <v>830</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>99</v>
@@ -4711,120 +4730,120 @@
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>658</v>
+        <v>160</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>46</v>
+        <v>658</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>725</v>
+        <v>659</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>726</v>
+        <v>46</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>727</v>
+        <v>52</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>725</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>513</v>
+        <v>726</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+        <v>727</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>790</v>
+        <v>513</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>728</v>
+        <v>790</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>647</v>
+        <v>728</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>648</v>
+        <v>729</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>762</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>309</v>
+        <v>647</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>100</v>
+        <v>648</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -4832,64 +4851,61 @@
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>741</v>
+        <v>309</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>742</v>
+        <v>310</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>47</v>
+        <v>741</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+        <v>742</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>288</v>
+        <v>47</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>703</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>660</v>
+        <v>288</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>661</v>
+        <v>289</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>101</v>
+        <v>290</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4897,33 +4913,33 @@
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>169</v>
+        <v>660</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>170</v>
+        <v>661</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+        <v>730</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>671</v>
+        <v>169</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>672</v>
+        <v>170</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>100</v>
+        <v>447</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -4931,13 +4947,16 @@
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>792</v>
+        <v>671</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>101</v>
+        <v>672</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4945,13 +4964,13 @@
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>827</v>
+        <v>792</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>99</v>
+        <v>793</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -4959,13 +4978,13 @@
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>731</v>
+        <v>827</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>101</v>
+        <v>828</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
@@ -4973,114 +4992,114 @@
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>489</v>
+        <v>731</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>732</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>177</v>
+        <v>489</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="F105" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B106" s="2" t="s">
+      <c r="F106" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B107" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C107" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F107" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>733</v>
+        <v>713</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>592</v>
+        <v>733</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>593</v>
+        <v>734</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>99</v>
+        <v>593</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
@@ -5088,10 +5107,10 @@
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>750</v>
+        <v>605</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>751</v>
+        <v>606</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>99</v>
@@ -5102,13 +5121,13 @@
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>596</v>
+        <v>750</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>100</v>
+        <v>751</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
@@ -5116,10 +5135,10 @@
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>662</v>
+        <v>596</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>663</v>
+        <v>597</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>100</v>
@@ -5130,13 +5149,13 @@
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>48</v>
+        <v>662</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>99</v>
+        <v>663</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
@@ -5144,30 +5163,27 @@
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>196</v>
+        <v>48</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>49</v>
+        <v>196</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>323</v>
+        <v>208</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -5175,33 +5191,33 @@
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>755</v>
+        <v>49</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>756</v>
+        <v>54</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>101</v>
+        <v>756</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5209,41 +5225,44 @@
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>669</v>
+        <v>748</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>670</v>
+        <v>749</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="F119" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+        <v>763</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>186</v>
+        <v>669</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>670</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>579</v>
+        <v>186</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>580</v>
+        <v>187</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>100</v>
@@ -5254,16 +5273,13 @@
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>203</v>
+        <v>579</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>338</v>
+        <v>580</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5271,75 +5287,78 @@
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>681</v>
+        <v>203</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>682</v>
+        <v>204</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>683</v>
+        <v>205</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F125" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="B125" s="2" t="s">
+    <row r="126" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B126" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C126" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="F125" s="14" t="s">
+      <c r="F126" s="14" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>679</v>
+        <v>452</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="F127" s="14" t="s">
-        <v>258</v>
+        <v>453</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5347,13 +5366,13 @@
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>651</v>
+        <v>679</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>100</v>
+        <v>680</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5361,10 +5380,10 @@
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>100</v>
@@ -5375,27 +5394,27 @@
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>574</v>
+        <v>653</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>575</v>
+        <v>654</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>649</v>
+        <v>574</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>99</v>
+        <v>575</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
@@ -5403,30 +5422,27 @@
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>598</v>
+        <v>649</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>596</v>
+        <v>650</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>736</v>
+        <v>598</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>738</v>
+        <v>599</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>596</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>99</v>
@@ -5437,13 +5453,16 @@
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>825</v>
+        <v>736</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>100</v>
+        <v>737</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5451,110 +5470,110 @@
         <v>43</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C136" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="F135" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="17" t="s">
+      <c r="F136" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B136" s="17" t="s">
+      <c r="B137" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="C136" s="17" t="s">
+      <c r="C137" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D136" s="17" t="s">
+      <c r="D137" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="E136" s="17"/>
-      <c r="F136" s="21" t="s">
+      <c r="E137" s="17"/>
+      <c r="F137" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="G136" s="17" t="s">
+      <c r="G137" s="17" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A137" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>631</v>
+        <v>705</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>631</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>418</v>
+        <v>271</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>183</v>
+        <v>418</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>100</v>
+        <v>419</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
@@ -5562,69 +5581,69 @@
         <v>275</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="17" t="s">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A143" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B143" s="17" t="s">
+      <c r="B143" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="B144" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C143" s="17" t="s">
+      <c r="C144" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="D143" s="17"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="20" t="s">
+      <c r="D144" s="17"/>
+      <c r="E144" s="17"/>
+      <c r="F144" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G143" s="17"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A144" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G144" s="17"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>794</v>
+        <v>471</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+        <v>472</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>101</v>
@@ -5635,10 +5654,10 @@
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>101</v>
@@ -5649,16 +5668,13 @@
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>473</v>
+        <v>796</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F148" s="3" t="s">
-        <v>99</v>
+        <v>799</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
@@ -5666,69 +5682,72 @@
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>380</v>
+        <v>473</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>381</v>
+        <v>474</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>475</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>56</v>
+        <v>380</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>268</v>
+        <v>381</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>313</v>
+        <v>56</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>783</v>
+        <v>313</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>784</v>
+        <v>314</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>629</v>
+        <v>783</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>630</v>
+        <v>784</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>101</v>
@@ -5739,13 +5758,10 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>526</v>
+        <v>629</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>527</v>
+        <v>630</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>101</v>
@@ -5756,10 +5772,13 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>800</v>
+        <v>526</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>785</v>
+        <v>801</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>101</v>
@@ -5770,13 +5789,13 @@
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>543</v>
+        <v>800</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>99</v>
+        <v>785</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -5784,61 +5803,58 @@
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>607</v>
+        <v>543</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F157" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>544</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>57</v>
+        <v>607</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+        <v>608</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>311</v>
+        <v>57</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>390</v>
+        <v>311</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F160" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>396</v>
+        <v>312</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5846,16 +5862,16 @@
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F161" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5863,129 +5879,132 @@
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F162" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>58</v>
+        <v>392</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+      <c r="F163" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>376</v>
+        <v>58</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>340</v>
+        <v>61</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B166" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C166" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="F165" s="3" t="s">
+      <c r="F166" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="166" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="17" t="s">
+    <row r="167" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B166" s="17" t="s">
+      <c r="B167" s="17" t="s">
         <v>441</v>
       </c>
-      <c r="C166" s="17" t="s">
+      <c r="C167" s="17" t="s">
         <v>442</v>
       </c>
-      <c r="F166" s="22" t="s">
+      <c r="F167" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G166" s="17" t="s">
+      <c r="G167" s="17" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A167" s="2" t="s">
+    <row r="168" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A168" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B168" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C168" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="D168" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="F167" s="3" t="s">
+      <c r="F168" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="168" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="17" t="s">
+    <row r="169" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A169" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="B168" s="17" t="s">
+      <c r="B169" s="17" t="s">
         <v>759</v>
       </c>
-      <c r="C168" s="17" t="s">
+      <c r="C169" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="D168" s="17" t="s">
+      <c r="D169" s="17" t="s">
         <v>761</v>
       </c>
-      <c r="F168" s="19" t="s">
+      <c r="F169" s="19" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A169" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
@@ -5993,13 +6012,13 @@
         <v>357</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F170" s="4" t="s">
-        <v>100</v>
+        <v>366</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
@@ -6007,27 +6026,24 @@
         <v>357</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>100</v>
@@ -6038,45 +6054,47 @@
         <v>357</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>370</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>816</v>
+        <v>364</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F175" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="G175" s="2" t="s">
-        <v>818</v>
+        <v>374</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6084,64 +6102,62 @@
         <v>357</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F176" s="6"/>
+      <c r="G176" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A177" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C176" s="2" t="s">
+      <c r="C177" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="F176" s="6" t="s">
+      <c r="F177" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G176" s="2" t="s">
+      <c r="G177" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="17" t="s">
+    <row r="178" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A178" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B177" s="17" t="s">
+      <c r="B178" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="C177" s="17" t="s">
+      <c r="C178" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="D177" s="17"/>
-      <c r="E177" s="17"/>
-      <c r="F177" s="20" t="s">
+      <c r="D178" s="17"/>
+      <c r="E178" s="17"/>
+      <c r="F178" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G177" s="17"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A178" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F178" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G178" s="17"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>519</v>
+        <v>206</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F179" s="14" t="s">
-        <v>400</v>
+        <v>207</v>
+      </c>
+      <c r="F179" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6149,16 +6165,16 @@
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>664</v>
+        <v>519</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>665</v>
+        <v>520</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F180" s="4" t="s">
-        <v>100</v>
+        <v>521</v>
+      </c>
+      <c r="F180" s="14" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6166,19 +6182,16 @@
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>197</v>
+        <v>664</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F181" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G181" s="2" t="s">
-        <v>339</v>
+        <v>665</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6186,13 +6199,19 @@
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>326</v>
+        <v>197</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>101</v>
+        <v>198</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F182" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6200,27 +6219,27 @@
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>64</v>
+        <v>326</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F183" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+        <v>327</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>497</v>
+        <v>64</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>101</v>
+        <v>67</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6228,16 +6247,13 @@
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>65</v>
+        <v>497</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F185" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G185" s="2" t="s">
-        <v>345</v>
+        <v>498</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
@@ -6245,13 +6261,16 @@
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>562</v>
+        <v>65</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>101</v>
+        <v>68</v>
+      </c>
+      <c r="F186" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -6259,13 +6278,13 @@
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>764</v>
+        <v>562</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="F187" s="4" t="s">
-        <v>100</v>
+        <v>563</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
@@ -6273,64 +6292,58 @@
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="F188" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>516</v>
+        <v>770</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F189" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+        <v>771</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>199</v>
+        <v>516</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F190" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>517</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>819</v>
+        <v>199</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F191" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G191" s="2" t="s">
-        <v>822</v>
+        <v>200</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6338,44 +6351,50 @@
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>66</v>
+        <v>819</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>69</v>
+        <v>820</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F192" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+        <v>821</v>
+      </c>
+      <c r="F192" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F193" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F193" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>277</v>
+        <v>190</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F194" s="5" t="s">
-        <v>101</v>
+        <v>191</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6383,10 +6402,10 @@
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>101</v>
@@ -6397,13 +6416,13 @@
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>100</v>
+        <v>281</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6411,103 +6430,100 @@
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>567</v>
+        <v>279</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F197" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>477</v>
+        <v>567</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="F198" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="17" t="s">
+    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A200" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B200" s="17" t="s">
+      <c r="B200" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A201" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B201" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="C200" s="17" t="s">
+      <c r="C201" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="D200" s="17"/>
-      <c r="E200" s="17"/>
-      <c r="F200" s="20" t="s">
+      <c r="D201" s="17"/>
+      <c r="E201" s="17"/>
+      <c r="F201" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G200" s="17"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A201" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G201" s="17"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>559</v>
+        <v>802</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>561</v>
+        <v>803</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>711</v>
+        <v>559</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>712</v>
+        <v>560</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>710</v>
+        <v>561</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>99</v>
@@ -6518,10 +6534,13 @@
         <v>420</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>428</v>
+        <v>711</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>429</v>
+        <v>712</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>710</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>99</v>
@@ -6532,10 +6551,10 @@
         <v>420</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>99</v>
@@ -6546,10 +6565,10 @@
         <v>420</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>99</v>
@@ -6560,44 +6579,44 @@
         <v>420</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>613</v>
+        <v>432</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>99</v>
@@ -6608,30 +6627,27 @@
         <v>420</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>530</v>
+        <v>422</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F211" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G211" s="2" t="s">
-        <v>532</v>
+        <v>424</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6639,48 +6655,48 @@
         <v>420</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>480</v>
+        <v>530</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F212" s="3"/>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+      <c r="F212" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>528</v>
+        <v>480</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F213" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G213" s="2" t="s">
-        <v>533</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F213" s="3"/>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>99</v>
+        <v>529</v>
+      </c>
+      <c r="F214" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
@@ -6688,13 +6704,16 @@
         <v>420</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F215" s="5" t="s">
-        <v>101</v>
+        <v>504</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
@@ -6702,10 +6721,10 @@
         <v>420</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>101</v>
@@ -6716,10 +6735,10 @@
         <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>425</v>
+        <v>468</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>101</v>
@@ -6730,10 +6749,10 @@
         <v>420</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>469</v>
+        <v>423</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>470</v>
+        <v>425</v>
       </c>
       <c r="F218" s="5" t="s">
         <v>101</v>
@@ -6744,106 +6763,106 @@
         <v>420</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>541</v>
+        <v>469</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>470</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>426</v>
+        <v>541</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F220" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>542</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B221" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F221" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A222" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B222" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="C221" s="2" t="s">
+      <c r="C222" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="F221" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="B222" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="C222" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="D222" s="17"/>
-      <c r="E222" s="17"/>
       <c r="F222" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="G222" s="17"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A223" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F223" s="5" t="s">
-        <v>101</v>
-      </c>
+    </row>
+    <row r="223" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A223" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B223" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="C223" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="D223" s="17"/>
+      <c r="E223" s="17"/>
+      <c r="F223" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G223" s="17"/>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>304</v>
+        <v>209</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F224" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>211</v>
+        <v>304</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F225" s="5" t="s">
-        <v>101</v>
+        <v>305</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F225" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6851,30 +6870,30 @@
         <v>93</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F226" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F227" s="5" t="s">
-        <v>101</v>
+        <v>214</v>
+      </c>
+      <c r="F227" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
@@ -6882,10 +6901,10 @@
         <v>93</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>101</v>
@@ -6896,128 +6915,128 @@
         <v>93</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>216</v>
+        <v>94</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F229" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B230" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A231" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="C231" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F230" s="12" t="s">
+      <c r="F231" s="12" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A231" s="17" t="s">
+    <row r="232" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A232" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B231" s="17" t="s">
+      <c r="B232" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C231" s="17" t="s">
+      <c r="C232" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D231" s="17"/>
-      <c r="E231" s="17"/>
-      <c r="F231" s="20" t="s">
+      <c r="D232" s="17"/>
+      <c r="E232" s="17"/>
+      <c r="F232" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G231" s="17"/>
-    </row>
-    <row r="232" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A232" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F232" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G232" s="2" t="s">
-        <v>331</v>
-      </c>
+      <c r="G232" s="17"/>
     </row>
     <row r="233" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>192</v>
+        <v>71</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>745</v>
+        <v>192</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>746</v>
+        <v>194</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G234" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A235" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="F235" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G235" s="2" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A235" s="17" t="s">
+    <row r="236" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A236" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B235" s="17" t="s">
+      <c r="B236" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C235" s="17" t="s">
+      <c r="C236" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="D235" s="17"/>
-      <c r="E235" s="17"/>
-      <c r="F235" s="22" t="s">
+      <c r="D236" s="17"/>
+      <c r="E236" s="17"/>
+      <c r="F236" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G235" s="17" t="s">
+      <c r="G236" s="17" t="s">
         <v>336</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A236" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F236" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -7025,13 +7044,13 @@
         <v>73</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>550</v>
+        <v>632</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>101</v>
+        <v>633</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -7039,13 +7058,13 @@
         <v>73</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>74</v>
+        <v>550</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F238" s="4" t="s">
-        <v>100</v>
+        <v>551</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
@@ -7053,41 +7072,41 @@
         <v>73</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F239" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>554</v>
+        <v>75</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>555</v>
+        <v>83</v>
       </c>
       <c r="F240" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>411</v>
+        <v>554</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F241" s="4" t="s">
-        <v>100</v>
+        <v>555</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
@@ -7095,10 +7114,10 @@
         <v>73</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>677</v>
+        <v>411</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>678</v>
+        <v>412</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>100</v>
@@ -7109,13 +7128,13 @@
         <v>73</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>552</v>
+        <v>677</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F243" s="5" t="s">
-        <v>101</v>
+        <v>678</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
@@ -7123,13 +7142,13 @@
         <v>73</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>283</v>
+        <v>552</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F244" s="3" t="s">
-        <v>99</v>
+        <v>553</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
@@ -7137,44 +7156,44 @@
         <v>73</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F246" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>804</v>
+        <v>236</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="F247" s="3" t="s">
-        <v>99</v>
+        <v>237</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
@@ -7182,13 +7201,13 @@
         <v>73</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>618</v>
+        <v>804</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F248" s="5" t="s">
-        <v>101</v>
+        <v>805</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
@@ -7196,10 +7215,10 @@
         <v>73</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>101</v>
@@ -7210,10 +7229,10 @@
         <v>73</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>232</v>
+        <v>620</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>233</v>
+        <v>621</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>101</v>
@@ -7224,10 +7243,10 @@
         <v>73</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>101</v>
@@ -7238,13 +7257,10 @@
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>634</v>
+        <v>228</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>636</v>
+        <v>229</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>101</v>
@@ -7255,10 +7271,13 @@
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>623</v>
+        <v>635</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>636</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>101</v>
@@ -7269,13 +7288,13 @@
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>823</v>
+        <v>622</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="F254" s="3" t="s">
-        <v>99</v>
+        <v>623</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
@@ -7283,10 +7302,10 @@
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>708</v>
+        <v>823</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>709</v>
+        <v>824</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>99</v>
@@ -7297,10 +7316,10 @@
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>637</v>
+        <v>708</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>638</v>
+        <v>709</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>99</v>
@@ -7311,10 +7330,10 @@
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>99</v>
@@ -7325,13 +7344,13 @@
         <v>73</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="F258" s="4" t="s">
-        <v>100</v>
+        <v>610</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
@@ -7339,44 +7358,44 @@
         <v>73</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>241</v>
+        <v>589</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>242</v>
+        <v>590</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F260" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>76</v>
+        <v>285</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F261" s="5" t="s">
-        <v>101</v>
+        <v>286</v>
+      </c>
+      <c r="F261" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
@@ -7384,10 +7403,10 @@
         <v>73</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>101</v>
@@ -7398,10 +7417,10 @@
         <v>73</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>101</v>
@@ -7412,13 +7431,13 @@
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F264" s="4" t="s">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -7426,16 +7445,13 @@
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>624</v>
+        <v>79</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="F265" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
@@ -7443,13 +7459,16 @@
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>448</v>
+        <v>624</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="F266" s="4" t="s">
-        <v>100</v>
+        <v>625</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="F266" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
@@ -7457,41 +7476,41 @@
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>639</v>
+        <v>478</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+        <v>479</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>739</v>
+        <v>639</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="F269" s="3" t="s">
-        <v>99</v>
+        <v>640</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
@@ -7499,10 +7518,10 @@
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>80</v>
+        <v>739</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>88</v>
+        <v>740</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>99</v>
@@ -7513,30 +7532,27 @@
         <v>73</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>548</v>
+        <v>80</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>293</v>
+        <v>548</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F272" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G272" s="2" t="s">
-        <v>335</v>
+        <v>549</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7544,10 +7560,10 @@
         <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F273" s="16" t="s">
         <v>303</v>
@@ -7561,10 +7577,10 @@
         <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>239</v>
+        <v>295</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="F274" s="16" t="s">
         <v>303</v>
@@ -7573,35 +7589,38 @@
         <v>335</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F275" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="F275" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>691</v>
+        <v>230</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F276" s="5" t="s">
-        <v>238</v>
+        <v>231</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7609,58 +7628,58 @@
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>81</v>
+        <v>691</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F277" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+        <v>692</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>743</v>
+        <v>81</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>744</v>
+        <v>89</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>443</v>
+        <v>743</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F279" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G279" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+        <v>744</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>641</v>
+        <v>443</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="F280" s="5" t="s">
-        <v>101</v>
+        <v>444</v>
+      </c>
+      <c r="F280" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
@@ -7668,44 +7687,44 @@
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>507</v>
+        <v>641</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>508</v>
+        <v>642</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>776</v>
+        <v>507</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F282" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G282" s="2" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+        <v>508</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>245</v>
+        <v>776</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F283" s="14" t="s">
-        <v>258</v>
+        <v>777</v>
+      </c>
+      <c r="F283" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
@@ -7713,13 +7732,13 @@
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F284" s="5" t="s">
-        <v>101</v>
+        <v>246</v>
+      </c>
+      <c r="F284" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
@@ -7727,13 +7746,13 @@
         <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>643</v>
+        <v>298</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>100</v>
+        <v>297</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
@@ -7741,13 +7760,13 @@
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>234</v>
+        <v>643</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F286" s="5" t="s">
-        <v>101</v>
+        <v>644</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -7755,10 +7774,10 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>627</v>
+        <v>234</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>628</v>
+        <v>235</v>
       </c>
       <c r="F287" s="5" t="s">
         <v>101</v>
@@ -7769,13 +7788,13 @@
         <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>226</v>
+        <v>627</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F288" s="12" t="s">
-        <v>250</v>
+        <v>628</v>
+      </c>
+      <c r="F288" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -7783,13 +7802,13 @@
         <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>524</v>
+        <v>226</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F289" s="14" t="s">
-        <v>258</v>
+        <v>227</v>
+      </c>
+      <c r="F289" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -7797,16 +7816,13 @@
         <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F290" s="5" t="s">
-        <v>101</v>
+        <v>525</v>
+      </c>
+      <c r="F290" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -7814,44 +7830,44 @@
         <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>224</v>
+        <v>522</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>225</v>
+        <v>523</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="F291" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>645</v>
+        <v>224</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="F292" s="20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="F292" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>584</v>
+        <v>645</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G293" s="2" t="s">
-        <v>587</v>
+        <v>646</v>
+      </c>
+      <c r="F293" s="20" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7859,81 +7875,81 @@
         <v>73</v>
       </c>
       <c r="B294" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G294" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A295" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="C295" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="F294" s="16" t="s">
+      <c r="F295" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="G294" s="2" t="s">
+      <c r="G295" s="2" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A295" s="17" t="s">
+    <row r="296" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A296" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B295" s="17" t="s">
+      <c r="B296" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C295" s="17" t="s">
+      <c r="C296" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D295" s="17"/>
-      <c r="E295" s="17"/>
-      <c r="F295" s="20" t="s">
+      <c r="D296" s="17"/>
+      <c r="E296" s="17"/>
+      <c r="F296" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G295" s="17"/>
-    </row>
-    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A296" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F296" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G296" s="17"/>
+    </row>
+    <row r="297" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>221</v>
+        <v>92</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>403</v>
+        <v>315</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>249</v>
+        <v>403</v>
       </c>
       <c r="F298" s="5" t="s">
         <v>101</v>
@@ -7944,27 +7960,30 @@
         <v>90</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>806</v>
+        <v>247</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="F299" s="25" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>351</v>
+        <v>806</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>100</v>
+        <v>807</v>
+      </c>
+      <c r="F300" s="25" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
@@ -7972,36 +7991,50 @@
         <v>90</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>564</v>
+        <v>351</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>566</v>
+        <v>352</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A302" s="17" t="s">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A302" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B302" s="17" t="s">
+      <c r="B302" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A303" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B303" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C302" s="17" t="s">
+      <c r="C303" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D302" s="17" t="s">
+      <c r="D303" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E302" s="17"/>
-      <c r="F302" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G302" s="17"/>
+      <c r="E303" s="17"/>
+      <c r="F303" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G303" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B03495-367A-425A-B8FF-BA60D751B3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DE3C43-F88F-45B3-93AC-4CC625C8192A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="834">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2372,15 +2372,6 @@
   </si>
   <si>
     <t>STfECCE</t>
-  </si>
-  <si>
-    <t>BUCMfNCR</t>
-  </si>
-  <si>
-    <t>Boolean Use Capacity Market for New Capacity Revenue</t>
-  </si>
-  <si>
-    <t>You wish the electricity sector to only collect capacity costs for new capacity and not pay them out to all resources in the market.</t>
   </si>
   <si>
     <t>FoICbCTBA</t>
@@ -2651,7 +2642,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2712,12 +2703,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3360,7 +3345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G303"/>
+  <dimension ref="A1:G302"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -3603,16 +3588,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4030,19 +4015,19 @@
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="F43" s="21" t="s">
         <v>303</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4181,16 +4166,16 @@
         <v>413</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -4295,108 +4280,105 @@
         <v>573</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>780</v>
+        <v>178</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>781</v>
+        <v>179</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>178</v>
+        <v>576</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>179</v>
+        <v>578</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>576</v>
+        <v>415</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>416</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>413</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>415</v>
+        <v>464</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" s="26" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="26" t="s">
+        <v>465</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="B63" s="26" t="s">
-        <v>464</v>
-      </c>
-      <c r="C63" s="26" t="s">
-        <v>465</v>
-      </c>
-      <c r="D63" s="26" t="s">
-        <v>721</v>
-      </c>
-      <c r="F63" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="G63" s="26" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="17" t="s">
-        <v>413</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>834</v>
-      </c>
-      <c r="C64" s="17" t="s">
-        <v>835</v>
-      </c>
-      <c r="D64" s="17"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="21" t="s">
+      <c r="B63" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>832</v>
+      </c>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="G64" s="17" t="s">
-        <v>836</v>
+      <c r="G63" s="17" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
@@ -4404,10 +4386,10 @@
         <v>38</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>39</v>
+        <v>201</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>41</v>
+        <v>202</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>99</v>
@@ -4418,13 +4400,13 @@
         <v>38</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>201</v>
+        <v>40</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>99</v>
+        <v>42</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -4432,46 +4414,46 @@
         <v>38</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>40</v>
+        <v>545</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>42</v>
+        <v>546</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="2" t="s">
+    <row r="68" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="F68" s="4" t="s">
+      <c r="B68" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="C69" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="D69" s="17"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G69" s="17" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
@@ -4479,27 +4461,30 @@
         <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>788</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>787</v>
+        <v>655</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>100</v>
+        <v>656</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4507,47 +4492,44 @@
         <v>43</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>655</v>
+        <v>181</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>656</v>
+        <v>722</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>723</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>181</v>
+        <v>328</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+        <v>329</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>328</v>
+        <v>603</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>99</v>
+        <v>602</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4555,13 +4537,16 @@
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>603</v>
+        <v>684</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>101</v>
+        <v>685</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4569,33 +4554,33 @@
         <v>43</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>684</v>
+        <v>175</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>175</v>
+        <v>594</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F77" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>320</v>
+        <v>595</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -4603,30 +4588,30 @@
         <v>43</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>594</v>
+        <v>44</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>99</v>
+        <v>51</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
@@ -4634,58 +4619,61 @@
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>45</v>
+        <v>752</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>51</v>
+        <v>753</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="F81" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+        <v>775</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>774</v>
+        <v>689</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>690</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>689</v>
+        <v>674</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>690</v>
+        <v>675</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>99</v>
@@ -4696,16 +4684,10 @@
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>674</v>
+        <v>826</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>203</v>
+        <v>827</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>99</v>
@@ -4716,10 +4698,10 @@
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>829</v>
+        <v>160</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>830</v>
+        <v>161</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>99</v>
@@ -4730,120 +4712,120 @@
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>160</v>
+        <v>658</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+        <v>659</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>658</v>
+        <v>46</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>659</v>
+        <v>52</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>725</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>46</v>
+        <v>726</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>726</v>
+        <v>513</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>513</v>
+        <v>787</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+        <v>788</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>790</v>
+        <v>728</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>791</v>
+        <v>729</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>762</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>728</v>
+        <v>647</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>762</v>
+        <v>648</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>647</v>
+        <v>309</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>101</v>
+        <v>310</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -4851,61 +4833,64 @@
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>309</v>
+        <v>741</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>310</v>
+        <v>742</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>741</v>
+        <v>47</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>47</v>
+        <v>288</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>171</v>
+        <v>289</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+        <v>290</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>288</v>
+        <v>660</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>289</v>
+        <v>661</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>100</v>
+        <v>730</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4913,33 +4898,33 @@
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>660</v>
+        <v>169</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>661</v>
+        <v>170</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>447</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>169</v>
+        <v>671</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>170</v>
+        <v>672</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>99</v>
+        <v>673</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -4947,16 +4932,13 @@
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>671</v>
+        <v>789</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>100</v>
+        <v>790</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4964,13 +4946,13 @@
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>792</v>
+        <v>824</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>101</v>
+        <v>825</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -4978,13 +4960,13 @@
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>827</v>
+        <v>731</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>99</v>
+        <v>732</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
@@ -4992,114 +4974,114 @@
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>731</v>
+        <v>489</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>489</v>
+        <v>177</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>177</v>
+        <v>766</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>321</v>
+        <v>768</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A106" s="2" t="s">
+      <c r="B106" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B107" s="2" t="s">
-        <v>767</v>
+        <v>713</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>714</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>733</v>
+        <v>592</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>734</v>
+        <v>593</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>100</v>
+        <v>606</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
@@ -5107,10 +5089,10 @@
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>605</v>
+        <v>750</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>606</v>
+        <v>751</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>99</v>
@@ -5121,13 +5103,13 @@
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>750</v>
+        <v>596</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>99</v>
+        <v>597</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
@@ -5135,10 +5117,10 @@
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>596</v>
+        <v>662</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>597</v>
+        <v>663</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>100</v>
@@ -5149,13 +5131,13 @@
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>662</v>
+        <v>48</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>100</v>
+        <v>53</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
@@ -5163,27 +5145,30 @@
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>48</v>
+        <v>196</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>196</v>
+        <v>49</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>100</v>
+        <v>54</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -5191,33 +5176,33 @@
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>49</v>
+        <v>755</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>54</v>
+        <v>756</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>757</v>
+        <v>749</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5225,44 +5210,41 @@
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>748</v>
+        <v>669</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>749</v>
+        <v>670</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>735</v>
+      </c>
+      <c r="F119" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>669</v>
+        <v>186</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="F120" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>186</v>
+        <v>579</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>187</v>
+        <v>580</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>100</v>
@@ -5273,13 +5255,16 @@
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>579</v>
+        <v>203</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>100</v>
+        <v>204</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5287,78 +5272,75 @@
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>203</v>
+        <v>681</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>204</v>
+        <v>682</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>205</v>
+        <v>683</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>681</v>
+        <v>600</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>682</v>
+        <v>601</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A125" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B125" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>667</v>
+        <v>452</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="F126" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>453</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>452</v>
+        <v>679</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>100</v>
+        <v>680</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5366,13 +5348,13 @@
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>679</v>
+        <v>651</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="F128" s="14" t="s">
-        <v>258</v>
+        <v>652</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5380,10 +5362,10 @@
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>100</v>
@@ -5394,27 +5376,27 @@
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>653</v>
+        <v>574</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>654</v>
+        <v>575</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>574</v>
+        <v>649</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>100</v>
+        <v>650</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
@@ -5422,27 +5404,30 @@
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>649</v>
+        <v>598</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>650</v>
+        <v>599</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>596</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>598</v>
+        <v>736</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>596</v>
+        <v>737</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>738</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>99</v>
@@ -5453,16 +5438,13 @@
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>736</v>
+        <v>822</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>99</v>
+        <v>823</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5470,110 +5452,110 @@
         <v>43</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>825</v>
+        <v>706</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="F135" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B136" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C136" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="D136" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="E136" s="17"/>
+      <c r="F136" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G136" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A137" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="F137" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B137" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="C137" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="D137" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="E137" s="17"/>
-      <c r="F137" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G137" s="17" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>705</v>
+        <v>631</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>631</v>
+        <v>272</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>271</v>
+        <v>418</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>418</v>
+        <v>183</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>101</v>
+        <v>182</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
@@ -5581,69 +5563,69 @@
         <v>275</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A143" s="2" t="s">
+    <row r="143" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F143" s="4" t="s">
+      <c r="B143" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C143" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D143" s="17"/>
+      <c r="E143" s="17"/>
+      <c r="F143" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="B144" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="C144" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="D144" s="17"/>
-      <c r="E144" s="17"/>
-      <c r="F144" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G144" s="17"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G143" s="17"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A144" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>471</v>
+        <v>791</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>794</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>101</v>
@@ -5654,10 +5636,10 @@
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>101</v>
@@ -5668,13 +5650,16 @@
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>796</v>
+        <v>473</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>101</v>
+        <v>474</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
@@ -5682,72 +5667,69 @@
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>473</v>
+        <v>380</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>380</v>
+        <v>56</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>381</v>
+        <v>59</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>268</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>56</v>
+        <v>313</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>313</v>
+        <v>780</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>314</v>
+        <v>781</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>783</v>
+        <v>629</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>784</v>
+        <v>630</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>101</v>
@@ -5758,10 +5740,13 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>629</v>
+        <v>526</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>630</v>
+        <v>798</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>101</v>
@@ -5772,13 +5757,10 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>526</v>
+        <v>797</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>527</v>
+        <v>782</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>101</v>
@@ -5789,13 +5771,13 @@
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>800</v>
+        <v>543</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>101</v>
+        <v>544</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -5803,58 +5785,61 @@
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>543</v>
+        <v>607</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+        <v>608</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>607</v>
+        <v>57</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F158" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>57</v>
+        <v>311</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>311</v>
+        <v>390</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>101</v>
+        <v>393</v>
+      </c>
+      <c r="F160" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5862,16 +5847,16 @@
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F161" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5879,132 +5864,129 @@
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F162" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>392</v>
+        <v>58</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F163" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>58</v>
+        <v>376</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>61</v>
+        <v>340</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F164" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>341</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F165" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F166" s="3" t="s">
+      <c r="B166" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="C166" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="F166" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="G166" s="17" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A167" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F167" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="167" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B167" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="C167" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="F167" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G167" s="17" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A168" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F168" s="3" t="s">
+    <row r="168" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A168" s="17" t="s">
+        <v>758</v>
+      </c>
+      <c r="B168" s="17" t="s">
+        <v>759</v>
+      </c>
+      <c r="C168" s="17" t="s">
+        <v>760</v>
+      </c>
+      <c r="D168" s="17" t="s">
+        <v>761</v>
+      </c>
+      <c r="F168" s="19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="169" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="17" t="s">
-        <v>758</v>
-      </c>
-      <c r="B169" s="17" t="s">
-        <v>759</v>
-      </c>
-      <c r="C169" s="17" t="s">
-        <v>760</v>
-      </c>
-      <c r="D169" s="17" t="s">
-        <v>761</v>
-      </c>
-      <c r="F169" s="19" t="s">
-        <v>99</v>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A169" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
@@ -6012,13 +5994,13 @@
         <v>357</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>101</v>
+        <v>367</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
@@ -6026,24 +6008,27 @@
         <v>357</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>100</v>
@@ -6054,47 +6039,45 @@
         <v>357</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F174" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+        <v>371</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>364</v>
+        <v>813</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F175" s="6" t="s">
-        <v>142</v>
-      </c>
+        <v>814</v>
+      </c>
+      <c r="F175" s="6"/>
       <c r="G175" s="2" t="s">
-        <v>374</v>
+        <v>815</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6102,62 +6085,64 @@
         <v>357</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>816</v>
+        <v>365</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F176" s="6"/>
+        <v>372</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="G176" s="2" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A177" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A177" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F177" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G177" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="B178" s="17" t="s">
+      <c r="B177" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="C178" s="17" t="s">
+      <c r="C177" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="D178" s="17"/>
-      <c r="E178" s="17"/>
-      <c r="F178" s="20" t="s">
+      <c r="D177" s="17"/>
+      <c r="E177" s="17"/>
+      <c r="F177" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G178" s="17"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G177" s="17"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A178" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>206</v>
+        <v>519</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F179" s="12" t="s">
-        <v>250</v>
+        <v>520</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F179" s="14" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6165,16 +6150,16 @@
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>519</v>
+        <v>664</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>520</v>
+        <v>665</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F180" s="14" t="s">
-        <v>400</v>
+        <v>666</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6182,16 +6167,19 @@
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>664</v>
+        <v>197</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F181" s="4" t="s">
-        <v>100</v>
+        <v>198</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F181" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6199,19 +6187,13 @@
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>197</v>
+        <v>326</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F182" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>339</v>
+        <v>327</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6219,27 +6201,27 @@
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>326</v>
+        <v>64</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>64</v>
+        <v>497</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F184" s="4" t="s">
-        <v>100</v>
+        <v>498</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6247,13 +6229,16 @@
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>497</v>
+        <v>65</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>101</v>
+        <v>68</v>
+      </c>
+      <c r="F185" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
@@ -6261,16 +6246,13 @@
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>65</v>
+        <v>562</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F186" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G186" s="2" t="s">
-        <v>345</v>
+        <v>563</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -6278,13 +6260,13 @@
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>562</v>
+        <v>764</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>101</v>
+        <v>765</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
@@ -6292,58 +6274,64 @@
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="F188" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>770</v>
+        <v>516</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F189" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>517</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>516</v>
+        <v>199</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F190" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G190" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>199</v>
+        <v>816</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F191" s="4" t="s">
-        <v>100</v>
+        <v>817</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="F191" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>819</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6351,50 +6339,44 @@
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>819</v>
+        <v>66</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>820</v>
+        <v>69</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F192" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G192" s="2" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>399</v>
+      </c>
+      <c r="F192" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F193" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>190</v>
+        <v>277</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F194" s="4" t="s">
-        <v>100</v>
+        <v>280</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6402,10 +6384,10 @@
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>101</v>
@@ -6416,13 +6398,13 @@
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F196" s="5" t="s">
-        <v>101</v>
+        <v>282</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6430,100 +6412,103 @@
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>279</v>
+        <v>567</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F197" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>567</v>
+        <v>477</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F198" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+        <v>476</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A200" s="2" t="s">
+    <row r="200" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A200" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F200" s="4" t="s">
+      <c r="B200" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="C200" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="D200" s="17"/>
+      <c r="E200" s="17"/>
+      <c r="F200" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B201" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="C201" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="D201" s="17"/>
-      <c r="E201" s="17"/>
-      <c r="F201" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G201" s="17"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G200" s="17"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A201" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>802</v>
+        <v>559</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>803</v>
+        <v>560</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>561</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>559</v>
+        <v>711</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>560</v>
+        <v>712</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>561</v>
+        <v>710</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>99</v>
@@ -6534,13 +6519,10 @@
         <v>420</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>711</v>
+        <v>428</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>710</v>
+        <v>429</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>99</v>
@@ -6551,10 +6533,10 @@
         <v>420</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>99</v>
@@ -6565,10 +6547,10 @@
         <v>420</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>430</v>
+        <v>401</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>431</v>
+        <v>402</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>99</v>
@@ -6579,44 +6561,44 @@
         <v>420</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>432</v>
+        <v>613</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>433</v>
+        <v>615</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>434</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>613</v>
+        <v>434</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>99</v>
@@ -6627,27 +6609,30 @@
         <v>420</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>422</v>
+        <v>530</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>99</v>
+        <v>531</v>
+      </c>
+      <c r="F211" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6655,48 +6640,48 @@
         <v>420</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>530</v>
+        <v>480</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F212" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G212" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>481</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F212" s="3"/>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>480</v>
+        <v>528</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F213" s="3"/>
+        <v>529</v>
+      </c>
+      <c r="F213" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>533</v>
+      </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>528</v>
+        <v>503</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F214" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G214" s="2" t="s">
-        <v>533</v>
+        <v>504</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
@@ -6704,16 +6689,13 @@
         <v>420</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F215" s="3" t="s">
-        <v>99</v>
+        <v>502</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
@@ -6721,10 +6703,10 @@
         <v>420</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>502</v>
+        <v>468</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>101</v>
@@ -6735,10 +6717,10 @@
         <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>467</v>
+        <v>423</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>468</v>
+        <v>425</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>101</v>
@@ -6749,10 +6731,10 @@
         <v>420</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>423</v>
+        <v>469</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>425</v>
+        <v>470</v>
       </c>
       <c r="F218" s="5" t="s">
         <v>101</v>
@@ -6763,106 +6745,106 @@
         <v>420</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F219" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+        <v>542</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>541</v>
+        <v>426</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F220" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>427</v>
+      </c>
+      <c r="F220" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>426</v>
+        <v>569</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F221" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G221" s="2" t="s">
-        <v>534</v>
+        <v>570</v>
+      </c>
+      <c r="F221" s="19" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="2" t="s">
+      <c r="A222" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="B222" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>570</v>
-      </c>
+      <c r="B222" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="C222" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="D222" s="17"/>
+      <c r="E222" s="17"/>
       <c r="F222" s="19" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A223" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="B223" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="C223" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="D223" s="17"/>
-      <c r="E223" s="17"/>
-      <c r="F223" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="G223" s="17"/>
+      <c r="G222" s="17"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A223" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F224" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F224" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>304</v>
+        <v>211</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F225" s="12" t="s">
-        <v>250</v>
+        <v>212</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6870,30 +6852,30 @@
         <v>93</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F226" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+      <c r="F226" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F227" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G227" s="2" t="s">
-        <v>346</v>
+        <v>220</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
@@ -6901,10 +6883,10 @@
         <v>93</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>215</v>
+        <v>94</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>101</v>
@@ -6915,128 +6897,128 @@
         <v>93</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F230" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A231" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F230" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A231" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B231" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F231" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A232" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B232" s="17" t="s">
+      <c r="B231" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C232" s="17" t="s">
+      <c r="C231" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D232" s="17"/>
-      <c r="E232" s="17"/>
-      <c r="F232" s="20" t="s">
+      <c r="D231" s="17"/>
+      <c r="E231" s="17"/>
+      <c r="F231" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G232" s="17"/>
+      <c r="G231" s="17"/>
+    </row>
+    <row r="232" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A232" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="233" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>192</v>
+        <v>745</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>194</v>
+        <v>746</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A235" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A235" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B235" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="F235" s="6" t="s">
+      <c r="B235" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C235" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D235" s="17"/>
+      <c r="E235" s="17"/>
+      <c r="F235" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G235" s="2" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A236" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B236" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C236" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="D236" s="17"/>
-      <c r="E236" s="17"/>
-      <c r="F236" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G236" s="17" t="s">
+      <c r="G235" s="17" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A236" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -7044,13 +7026,13 @@
         <v>73</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>632</v>
+        <v>550</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F237" s="4" t="s">
-        <v>100</v>
+        <v>551</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -7058,13 +7040,13 @@
         <v>73</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>550</v>
+        <v>74</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F238" s="5" t="s">
-        <v>101</v>
+        <v>82</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
@@ -7072,41 +7054,41 @@
         <v>73</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F239" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>75</v>
+        <v>554</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>83</v>
+        <v>555</v>
       </c>
       <c r="F240" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>554</v>
+        <v>411</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F241" s="5" t="s">
-        <v>101</v>
+        <v>412</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
@@ -7114,10 +7096,10 @@
         <v>73</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>411</v>
+        <v>677</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>412</v>
+        <v>678</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>100</v>
@@ -7128,13 +7110,13 @@
         <v>73</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>677</v>
+        <v>552</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F243" s="4" t="s">
-        <v>100</v>
+        <v>553</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
@@ -7142,13 +7124,13 @@
         <v>73</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>552</v>
+        <v>283</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F244" s="5" t="s">
-        <v>101</v>
+        <v>284</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
@@ -7156,44 +7138,44 @@
         <v>73</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F246" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>236</v>
+        <v>801</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F247" s="5" t="s">
-        <v>101</v>
+        <v>802</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
@@ -7201,13 +7183,13 @@
         <v>73</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>804</v>
+        <v>618</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="F248" s="3" t="s">
-        <v>99</v>
+        <v>619</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
@@ -7215,10 +7197,10 @@
         <v>73</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>101</v>
@@ -7229,10 +7211,10 @@
         <v>73</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>620</v>
+        <v>232</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>621</v>
+        <v>233</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>101</v>
@@ -7243,10 +7225,10 @@
         <v>73</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>101</v>
@@ -7257,10 +7239,13 @@
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>228</v>
+        <v>634</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>229</v>
+        <v>635</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>636</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>101</v>
@@ -7271,13 +7256,10 @@
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>101</v>
@@ -7288,13 +7270,13 @@
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>622</v>
+        <v>820</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F254" s="5" t="s">
-        <v>101</v>
+        <v>821</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
@@ -7302,10 +7284,10 @@
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>823</v>
+        <v>708</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>824</v>
+        <v>709</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>99</v>
@@ -7316,10 +7298,10 @@
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>708</v>
+        <v>637</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>709</v>
+        <v>638</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>99</v>
@@ -7330,10 +7312,10 @@
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>638</v>
+        <v>610</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>99</v>
@@ -7344,13 +7326,13 @@
         <v>73</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>99</v>
+        <v>590</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
@@ -7358,44 +7340,44 @@
         <v>73</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>589</v>
+        <v>241</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>590</v>
+        <v>242</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F260" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="F260" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F261" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G261" s="2" t="s">
-        <v>334</v>
+        <v>84</v>
+      </c>
+      <c r="F261" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
@@ -7403,10 +7385,10 @@
         <v>73</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>101</v>
@@ -7417,10 +7399,10 @@
         <v>73</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>101</v>
@@ -7431,13 +7413,13 @@
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F264" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -7445,13 +7427,16 @@
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>79</v>
+        <v>624</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F265" s="4" t="s">
-        <v>100</v>
+        <v>625</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
@@ -7459,16 +7444,13 @@
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>624</v>
+        <v>448</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="F266" s="5" t="s">
-        <v>101</v>
+        <v>449</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
@@ -7476,41 +7458,41 @@
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>478</v>
+        <v>639</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="F268" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>640</v>
+      </c>
+      <c r="F268" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>639</v>
+        <v>739</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="F269" s="5" t="s">
-        <v>101</v>
+        <v>740</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
@@ -7518,10 +7500,10 @@
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>739</v>
+        <v>80</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>740</v>
+        <v>88</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>99</v>
@@ -7532,27 +7514,30 @@
         <v>73</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>80</v>
+        <v>548</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F271" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+        <v>549</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>548</v>
+        <v>293</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F272" s="5" t="s">
-        <v>101</v>
+        <v>294</v>
+      </c>
+      <c r="F272" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G272" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7560,10 +7545,10 @@
         <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F273" s="16" t="s">
         <v>303</v>
@@ -7577,10 +7562,10 @@
         <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="F274" s="16" t="s">
         <v>303</v>
@@ -7589,38 +7574,35 @@
         <v>335</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F275" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G275" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>230</v>
+        <v>691</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F276" s="4" t="s">
-        <v>100</v>
+        <v>692</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7628,58 +7610,58 @@
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>691</v>
+        <v>81</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F277" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>81</v>
+        <v>743</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>89</v>
+        <v>744</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>743</v>
+        <v>443</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="F279" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>444</v>
+      </c>
+      <c r="F279" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>443</v>
+        <v>641</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F280" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G280" s="2" t="s">
-        <v>377</v>
+        <v>642</v>
+      </c>
+      <c r="F280" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
@@ -7687,44 +7669,44 @@
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>641</v>
+        <v>507</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>642</v>
+        <v>508</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>507</v>
+        <v>776</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F282" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>777</v>
+      </c>
+      <c r="F282" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>776</v>
+        <v>245</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F283" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G283" s="2" t="s">
-        <v>778</v>
+        <v>246</v>
+      </c>
+      <c r="F283" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
@@ -7732,13 +7714,13 @@
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>245</v>
+        <v>298</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F284" s="14" t="s">
-        <v>258</v>
+        <v>297</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
@@ -7746,13 +7728,13 @@
         <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>298</v>
+        <v>643</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F285" s="5" t="s">
-        <v>101</v>
+        <v>644</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
@@ -7760,13 +7742,13 @@
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>643</v>
+        <v>234</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F286" s="4" t="s">
-        <v>100</v>
+        <v>235</v>
+      </c>
+      <c r="F286" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -7774,10 +7756,10 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>234</v>
+        <v>627</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>235</v>
+        <v>628</v>
       </c>
       <c r="F287" s="5" t="s">
         <v>101</v>
@@ -7788,13 +7770,13 @@
         <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>627</v>
+        <v>226</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="F288" s="5" t="s">
-        <v>101</v>
+        <v>227</v>
+      </c>
+      <c r="F288" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -7802,13 +7784,13 @@
         <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>226</v>
+        <v>524</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F289" s="12" t="s">
-        <v>250</v>
+        <v>525</v>
+      </c>
+      <c r="F289" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -7816,13 +7798,16 @@
         <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F290" s="14" t="s">
-        <v>258</v>
+        <v>523</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -7830,44 +7815,44 @@
         <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>522</v>
+        <v>224</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F291" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>224</v>
+        <v>645</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F292" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>646</v>
+      </c>
+      <c r="F292" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>645</v>
+        <v>584</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="F293" s="20" t="s">
-        <v>100</v>
+        <v>586</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7875,81 +7860,81 @@
         <v>73</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F294" s="3" t="s">
-        <v>99</v>
+        <v>588</v>
+      </c>
+      <c r="F294" s="16" t="s">
+        <v>303</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A295" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A295" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B295" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F295" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G295" s="2" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A296" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B296" s="17" t="s">
+      <c r="B295" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C296" s="17" t="s">
+      <c r="C295" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D296" s="17"/>
-      <c r="E296" s="17"/>
-      <c r="F296" s="20" t="s">
+      <c r="D295" s="17"/>
+      <c r="E295" s="17"/>
+      <c r="F295" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G296" s="17"/>
-    </row>
-    <row r="297" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G295" s="17"/>
+    </row>
+    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A296" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F296" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>91</v>
+        <v>222</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>315</v>
+        <v>403</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>403</v>
+        <v>249</v>
       </c>
       <c r="F298" s="5" t="s">
         <v>101</v>
@@ -7960,30 +7945,27 @@
         <v>90</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>247</v>
+        <v>803</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D299" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F299" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>804</v>
+      </c>
+      <c r="F299" s="25" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>806</v>
+        <v>351</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="F300" s="25" t="s">
-        <v>808</v>
+        <v>352</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
@@ -7991,50 +7973,36 @@
         <v>90</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>351</v>
+        <v>564</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>352</v>
+        <v>565</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>566</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A302" s="2" t="s">
+    <row r="302" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A302" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B302" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D302" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F302" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A303" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B303" s="17" t="s">
+      <c r="B302" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C303" s="17" t="s">
+      <c r="C302" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D303" s="17" t="s">
+      <c r="D302" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E303" s="17"/>
-      <c r="F303" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G303" s="17"/>
+      <c r="E302" s="17"/>
+      <c r="F302" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G302" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DE3C43-F88F-45B3-93AC-4CC625C8192A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A8D342-CF64-453A-BCA2-30B4659ED6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="832">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2399,12 +2399,6 @@
   </si>
   <si>
     <t>Cap Ret per Unit Net Loss</t>
-  </si>
-  <si>
-    <t>ESUfRaLCD</t>
-  </si>
-  <si>
-    <t>Elec Sources Used for Rlbty and Lst Cst Dsptch</t>
   </si>
   <si>
     <t>BFoICbCTBA</t>
@@ -3345,7 +3339,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G302"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -3588,16 +3582,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4015,19 +4009,19 @@
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>809</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>811</v>
       </c>
       <c r="F43" s="21" t="s">
         <v>303</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4166,16 +4160,16 @@
         <v>413</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -4353,10 +4347,10 @@
         <v>413</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D63" s="17"/>
       <c r="E63" s="17"/>
@@ -4364,7 +4358,7 @@
         <v>303</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -4684,10 +4678,10 @@
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>99</v>
@@ -4932,13 +4926,13 @@
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>789</v>
+        <v>822</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>101</v>
+        <v>823</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4946,13 +4940,13 @@
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>824</v>
+        <v>731</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>99</v>
+        <v>732</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -4960,114 +4954,114 @@
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>731</v>
+        <v>489</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>489</v>
+        <v>177</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>177</v>
+        <v>766</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>321</v>
+        <v>768</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105" s="2" t="s">
+      <c r="B105" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B106" s="2" t="s">
-        <v>767</v>
+        <v>713</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>714</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>733</v>
+        <v>592</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>734</v>
+        <v>593</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>100</v>
+        <v>606</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
@@ -5075,10 +5069,10 @@
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>605</v>
+        <v>750</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>606</v>
+        <v>751</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>99</v>
@@ -5089,13 +5083,13 @@
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>750</v>
+        <v>596</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>99</v>
+        <v>597</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
@@ -5103,10 +5097,10 @@
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>596</v>
+        <v>662</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>597</v>
+        <v>663</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>100</v>
@@ -5117,13 +5111,13 @@
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>662</v>
+        <v>48</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>100</v>
+        <v>53</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
@@ -5131,27 +5125,30 @@
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>48</v>
+        <v>196</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>196</v>
+        <v>49</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>100</v>
+        <v>54</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -5159,33 +5156,33 @@
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>49</v>
+        <v>755</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>54</v>
+        <v>756</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>757</v>
+        <v>749</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5193,44 +5190,41 @@
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>748</v>
+        <v>669</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>749</v>
+        <v>670</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>735</v>
+      </c>
+      <c r="F118" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>669</v>
+        <v>186</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="F119" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>186</v>
+        <v>579</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>187</v>
+        <v>580</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>100</v>
@@ -5241,13 +5235,16 @@
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>579</v>
+        <v>203</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>100</v>
+        <v>204</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5255,78 +5252,75 @@
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>203</v>
+        <v>681</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>204</v>
+        <v>682</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>205</v>
+        <v>683</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>681</v>
+        <v>600</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>682</v>
+        <v>601</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A124" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B124" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="F124" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B125" s="2" t="s">
-        <v>667</v>
+        <v>452</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="F125" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>453</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>452</v>
+        <v>679</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>100</v>
+        <v>680</v>
+      </c>
+      <c r="F126" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5334,13 +5328,13 @@
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>679</v>
+        <v>651</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="F127" s="14" t="s">
-        <v>258</v>
+        <v>652</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5348,10 +5342,10 @@
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>100</v>
@@ -5362,27 +5356,27 @@
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>653</v>
+        <v>574</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>654</v>
+        <v>575</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>574</v>
+        <v>649</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>100</v>
+        <v>650</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
@@ -5390,27 +5384,30 @@
         <v>43</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>649</v>
+        <v>598</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>650</v>
+        <v>599</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>596</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>598</v>
+        <v>736</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>596</v>
+        <v>737</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>738</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>99</v>
@@ -5421,16 +5418,13 @@
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>736</v>
+        <v>820</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="F133" s="3" t="s">
-        <v>99</v>
+        <v>821</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5438,110 +5432,110 @@
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>822</v>
+        <v>706</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F134" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B135" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C135" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="D135" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="E135" s="17"/>
+      <c r="F135" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G135" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A136" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="F136" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B136" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="C136" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="D136" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="E136" s="17"/>
-      <c r="F136" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G136" s="17" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>705</v>
+        <v>631</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>631</v>
+        <v>272</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>271</v>
+        <v>418</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>418</v>
+        <v>183</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>101</v>
+        <v>182</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
@@ -5549,69 +5543,69 @@
         <v>275</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A142" s="2" t="s">
+    <row r="142" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F142" s="4" t="s">
+      <c r="B142" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C142" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D142" s="17"/>
+      <c r="E142" s="17"/>
+      <c r="F142" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="B143" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="C143" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="D143" s="17"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G143" s="17"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G142" s="17"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A143" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>471</v>
+        <v>789</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>792</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>101</v>
@@ -5622,10 +5616,10 @@
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>101</v>
@@ -5636,13 +5630,16 @@
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>793</v>
+        <v>473</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>101</v>
+        <v>474</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
@@ -5650,72 +5647,69 @@
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>473</v>
+        <v>380</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>380</v>
+        <v>56</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>381</v>
+        <v>59</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>268</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>56</v>
+        <v>313</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>313</v>
+        <v>780</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>314</v>
+        <v>781</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>780</v>
+        <v>629</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>781</v>
+        <v>630</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>101</v>
@@ -5726,10 +5720,13 @@
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>629</v>
+        <v>526</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>630</v>
+        <v>796</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>101</v>
@@ -5740,13 +5737,10 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>526</v>
+        <v>795</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>527</v>
+        <v>782</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>101</v>
@@ -5757,13 +5751,13 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>797</v>
+        <v>543</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>101</v>
+        <v>544</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
@@ -5771,58 +5765,61 @@
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>543</v>
+        <v>607</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+        <v>608</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>607</v>
+        <v>57</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F157" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>57</v>
+        <v>311</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>311</v>
+        <v>390</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>101</v>
+        <v>393</v>
+      </c>
+      <c r="F159" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5830,16 +5827,16 @@
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F160" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5847,132 +5844,129 @@
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F161" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>392</v>
+        <v>58</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F162" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G162" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>58</v>
+        <v>376</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>61</v>
+        <v>340</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>341</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A165" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F165" s="3" t="s">
+      <c r="B165" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="C165" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="F165" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="G165" s="17" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A166" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F166" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="166" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B166" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="C166" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="F166" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G166" s="17" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A167" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F167" s="3" t="s">
+    <row r="167" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="17" t="s">
+        <v>758</v>
+      </c>
+      <c r="B167" s="17" t="s">
+        <v>759</v>
+      </c>
+      <c r="C167" s="17" t="s">
+        <v>760</v>
+      </c>
+      <c r="D167" s="17" t="s">
+        <v>761</v>
+      </c>
+      <c r="F167" s="19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="168" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="17" t="s">
-        <v>758</v>
-      </c>
-      <c r="B168" s="17" t="s">
-        <v>759</v>
-      </c>
-      <c r="C168" s="17" t="s">
-        <v>760</v>
-      </c>
-      <c r="D168" s="17" t="s">
-        <v>761</v>
-      </c>
-      <c r="F168" s="19" t="s">
-        <v>99</v>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A168" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
@@ -5980,13 +5974,13 @@
         <v>357</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>101</v>
+        <v>367</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
@@ -5994,24 +5988,27 @@
         <v>357</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>100</v>
@@ -6022,47 +6019,45 @@
         <v>357</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F173" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+        <v>371</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>364</v>
+        <v>811</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>142</v>
-      </c>
+        <v>812</v>
+      </c>
+      <c r="F174" s="6"/>
       <c r="G174" s="2" t="s">
-        <v>374</v>
+        <v>813</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6070,62 +6065,64 @@
         <v>357</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>813</v>
+        <v>365</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F175" s="6"/>
+        <v>372</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="G175" s="2" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A176" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A176" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F176" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G176" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="B177" s="17" t="s">
+      <c r="B176" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="C177" s="17" t="s">
+      <c r="C176" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="D177" s="17"/>
-      <c r="E177" s="17"/>
-      <c r="F177" s="20" t="s">
+      <c r="D176" s="17"/>
+      <c r="E176" s="17"/>
+      <c r="F176" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G177" s="17"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G176" s="17"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A177" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>206</v>
+        <v>519</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F178" s="12" t="s">
-        <v>250</v>
+        <v>520</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F178" s="14" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6133,16 +6130,16 @@
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>519</v>
+        <v>664</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>520</v>
+        <v>665</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F179" s="14" t="s">
-        <v>400</v>
+        <v>666</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6150,16 +6147,19 @@
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>664</v>
+        <v>197</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F180" s="4" t="s">
-        <v>100</v>
+        <v>198</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F180" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6167,19 +6167,13 @@
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>197</v>
+        <v>326</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F181" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G181" s="2" t="s">
-        <v>339</v>
+        <v>327</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6187,27 +6181,27 @@
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>326</v>
+        <v>64</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>64</v>
+        <v>497</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F183" s="4" t="s">
-        <v>100</v>
+        <v>498</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
@@ -6215,13 +6209,16 @@
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>497</v>
+        <v>65</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>101</v>
+        <v>68</v>
+      </c>
+      <c r="F184" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6229,16 +6226,13 @@
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>65</v>
+        <v>562</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F185" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G185" s="2" t="s">
-        <v>345</v>
+        <v>563</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
@@ -6246,13 +6240,13 @@
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>562</v>
+        <v>764</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>101</v>
+        <v>765</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -6260,58 +6254,64 @@
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="F187" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>770</v>
+        <v>516</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F188" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>517</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>516</v>
+        <v>199</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F189" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>199</v>
+        <v>814</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F190" s="4" t="s">
-        <v>100</v>
+        <v>815</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="F190" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>817</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6319,50 +6319,44 @@
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>816</v>
+        <v>66</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>817</v>
+        <v>69</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="F191" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G191" s="2" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>399</v>
+      </c>
+      <c r="F191" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F192" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>190</v>
+        <v>277</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F193" s="4" t="s">
-        <v>100</v>
+        <v>280</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6370,10 +6364,10 @@
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F194" s="5" t="s">
         <v>101</v>
@@ -6384,13 +6378,13 @@
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F195" s="5" t="s">
-        <v>101</v>
+        <v>282</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6398,100 +6392,103 @@
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>279</v>
+        <v>567</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>567</v>
+        <v>477</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F197" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+        <v>476</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A199" s="2" t="s">
+    <row r="199" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A199" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F199" s="4" t="s">
+      <c r="B199" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="C199" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="D199" s="17"/>
+      <c r="E199" s="17"/>
+      <c r="F199" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B200" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="C200" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="D200" s="17"/>
-      <c r="E200" s="17"/>
-      <c r="F200" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G200" s="17"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G199" s="17"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A200" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>799</v>
+        <v>559</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>800</v>
+        <v>560</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>561</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>559</v>
+        <v>711</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>560</v>
+        <v>712</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>561</v>
+        <v>710</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>99</v>
@@ -6502,13 +6499,10 @@
         <v>420</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>711</v>
+        <v>428</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>710</v>
+        <v>429</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>99</v>
@@ -6519,10 +6513,10 @@
         <v>420</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>99</v>
@@ -6533,10 +6527,10 @@
         <v>420</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>430</v>
+        <v>401</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>431</v>
+        <v>402</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>99</v>
@@ -6547,44 +6541,44 @@
         <v>420</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>432</v>
+        <v>613</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>433</v>
+        <v>615</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>434</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>613</v>
+        <v>434</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>99</v>
@@ -6595,27 +6589,30 @@
         <v>420</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>422</v>
+        <v>530</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F210" s="3" t="s">
-        <v>99</v>
+        <v>531</v>
+      </c>
+      <c r="F210" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6623,48 +6620,48 @@
         <v>420</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>530</v>
+        <v>480</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F211" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G211" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>481</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F211" s="3"/>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>480</v>
+        <v>528</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F212" s="3"/>
+        <v>529</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>533</v>
+      </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>528</v>
+        <v>503</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F213" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G213" s="2" t="s">
-        <v>533</v>
+        <v>504</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
@@ -6672,16 +6669,13 @@
         <v>420</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>99</v>
+        <v>502</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
@@ -6689,10 +6683,10 @@
         <v>420</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>502</v>
+        <v>468</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>101</v>
@@ -6703,10 +6697,10 @@
         <v>420</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>467</v>
+        <v>423</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>468</v>
+        <v>425</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>101</v>
@@ -6717,10 +6711,10 @@
         <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>423</v>
+        <v>469</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>425</v>
+        <v>470</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>101</v>
@@ -6731,106 +6725,106 @@
         <v>420</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>469</v>
+        <v>541</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F218" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+        <v>542</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>541</v>
+        <v>426</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>427</v>
+      </c>
+      <c r="F219" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>426</v>
+        <v>569</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F220" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>534</v>
+        <v>570</v>
+      </c>
+      <c r="F220" s="19" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="221" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="2" t="s">
+      <c r="A221" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>570</v>
-      </c>
+      <c r="B221" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="C221" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="D221" s="17"/>
+      <c r="E221" s="17"/>
       <c r="F221" s="19" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A222" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="B222" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="C222" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="D222" s="17"/>
-      <c r="E222" s="17"/>
-      <c r="F222" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="G222" s="17"/>
+      <c r="G221" s="17"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A222" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F222" s="5" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F223" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>304</v>
+        <v>211</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F224" s="12" t="s">
-        <v>250</v>
+        <v>212</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6838,30 +6832,30 @@
         <v>93</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F225" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+      <c r="F225" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F226" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>346</v>
+        <v>220</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
@@ -6869,10 +6863,10 @@
         <v>93</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>215</v>
+        <v>94</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="F227" s="5" t="s">
         <v>101</v>
@@ -6883,128 +6877,128 @@
         <v>93</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F228" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F229" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A230" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F229" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A230" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F230" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A231" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B231" s="17" t="s">
+      <c r="B230" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C231" s="17" t="s">
+      <c r="C230" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D231" s="17"/>
-      <c r="E231" s="17"/>
-      <c r="F231" s="20" t="s">
+      <c r="D230" s="17"/>
+      <c r="E230" s="17"/>
+      <c r="F230" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G231" s="17"/>
+      <c r="G230" s="17"/>
+    </row>
+    <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A231" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F231" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="232" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="F232" s="6" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>192</v>
+        <v>745</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>194</v>
+        <v>746</v>
       </c>
       <c r="F233" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A234" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A234" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B234" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="F234" s="6" t="s">
+      <c r="B234" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C234" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D234" s="17"/>
+      <c r="E234" s="17"/>
+      <c r="F234" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G234" s="2" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A235" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B235" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C235" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="D235" s="17"/>
-      <c r="E235" s="17"/>
-      <c r="F235" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G235" s="17" t="s">
+      <c r="G234" s="17" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A235" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
@@ -7012,13 +7006,13 @@
         <v>73</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>632</v>
+        <v>550</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F236" s="4" t="s">
-        <v>100</v>
+        <v>551</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -7026,13 +7020,13 @@
         <v>73</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>550</v>
+        <v>74</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>101</v>
+        <v>82</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -7040,41 +7034,41 @@
         <v>73</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F238" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>75</v>
+        <v>554</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>83</v>
+        <v>555</v>
       </c>
       <c r="F239" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>554</v>
+        <v>411</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F240" s="5" t="s">
-        <v>101</v>
+        <v>412</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.35">
@@ -7082,10 +7076,10 @@
         <v>73</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>411</v>
+        <v>677</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>412</v>
+        <v>678</v>
       </c>
       <c r="F241" s="4" t="s">
         <v>100</v>
@@ -7096,13 +7090,13 @@
         <v>73</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>677</v>
+        <v>552</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F242" s="4" t="s">
-        <v>100</v>
+        <v>553</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
@@ -7110,13 +7104,13 @@
         <v>73</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>552</v>
+        <v>283</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F243" s="5" t="s">
-        <v>101</v>
+        <v>284</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
@@ -7124,44 +7118,44 @@
         <v>73</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F245" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>236</v>
+        <v>799</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F246" s="5" t="s">
-        <v>101</v>
+        <v>800</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
@@ -7169,13 +7163,13 @@
         <v>73</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>801</v>
+        <v>618</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="F247" s="3" t="s">
-        <v>99</v>
+        <v>619</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
@@ -7183,10 +7177,10 @@
         <v>73</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F248" s="5" t="s">
         <v>101</v>
@@ -7197,10 +7191,10 @@
         <v>73</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>620</v>
+        <v>232</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>621</v>
+        <v>233</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>101</v>
@@ -7211,10 +7205,10 @@
         <v>73</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>101</v>
@@ -7225,10 +7219,13 @@
         <v>73</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>228</v>
+        <v>634</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>229</v>
+        <v>635</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>636</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>101</v>
@@ -7239,13 +7236,10 @@
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>101</v>
@@ -7256,13 +7250,13 @@
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>622</v>
+        <v>818</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F253" s="5" t="s">
-        <v>101</v>
+        <v>819</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
@@ -7270,10 +7264,10 @@
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>820</v>
+        <v>708</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>821</v>
+        <v>709</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>99</v>
@@ -7284,10 +7278,10 @@
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>708</v>
+        <v>637</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>709</v>
+        <v>638</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>99</v>
@@ -7298,10 +7292,10 @@
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>638</v>
+        <v>610</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>99</v>
@@ -7312,13 +7306,13 @@
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="F257" s="3" t="s">
-        <v>99</v>
+        <v>590</v>
+      </c>
+      <c r="F257" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
@@ -7326,44 +7320,44 @@
         <v>73</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>589</v>
+        <v>241</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>590</v>
+        <v>242</v>
       </c>
       <c r="F258" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F259" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="F259" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F260" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>334</v>
+        <v>84</v>
+      </c>
+      <c r="F260" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
@@ -7371,10 +7365,10 @@
         <v>73</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>101</v>
@@ -7385,10 +7379,10 @@
         <v>73</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>101</v>
@@ -7399,13 +7393,13 @@
         <v>73</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F263" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
@@ -7413,13 +7407,16 @@
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>79</v>
+        <v>624</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F264" s="4" t="s">
-        <v>100</v>
+        <v>625</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -7427,16 +7424,13 @@
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>624</v>
+        <v>448</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="F265" s="5" t="s">
-        <v>101</v>
+        <v>449</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
@@ -7444,41 +7438,41 @@
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>478</v>
+        <v>639</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="F267" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>640</v>
+      </c>
+      <c r="F267" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>639</v>
+        <v>739</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>101</v>
+        <v>740</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
@@ -7486,10 +7480,10 @@
         <v>73</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>739</v>
+        <v>80</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>740</v>
+        <v>88</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>99</v>
@@ -7500,27 +7494,30 @@
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>80</v>
+        <v>548</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F270" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+        <v>549</v>
+      </c>
+      <c r="F270" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>548</v>
+        <v>293</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>101</v>
+        <v>294</v>
+      </c>
+      <c r="F271" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="272" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7528,10 +7525,10 @@
         <v>73</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F272" s="16" t="s">
         <v>303</v>
@@ -7545,10 +7542,10 @@
         <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="F273" s="16" t="s">
         <v>303</v>
@@ -7557,38 +7554,35 @@
         <v>335</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F274" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G274" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>230</v>
+        <v>691</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F275" s="4" t="s">
-        <v>100</v>
+        <v>692</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7596,58 +7590,58 @@
         <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>691</v>
+        <v>81</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F276" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>81</v>
+        <v>743</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>89</v>
+        <v>744</v>
       </c>
       <c r="F277" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>743</v>
+        <v>443</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="F278" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>444</v>
+      </c>
+      <c r="F278" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G278" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>443</v>
+        <v>641</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F279" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G279" s="2" t="s">
-        <v>377</v>
+        <v>642</v>
+      </c>
+      <c r="F279" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
@@ -7655,44 +7649,44 @@
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>641</v>
+        <v>507</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>642</v>
+        <v>508</v>
       </c>
       <c r="F280" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>507</v>
+        <v>776</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F281" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>777</v>
+      </c>
+      <c r="F281" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G281" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>776</v>
+        <v>245</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F282" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G282" s="2" t="s">
-        <v>778</v>
+        <v>246</v>
+      </c>
+      <c r="F282" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
@@ -7700,13 +7694,13 @@
         <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>245</v>
+        <v>298</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F283" s="14" t="s">
-        <v>258</v>
+        <v>297</v>
+      </c>
+      <c r="F283" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
@@ -7714,13 +7708,13 @@
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>298</v>
+        <v>643</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F284" s="5" t="s">
-        <v>101</v>
+        <v>644</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
@@ -7728,13 +7722,13 @@
         <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>643</v>
+        <v>234</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>100</v>
+        <v>235</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
@@ -7742,10 +7736,10 @@
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>234</v>
+        <v>627</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>235</v>
+        <v>628</v>
       </c>
       <c r="F286" s="5" t="s">
         <v>101</v>
@@ -7756,13 +7750,13 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>627</v>
+        <v>226</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="F287" s="5" t="s">
-        <v>101</v>
+        <v>227</v>
+      </c>
+      <c r="F287" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
@@ -7770,13 +7764,13 @@
         <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>226</v>
+        <v>524</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F288" s="12" t="s">
-        <v>250</v>
+        <v>525</v>
+      </c>
+      <c r="F288" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -7784,13 +7778,16 @@
         <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F289" s="14" t="s">
-        <v>258</v>
+        <v>523</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F289" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -7798,44 +7795,44 @@
         <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>522</v>
+        <v>224</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F290" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>224</v>
+        <v>645</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F291" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>646</v>
+      </c>
+      <c r="F291" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>645</v>
+        <v>584</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="F292" s="20" t="s">
-        <v>100</v>
+        <v>586</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G292" s="2" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7843,81 +7840,81 @@
         <v>73</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>99</v>
+        <v>588</v>
+      </c>
+      <c r="F293" s="16" t="s">
+        <v>303</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A294" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A294" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B294" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F294" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G294" s="2" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A295" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B295" s="17" t="s">
+      <c r="B294" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C295" s="17" t="s">
+      <c r="C294" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D295" s="17"/>
-      <c r="E295" s="17"/>
-      <c r="F295" s="20" t="s">
+      <c r="D294" s="17"/>
+      <c r="E294" s="17"/>
+      <c r="F294" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G295" s="17"/>
-    </row>
-    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G294" s="17"/>
+    </row>
+    <row r="295" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A295" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F295" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>91</v>
+        <v>222</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>315</v>
+        <v>403</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>403</v>
+        <v>249</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>101</v>
@@ -7928,30 +7925,27 @@
         <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>247</v>
+        <v>801</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F298" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>802</v>
+      </c>
+      <c r="F298" s="25" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>803</v>
+        <v>351</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="F299" s="25" t="s">
-        <v>805</v>
+        <v>352</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.35">
@@ -7959,50 +7953,36 @@
         <v>90</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>351</v>
+        <v>564</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>352</v>
+        <v>565</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>566</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A301" s="2" t="s">
+    <row r="301" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A301" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B301" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F301" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A302" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B302" s="17" t="s">
+      <c r="B301" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C302" s="17" t="s">
+      <c r="C301" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D302" s="17" t="s">
+      <c r="D301" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E302" s="17"/>
-      <c r="F302" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G302" s="17"/>
+      <c r="E301" s="17"/>
+      <c r="F301" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G301" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A8D342-CF64-453A-BCA2-30B4659ED6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90689264-523C-45BA-A423-5DBE46709A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1375,9 +1375,6 @@
     <t>Quantization Size for Pollutants</t>
   </si>
   <si>
-    <t>BAU Imported Electricity, BAU Exported Electricity, Imported Electricity Price, BAU Exported Electricity Price</t>
-  </si>
-  <si>
     <t>EVCC</t>
   </si>
   <si>
@@ -2528,6 +2525,9 @@
   </si>
   <si>
     <t>You are using a different model start year than the US EPS (this file should note which vintages are for historical years rather than modeled years)</t>
+  </si>
+  <si>
+    <t>BAU Imported Electricity, BAU Exported Electricity, Imported Electricity Price</t>
   </si>
 </sst>
 </file>
@@ -3380,10 +3380,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -3391,7 +3391,7 @@
         <v>99</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3399,16 +3399,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -3416,10 +3416,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>101</v>
@@ -3430,16 +3430,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -3506,10 +3506,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>99</v>
@@ -3537,10 +3537,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>99</v>
@@ -3582,16 +3582,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>804</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>805</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3605,7 +3605,7 @@
         <v>168</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>100</v>
@@ -3686,10 +3686,10 @@
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>101</v>
@@ -3700,10 +3700,10 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>101</v>
@@ -3807,10 +3807,10 @@
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="F30" s="16" t="s">
         <v>303</v>
@@ -3824,10 +3824,10 @@
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>100</v>
@@ -3838,10 +3838,10 @@
         <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>101</v>
@@ -3866,10 +3866,10 @@
         <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>100</v>
@@ -3880,10 +3880,10 @@
         <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>11</v>
@@ -3897,10 +3897,10 @@
         <v>9</v>
       </c>
       <c r="B36" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="C36" s="17" t="s">
         <v>457</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>458</v>
       </c>
       <c r="D36" s="17"/>
       <c r="E36" s="17" t="s">
@@ -3916,10 +3916,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>617</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>99</v>
@@ -3930,13 +3930,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>696</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>101</v>
@@ -3947,10 +3947,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>100</v>
@@ -3967,7 +3967,7 @@
         <v>417</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>101</v>
@@ -3984,7 +3984,7 @@
         <v>410</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>101</v>
@@ -3995,10 +3995,10 @@
         <v>36</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>101</v>
@@ -4009,19 +4009,19 @@
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>809</v>
       </c>
       <c r="F43" s="21" t="s">
         <v>303</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4029,10 +4029,10 @@
         <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>702</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>100</v>
@@ -4043,10 +4043,10 @@
         <v>36</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F45" s="20" t="s">
         <v>100</v>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="48" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B48" s="17" t="s">
         <v>445</v>
@@ -4101,7 +4101,7 @@
         <v>142</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -4126,16 +4126,16 @@
         <v>413</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -4160,16 +4160,16 @@
         <v>413</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>826</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>827</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -4211,16 +4211,16 @@
         <v>413</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -4228,16 +4228,16 @@
         <v>413</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -4254,7 +4254,7 @@
         <v>180</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -4262,16 +4262,16 @@
         <v>413</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>572</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4296,16 +4296,16 @@
         <v>413</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4327,19 +4327,19 @@
         <v>413</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="D62" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
@@ -4347,10 +4347,10 @@
         <v>413</v>
       </c>
       <c r="B63" s="17" t="s">
+        <v>828</v>
+      </c>
+      <c r="C63" s="17" t="s">
         <v>829</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>830</v>
       </c>
       <c r="D63" s="17"/>
       <c r="E63" s="17"/>
@@ -4358,7 +4358,7 @@
         <v>303</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -4408,10 +4408,10 @@
         <v>38</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>100</v>
@@ -4441,10 +4441,10 @@
         <v>43</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>100</v>
@@ -4455,10 +4455,10 @@
         <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>100</v>
@@ -4469,13 +4469,13 @@
         <v>43</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>101</v>
@@ -4489,10 +4489,10 @@
         <v>181</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>100</v>
@@ -4517,10 +4517,10 @@
         <v>43</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>101</v>
@@ -4531,13 +4531,13 @@
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>686</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>100</v>
@@ -4565,13 +4565,13 @@
         <v>43</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>595</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>250</v>
@@ -4613,16 +4613,16 @@
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>753</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
@@ -4630,10 +4630,10 @@
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>101</v>
@@ -4644,10 +4644,10 @@
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>689</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>690</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>99</v>
@@ -4658,13 +4658,13 @@
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>203</v>
@@ -4678,10 +4678,10 @@
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>825</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>99</v>
@@ -4706,10 +4706,10 @@
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>101</v>
@@ -4726,7 +4726,7 @@
         <v>52</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>101</v>
@@ -4737,10 +4737,10 @@
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>727</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>101</v>
@@ -4751,16 +4751,16 @@
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
@@ -4768,10 +4768,10 @@
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>787</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>788</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>101</v>
@@ -4782,13 +4782,13 @@
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>729</v>
-      </c>
       <c r="D91" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>101</v>
@@ -4799,10 +4799,10 @@
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>101</v>
@@ -4827,10 +4827,10 @@
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>742</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>100</v>
@@ -4847,7 +4847,7 @@
         <v>171</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>99</v>
@@ -4875,19 +4875,19 @@
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>661</v>
-      </c>
       <c r="D97" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>170</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>447</v>
+        <v>831</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>99</v>
@@ -4909,13 +4909,13 @@
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="D99" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>100</v>
@@ -4926,10 +4926,10 @@
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>822</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>823</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>99</v>
@@ -4940,10 +4940,10 @@
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>732</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>101</v>
@@ -4954,13 +4954,13 @@
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="D102" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>99</v>
@@ -4988,10 +4988,10 @@
         <v>43</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>101</v>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B105" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>101</v>
@@ -5013,10 +5013,10 @@
         <v>43</v>
       </c>
       <c r="B106" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>100</v>
@@ -5027,10 +5027,10 @@
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>734</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>100</v>
@@ -5041,10 +5041,10 @@
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>593</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>100</v>
@@ -5055,10 +5055,10 @@
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>99</v>
@@ -5069,10 +5069,10 @@
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>99</v>
@@ -5083,10 +5083,10 @@
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>100</v>
@@ -5097,10 +5097,10 @@
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>100</v>
@@ -5156,16 +5156,16 @@
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5173,13 +5173,13 @@
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>749</v>
-      </c>
       <c r="D117" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>101</v>
@@ -5190,13 +5190,13 @@
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>670</v>
-      </c>
       <c r="D118" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F118" s="14" t="s">
         <v>258</v>
@@ -5221,10 +5221,10 @@
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>100</v>
@@ -5252,13 +5252,13 @@
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="D122" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>101</v>
@@ -5269,13 +5269,13 @@
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>601</v>
-      </c>
       <c r="D123" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>99</v>
@@ -5283,10 +5283,10 @@
     </row>
     <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B124" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="F124" s="14" t="s">
         <v>258</v>
@@ -5297,13 +5297,13 @@
         <v>43</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>100</v>
@@ -5314,10 +5314,10 @@
         <v>43</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="F126" s="14" t="s">
         <v>258</v>
@@ -5328,10 +5328,10 @@
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>652</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>100</v>
@@ -5342,10 +5342,10 @@
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>654</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>100</v>
@@ -5356,10 +5356,10 @@
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>100</v>
@@ -5370,10 +5370,10 @@
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>650</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>99</v>
@@ -5384,13 +5384,13 @@
         <v>43</v>
       </c>
       <c r="B131" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>599</v>
-      </c>
       <c r="E131" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>99</v>
@@ -5401,13 +5401,13 @@
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="D132" s="2" t="s">
         <v>737</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>99</v>
@@ -5418,10 +5418,10 @@
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>820</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>821</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>100</v>
@@ -5432,10 +5432,10 @@
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>101</v>
@@ -5473,7 +5473,7 @@
         <v>270</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>100</v>
@@ -5490,7 +5490,7 @@
         <v>274</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>100</v>
@@ -5574,10 +5574,10 @@
         <v>55</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>99</v>
@@ -5588,10 +5588,10 @@
         <v>55</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>101</v>
@@ -5602,10 +5602,10 @@
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>101</v>
@@ -5616,10 +5616,10 @@
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>101</v>
@@ -5630,13 +5630,13 @@
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="D147" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>99</v>
@@ -5692,10 +5692,10 @@
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>101</v>
@@ -5706,10 +5706,10 @@
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>101</v>
@@ -5720,13 +5720,13 @@
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>527</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>101</v>
@@ -5737,10 +5737,10 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>101</v>
@@ -5751,10 +5751,10 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>99</v>
@@ -5765,10 +5765,10 @@
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>608</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>100</v>
@@ -5940,16 +5940,16 @@
     </row>
     <row r="167" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="B167" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="B167" s="17" t="s">
+      <c r="C167" s="17" t="s">
         <v>759</v>
       </c>
-      <c r="C167" s="17" t="s">
+      <c r="D167" s="17" t="s">
         <v>760</v>
-      </c>
-      <c r="D167" s="17" t="s">
-        <v>761</v>
       </c>
       <c r="F167" s="19" t="s">
         <v>99</v>
@@ -6050,14 +6050,14 @@
         <v>357</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>811</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>812</v>
       </c>
       <c r="F174" s="6"/>
       <c r="G174" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6082,10 +6082,10 @@
         <v>357</v>
       </c>
       <c r="B176" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="C176" s="17" t="s">
         <v>499</v>
-      </c>
-      <c r="C176" s="17" t="s">
-        <v>500</v>
       </c>
       <c r="D176" s="17"/>
       <c r="E176" s="17"/>
@@ -6113,13 +6113,13 @@
         <v>63</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="C178" s="2" t="s">
+      <c r="D178" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="F178" s="14" t="s">
         <v>400</v>
@@ -6130,13 +6130,13 @@
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="C179" s="2" t="s">
+      <c r="D179" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>100</v>
@@ -6195,10 +6195,10 @@
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>101</v>
@@ -6226,10 +6226,10 @@
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>101</v>
@@ -6240,10 +6240,10 @@
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="F186" s="4" t="s">
         <v>100</v>
@@ -6254,10 +6254,10 @@
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="F187" s="4" t="s">
         <v>100</v>
@@ -6268,16 +6268,16 @@
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C188" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
@@ -6299,19 +6299,19 @@
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C190" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="C190" s="2" t="s">
+      <c r="D190" s="2" t="s">
         <v>815</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>816</v>
       </c>
       <c r="F190" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6392,10 +6392,10 @@
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>568</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>101</v>
@@ -6406,10 +6406,10 @@
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>100</v>
@@ -6420,10 +6420,10 @@
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>100</v>
@@ -6434,10 +6434,10 @@
         <v>63</v>
       </c>
       <c r="B199" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="C199" s="17" t="s">
         <v>495</v>
-      </c>
-      <c r="C199" s="17" t="s">
-        <v>496</v>
       </c>
       <c r="D199" s="17"/>
       <c r="E199" s="17"/>
@@ -6451,10 +6451,10 @@
         <v>420</v>
       </c>
       <c r="B200" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C200" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>798</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>99</v>
@@ -6465,13 +6465,13 @@
         <v>420</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="C201" s="2" t="s">
+      <c r="D201" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>99</v>
@@ -6482,13 +6482,13 @@
         <v>420</v>
       </c>
       <c r="B202" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="C202" s="2" t="s">
-        <v>712</v>
-      </c>
       <c r="D202" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>99</v>
@@ -6555,13 +6555,13 @@
         <v>420</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="D207" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>614</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>434</v>
@@ -6603,16 +6603,16 @@
         <v>420</v>
       </c>
       <c r="B210" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C210" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="F210" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6620,13 +6620,13 @@
         <v>420</v>
       </c>
       <c r="B211" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="D211" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="F211" s="3"/>
     </row>
@@ -6635,16 +6635,16 @@
         <v>420</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C212" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
@@ -6652,10 +6652,10 @@
         <v>420</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C213" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>422</v>
@@ -6669,10 +6669,10 @@
         <v>420</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>101</v>
@@ -6683,10 +6683,10 @@
         <v>420</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>101</v>
@@ -6711,10 +6711,10 @@
         <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C217" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>470</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>101</v>
@@ -6725,10 +6725,10 @@
         <v>420</v>
       </c>
       <c r="B218" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>99</v>
@@ -6748,7 +6748,7 @@
         <v>303</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="220" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6756,10 +6756,10 @@
         <v>420</v>
       </c>
       <c r="B220" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C220" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="F220" s="19" t="s">
         <v>99</v>
@@ -6770,10 +6770,10 @@
         <v>420</v>
       </c>
       <c r="B221" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="C221" s="17" t="s">
         <v>491</v>
-      </c>
-      <c r="C221" s="17" t="s">
-        <v>492</v>
       </c>
       <c r="D221" s="17"/>
       <c r="E221" s="17"/>
@@ -6948,7 +6948,7 @@
         <v>142</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
@@ -6956,16 +6956,16 @@
         <v>70</v>
       </c>
       <c r="B233" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>745</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>746</v>
       </c>
       <c r="F233" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6992,10 +6992,10 @@
         <v>73</v>
       </c>
       <c r="B235" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="F235" s="4" t="s">
         <v>100</v>
@@ -7006,10 +7006,10 @@
         <v>73</v>
       </c>
       <c r="B236" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="F236" s="5" t="s">
         <v>101</v>
@@ -7048,10 +7048,10 @@
         <v>73</v>
       </c>
       <c r="B239" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C239" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="F239" s="5" t="s">
         <v>101</v>
@@ -7076,10 +7076,10 @@
         <v>73</v>
       </c>
       <c r="B241" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C241" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="F241" s="4" t="s">
         <v>100</v>
@@ -7090,10 +7090,10 @@
         <v>73</v>
       </c>
       <c r="B242" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C242" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="F242" s="5" t="s">
         <v>101</v>
@@ -7149,10 +7149,10 @@
         <v>73</v>
       </c>
       <c r="B246" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C246" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>99</v>
@@ -7163,10 +7163,10 @@
         <v>73</v>
       </c>
       <c r="B247" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C247" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="F247" s="5" t="s">
         <v>101</v>
@@ -7177,10 +7177,10 @@
         <v>73</v>
       </c>
       <c r="B248" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C248" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="F248" s="5" t="s">
         <v>101</v>
@@ -7219,13 +7219,13 @@
         <v>73</v>
       </c>
       <c r="B251" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C251" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="C251" s="2" t="s">
+      <c r="D251" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>101</v>
@@ -7236,10 +7236,10 @@
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C252" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>623</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>101</v>
@@ -7250,10 +7250,10 @@
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>819</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>99</v>
@@ -7264,10 +7264,10 @@
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C254" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>709</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>99</v>
@@ -7278,10 +7278,10 @@
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>638</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>99</v>
@@ -7292,10 +7292,10 @@
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>99</v>
@@ -7306,10 +7306,10 @@
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C257" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>590</v>
       </c>
       <c r="F257" s="4" t="s">
         <v>100</v>
@@ -7407,13 +7407,13 @@
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C264" s="2" t="s">
+      <c r="D264" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>626</v>
       </c>
       <c r="F264" s="5" t="s">
         <v>101</v>
@@ -7424,10 +7424,10 @@
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C265" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>100</v>
@@ -7438,10 +7438,10 @@
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C266" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>100</v>
@@ -7452,10 +7452,10 @@
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C267" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="F267" s="5" t="s">
         <v>101</v>
@@ -7466,10 +7466,10 @@
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="C268" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>99</v>
@@ -7494,10 +7494,10 @@
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C270" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="F270" s="5" t="s">
         <v>101</v>
@@ -7576,10 +7576,10 @@
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C275" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="F275" s="5" t="s">
         <v>238</v>
@@ -7604,10 +7604,10 @@
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="C277" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="F277" s="4" t="s">
         <v>100</v>
@@ -7635,10 +7635,10 @@
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C279" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="F279" s="5" t="s">
         <v>101</v>
@@ -7649,10 +7649,10 @@
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C280" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="F280" s="5" t="s">
         <v>101</v>
@@ -7663,16 +7663,16 @@
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="C281" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>777</v>
       </c>
       <c r="F281" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
@@ -7708,10 +7708,10 @@
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C284" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>644</v>
       </c>
       <c r="F284" s="4" t="s">
         <v>100</v>
@@ -7736,10 +7736,10 @@
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C286" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="F286" s="5" t="s">
         <v>101</v>
@@ -7764,10 +7764,10 @@
         <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C288" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="F288" s="14" t="s">
         <v>258</v>
@@ -7778,10 +7778,10 @@
         <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C289" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>226</v>
@@ -7809,10 +7809,10 @@
         <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="F291" s="20" t="s">
         <v>100</v>
@@ -7823,16 +7823,16 @@
         <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7840,16 +7840,16 @@
         <v>73</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F293" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7925,13 +7925,13 @@
         <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="C298" s="2" t="s">
+      <c r="F298" s="25" t="s">
         <v>802</v>
-      </c>
-      <c r="F298" s="25" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.35">
@@ -7953,13 +7953,13 @@
         <v>90</v>
       </c>
       <c r="B300" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C300" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C300" s="2" t="s">
+      <c r="D300" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>566</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>100</v>
@@ -8049,10 +8049,10 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>484</v>
+      </c>
+      <c r="B7" t="s">
         <v>485</v>
-      </c>
-      <c r="B7" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90689264-523C-45BA-A423-5DBE46709A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B9A522-AC81-49EE-88D1-EB8CBF90E990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="829">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2011,12 +2011,6 @@
     <t>BAU Zero Emis Credit for Nuc Plants</t>
   </si>
   <si>
-    <t>EDWP</t>
-  </si>
-  <si>
-    <t>Electricity Dispatch Weibull Parameters</t>
-  </si>
-  <si>
     <t>MLfPPR</t>
   </si>
   <si>
@@ -2219,9 +2213,6 @@
   </si>
   <si>
     <t>Capacity Supply Curve</t>
-  </si>
-  <si>
-    <t>Electricity Dispatch Weibull Parameter A, Electricity Dispatch Weibull Parameter B</t>
   </si>
   <si>
     <t>GBCGpUNR</t>
@@ -3339,7 +3330,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:G300"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -3506,10 +3497,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>99</v>
@@ -3582,16 +3573,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -3700,10 +3691,10 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>101</v>
@@ -3930,13 +3921,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>101</v>
@@ -3947,10 +3938,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>100</v>
@@ -3967,7 +3958,7 @@
         <v>417</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>101</v>
@@ -3984,7 +3975,7 @@
         <v>410</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>101</v>
@@ -3995,10 +3986,10 @@
         <v>36</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>101</v>
@@ -4009,19 +4000,19 @@
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="F43" s="21" t="s">
         <v>303</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -4029,10 +4020,10 @@
         <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>100</v>
@@ -4043,10 +4034,10 @@
         <v>36</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F45" s="20" t="s">
         <v>100</v>
@@ -4101,7 +4092,7 @@
         <v>142</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -4160,16 +4151,16 @@
         <v>413</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -4211,16 +4202,16 @@
         <v>413</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -4333,7 +4324,7 @@
         <v>464</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>180</v>
@@ -4347,10 +4338,10 @@
         <v>413</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D63" s="17"/>
       <c r="E63" s="17"/>
@@ -4358,7 +4349,7 @@
         <v>303</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -4441,10 +4432,10 @@
         <v>43</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>100</v>
@@ -4455,10 +4446,10 @@
         <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>100</v>
@@ -4489,10 +4480,10 @@
         <v>181</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>100</v>
@@ -4531,13 +4522,13 @@
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>100</v>
@@ -4571,7 +4562,7 @@
         <v>594</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>250</v>
@@ -4613,16 +4604,16 @@
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
@@ -4630,10 +4621,10 @@
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>101</v>
@@ -4644,10 +4635,10 @@
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>99</v>
@@ -4658,13 +4649,13 @@
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>203</v>
@@ -4678,10 +4669,10 @@
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>99</v>
@@ -4726,7 +4717,7 @@
         <v>52</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>101</v>
@@ -4737,10 +4728,10 @@
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>101</v>
@@ -4768,10 +4759,10 @@
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>101</v>
@@ -4782,13 +4773,13 @@
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>101</v>
@@ -4827,10 +4818,10 @@
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>100</v>
@@ -4847,7 +4838,7 @@
         <v>171</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>99</v>
@@ -4870,21 +4861,21 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>659</v>
+        <v>169</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>660</v>
+        <v>170</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>101</v>
+        <v>828</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
@@ -4892,16 +4883,16 @@
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>169</v>
+        <v>668</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>170</v>
+        <v>669</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>99</v>
+        <v>670</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
@@ -4909,16 +4900,13 @@
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>670</v>
+        <v>818</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>100</v>
+        <v>819</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -4926,13 +4914,13 @@
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>821</v>
+        <v>727</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>99</v>
+        <v>728</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4940,114 +4928,114 @@
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>730</v>
+        <v>488</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+        <v>489</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>488</v>
+        <v>177</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>177</v>
+        <v>762</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>321</v>
+        <v>764</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A104" s="2" t="s">
+      <c r="B104" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B105" s="2" t="s">
-        <v>766</v>
+        <v>710</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>711</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>712</v>
+        <v>729</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>713</v>
+        <v>730</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>732</v>
+        <v>591</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>733</v>
+        <v>592</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>100</v>
+        <v>605</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
@@ -5055,10 +5043,10 @@
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>604</v>
+        <v>746</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>605</v>
+        <v>747</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>99</v>
@@ -5069,13 +5057,13 @@
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>749</v>
+        <v>595</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>99</v>
+        <v>596</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
@@ -5083,10 +5071,10 @@
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>595</v>
+        <v>659</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>596</v>
+        <v>660</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>100</v>
@@ -5097,13 +5085,13 @@
         <v>43</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>661</v>
+        <v>48</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>100</v>
+        <v>53</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
@@ -5111,27 +5099,30 @@
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>48</v>
+        <v>196</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>196</v>
+        <v>49</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>100</v>
+        <v>54</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -5139,33 +5130,33 @@
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>49</v>
+        <v>751</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>54</v>
+        <v>752</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>756</v>
+        <v>745</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5173,44 +5164,41 @@
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>747</v>
+        <v>666</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>748</v>
+        <v>667</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>731</v>
+      </c>
+      <c r="F117" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>668</v>
+        <v>186</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="F118" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>186</v>
+        <v>578</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>187</v>
+        <v>579</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>100</v>
@@ -5221,13 +5209,16 @@
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>578</v>
+        <v>203</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>100</v>
+        <v>204</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5235,78 +5226,75 @@
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>203</v>
+        <v>678</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>204</v>
+        <v>679</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>205</v>
+        <v>680</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>680</v>
+        <v>599</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>681</v>
+        <v>600</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A123" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B123" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F123" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B124" s="2" t="s">
-        <v>666</v>
+        <v>451</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="F124" s="14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>452</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>451</v>
+        <v>676</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>100</v>
+        <v>677</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5314,13 +5302,13 @@
         <v>43</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>678</v>
+        <v>650</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="F126" s="14" t="s">
-        <v>258</v>
+        <v>651</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5328,10 +5316,10 @@
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>100</v>
@@ -5342,27 +5330,27 @@
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>652</v>
+        <v>573</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>653</v>
+        <v>574</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>573</v>
+        <v>648</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>100</v>
+        <v>649</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
@@ -5370,27 +5358,30 @@
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>648</v>
+        <v>597</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>649</v>
+        <v>598</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>595</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>597</v>
+        <v>732</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>595</v>
+        <v>733</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>99</v>
@@ -5401,16 +5392,13 @@
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>735</v>
+        <v>816</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>99</v>
+        <v>817</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5418,110 +5406,110 @@
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>819</v>
+        <v>703</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="F133" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B134" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C134" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="D134" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="E134" s="17"/>
+      <c r="F134" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="G134" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A135" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="F135" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B135" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="C135" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="D135" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="E135" s="17"/>
-      <c r="F135" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="G135" s="17" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>704</v>
+        <v>630</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>630</v>
+        <v>272</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>271</v>
+        <v>418</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>418</v>
+        <v>183</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>101</v>
+        <v>182</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
@@ -5529,69 +5517,69 @@
         <v>275</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A141" s="2" t="s">
+    <row r="141" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F141" s="4" t="s">
+      <c r="B141" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C141" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D141" s="17"/>
+      <c r="E141" s="17"/>
+      <c r="F141" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="B142" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="C142" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="D142" s="17"/>
-      <c r="E142" s="17"/>
-      <c r="F142" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G142" s="17"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G141" s="17"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A142" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>470</v>
+        <v>785</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>788</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>101</v>
@@ -5602,10 +5590,10 @@
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>101</v>
@@ -5616,13 +5604,16 @@
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>790</v>
+        <v>472</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>101</v>
+        <v>473</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
@@ -5630,72 +5621,69 @@
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>472</v>
+        <v>380</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>474</v>
+        <v>381</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>380</v>
+        <v>56</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>381</v>
+        <v>59</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>268</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>56</v>
+        <v>313</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>313</v>
+        <v>776</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>314</v>
+        <v>777</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>779</v>
+        <v>628</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>780</v>
+        <v>629</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>101</v>
@@ -5706,10 +5694,13 @@
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>628</v>
+        <v>525</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>629</v>
+        <v>792</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>526</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>101</v>
@@ -5720,13 +5711,10 @@
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>525</v>
+        <v>791</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>526</v>
+        <v>778</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>101</v>
@@ -5737,13 +5725,13 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>794</v>
+        <v>542</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>101</v>
+        <v>543</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
@@ -5751,58 +5739,61 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>542</v>
+        <v>606</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+        <v>607</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>606</v>
+        <v>57</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F156" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>57</v>
+        <v>311</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F157" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>311</v>
+        <v>390</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>101</v>
+        <v>393</v>
+      </c>
+      <c r="F158" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5810,16 +5801,16 @@
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F159" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5827,132 +5818,129 @@
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F160" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>392</v>
+        <v>58</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F161" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>58</v>
+        <v>376</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>61</v>
+        <v>340</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>341</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F163" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A164" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F164" s="3" t="s">
+      <c r="B164" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="C164" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="F164" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="G164" s="17" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A165" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F165" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="165" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B165" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="C165" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="F165" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G165" s="17" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A166" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F166" s="3" t="s">
+    <row r="166" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="B166" s="17" t="s">
+        <v>755</v>
+      </c>
+      <c r="C166" s="17" t="s">
+        <v>756</v>
+      </c>
+      <c r="D166" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="F166" s="19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="167" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="17" t="s">
-        <v>757</v>
-      </c>
-      <c r="B167" s="17" t="s">
-        <v>758</v>
-      </c>
-      <c r="C167" s="17" t="s">
-        <v>759</v>
-      </c>
-      <c r="D167" s="17" t="s">
-        <v>760</v>
-      </c>
-      <c r="F167" s="19" t="s">
-        <v>99</v>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A167" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
@@ -5960,13 +5948,13 @@
         <v>357</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>101</v>
+        <v>367</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
@@ -5974,24 +5962,27 @@
         <v>357</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>100</v>
@@ -6002,47 +5993,45 @@
         <v>357</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F172" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+        <v>371</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>364</v>
+        <v>807</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F173" s="6" t="s">
-        <v>142</v>
-      </c>
+        <v>808</v>
+      </c>
+      <c r="F173" s="6"/>
       <c r="G173" s="2" t="s">
-        <v>374</v>
+        <v>809</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6050,62 +6039,64 @@
         <v>357</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>810</v>
+        <v>365</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="F174" s="6"/>
+        <v>372</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="G174" s="2" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A175" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F175" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G175" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="B176" s="17" t="s">
+      <c r="B175" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="C176" s="17" t="s">
+      <c r="C175" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="D176" s="17"/>
-      <c r="E176" s="17"/>
-      <c r="F176" s="20" t="s">
+      <c r="D175" s="17"/>
+      <c r="E175" s="17"/>
+      <c r="F175" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G176" s="17"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G175" s="17"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A176" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F176" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F177" s="12" t="s">
-        <v>250</v>
+        <v>519</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F177" s="14" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6113,16 +6104,16 @@
         <v>63</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>518</v>
+        <v>661</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>519</v>
+        <v>662</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="F178" s="14" t="s">
-        <v>400</v>
+        <v>663</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6130,16 +6121,19 @@
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>663</v>
+        <v>197</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="F179" s="4" t="s">
-        <v>100</v>
+        <v>198</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F179" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6147,19 +6141,13 @@
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>197</v>
+        <v>326</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F180" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G180" s="2" t="s">
-        <v>339</v>
+        <v>327</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6167,27 +6155,27 @@
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>326</v>
+        <v>64</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>64</v>
+        <v>496</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F182" s="4" t="s">
-        <v>100</v>
+        <v>497</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
@@ -6195,13 +6183,16 @@
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>496</v>
+        <v>65</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>101</v>
+        <v>68</v>
+      </c>
+      <c r="F183" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
@@ -6209,16 +6200,13 @@
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>65</v>
+        <v>561</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F184" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G184" s="2" t="s">
-        <v>345</v>
+        <v>562</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6226,13 +6214,13 @@
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>561</v>
+        <v>760</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>101</v>
+        <v>761</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
@@ -6240,58 +6228,64 @@
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="F186" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>769</v>
+        <v>515</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="F187" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>516</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>515</v>
+        <v>199</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F188" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G188" s="2" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>199</v>
+        <v>810</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F189" s="4" t="s">
-        <v>100</v>
+        <v>811</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F189" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>813</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6299,50 +6293,44 @@
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>813</v>
+        <v>66</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>814</v>
+        <v>69</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="F190" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G190" s="2" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>399</v>
+      </c>
+      <c r="F190" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F191" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>190</v>
+        <v>277</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F192" s="4" t="s">
-        <v>100</v>
+        <v>280</v>
+      </c>
+      <c r="F192" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6350,10 +6338,10 @@
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>101</v>
@@ -6364,13 +6352,13 @@
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F194" s="5" t="s">
-        <v>101</v>
+        <v>282</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6378,100 +6366,103 @@
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>279</v>
+        <v>566</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F195" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>567</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>566</v>
+        <v>476</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F196" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+        <v>475</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A198" s="2" t="s">
+    <row r="198" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A198" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F198" s="4" t="s">
+      <c r="B198" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="C198" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="D198" s="17"/>
+      <c r="E198" s="17"/>
+      <c r="F198" s="20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B199" s="17" t="s">
-        <v>494</v>
-      </c>
-      <c r="C199" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="D199" s="17"/>
-      <c r="E199" s="17"/>
-      <c r="F199" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G199" s="17"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G198" s="17"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A199" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>796</v>
+        <v>558</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>797</v>
+        <v>559</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>560</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>558</v>
+        <v>708</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>559</v>
+        <v>709</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>560</v>
+        <v>707</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>99</v>
@@ -6482,13 +6473,10 @@
         <v>420</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>710</v>
+        <v>428</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>709</v>
+        <v>429</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>99</v>
@@ -6499,10 +6487,10 @@
         <v>420</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>99</v>
@@ -6513,10 +6501,10 @@
         <v>420</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>430</v>
+        <v>401</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>431</v>
+        <v>402</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>99</v>
@@ -6527,44 +6515,44 @@
         <v>420</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>432</v>
+        <v>612</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>433</v>
+        <v>614</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>434</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>612</v>
+        <v>434</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>99</v>
@@ -6575,27 +6563,30 @@
         <v>420</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>422</v>
+        <v>529</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>99</v>
+        <v>530</v>
+      </c>
+      <c r="F209" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6603,48 +6594,48 @@
         <v>420</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>529</v>
+        <v>479</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F210" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G210" s="2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>480</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F210" s="3"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>479</v>
+        <v>527</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="F211" s="3"/>
+        <v>528</v>
+      </c>
+      <c r="F211" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F212" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G212" s="2" t="s">
-        <v>532</v>
+        <v>503</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
@@ -6652,16 +6643,13 @@
         <v>420</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F213" s="3" t="s">
-        <v>99</v>
+        <v>501</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
@@ -6669,10 +6657,10 @@
         <v>420</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>500</v>
+        <v>466</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>101</v>
@@ -6683,10 +6671,10 @@
         <v>420</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>467</v>
+        <v>425</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>101</v>
@@ -6697,10 +6685,10 @@
         <v>420</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>101</v>
@@ -6711,106 +6699,106 @@
         <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F217" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+        <v>541</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>540</v>
+        <v>426</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F218" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>427</v>
+      </c>
+      <c r="F218" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>426</v>
+        <v>568</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F219" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G219" s="2" t="s">
-        <v>533</v>
+        <v>569</v>
+      </c>
+      <c r="F219" s="19" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="220" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="2" t="s">
+      <c r="A220" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>569</v>
-      </c>
+      <c r="B220" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="C220" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="D220" s="17"/>
+      <c r="E220" s="17"/>
       <c r="F220" s="19" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A221" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="B221" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="C221" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="D221" s="17"/>
-      <c r="E221" s="17"/>
-      <c r="F221" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="G221" s="17"/>
+      <c r="G220" s="17"/>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A221" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F221" s="5" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F222" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F222" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>304</v>
+        <v>211</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F223" s="12" t="s">
-        <v>250</v>
+        <v>212</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="224" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6818,30 +6806,30 @@
         <v>93</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F224" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+      <c r="F224" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F225" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G225" s="2" t="s">
-        <v>346</v>
+        <v>220</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
@@ -6849,10 +6837,10 @@
         <v>93</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>215</v>
+        <v>94</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>101</v>
@@ -6863,128 +6851,128 @@
         <v>93</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F227" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F228" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A229" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F228" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A229" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B229" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F229" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A230" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B230" s="17" t="s">
+      <c r="B229" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C230" s="17" t="s">
+      <c r="C229" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D230" s="17"/>
-      <c r="E230" s="17"/>
-      <c r="F230" s="20" t="s">
+      <c r="D229" s="17"/>
+      <c r="E229" s="17"/>
+      <c r="F229" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G230" s="17"/>
+      <c r="G229" s="17"/>
+    </row>
+    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A230" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F230" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>192</v>
+        <v>741</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>194</v>
+        <v>742</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A233" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A233" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B233" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="F233" s="6" t="s">
+      <c r="B233" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C233" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D233" s="17"/>
+      <c r="E233" s="17"/>
+      <c r="F233" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G233" s="2" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A234" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B234" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C234" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="D234" s="17"/>
-      <c r="E234" s="17"/>
-      <c r="F234" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G234" s="17" t="s">
+      <c r="G233" s="17" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A234" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
@@ -6992,13 +6980,13 @@
         <v>73</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>631</v>
+        <v>549</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="F235" s="4" t="s">
-        <v>100</v>
+        <v>550</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
@@ -7006,13 +6994,13 @@
         <v>73</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>549</v>
+        <v>74</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F236" s="5" t="s">
-        <v>101</v>
+        <v>82</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -7020,41 +7008,41 @@
         <v>73</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F237" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>75</v>
+        <v>553</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>83</v>
+        <v>554</v>
       </c>
       <c r="F238" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>553</v>
+        <v>411</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F239" s="5" t="s">
-        <v>101</v>
+        <v>412</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
@@ -7062,10 +7050,10 @@
         <v>73</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>411</v>
+        <v>674</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>412</v>
+        <v>675</v>
       </c>
       <c r="F240" s="4" t="s">
         <v>100</v>
@@ -7076,13 +7064,13 @@
         <v>73</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>676</v>
+        <v>551</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="F241" s="4" t="s">
-        <v>100</v>
+        <v>552</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
@@ -7090,13 +7078,13 @@
         <v>73</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>551</v>
+        <v>283</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="F242" s="5" t="s">
-        <v>101</v>
+        <v>284</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
@@ -7104,44 +7092,44 @@
         <v>73</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F244" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>236</v>
+        <v>795</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F245" s="5" t="s">
-        <v>101</v>
+        <v>796</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
@@ -7149,13 +7137,13 @@
         <v>73</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>798</v>
+        <v>617</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="F246" s="3" t="s">
-        <v>99</v>
+        <v>618</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
@@ -7163,10 +7151,10 @@
         <v>73</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F247" s="5" t="s">
         <v>101</v>
@@ -7177,10 +7165,10 @@
         <v>73</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>619</v>
+        <v>232</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>620</v>
+        <v>233</v>
       </c>
       <c r="F248" s="5" t="s">
         <v>101</v>
@@ -7191,10 +7179,10 @@
         <v>73</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>101</v>
@@ -7205,10 +7193,13 @@
         <v>73</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>228</v>
+        <v>633</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>229</v>
+        <v>634</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>635</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>101</v>
@@ -7219,13 +7210,10 @@
         <v>73</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>101</v>
@@ -7236,13 +7224,13 @@
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>621</v>
+        <v>814</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="F252" s="5" t="s">
-        <v>101</v>
+        <v>815</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
@@ -7250,10 +7238,10 @@
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>817</v>
+        <v>705</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>818</v>
+        <v>706</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>99</v>
@@ -7264,10 +7252,10 @@
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>707</v>
+        <v>636</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>708</v>
+        <v>637</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>99</v>
@@ -7278,10 +7266,10 @@
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>636</v>
+        <v>608</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>99</v>
@@ -7292,13 +7280,13 @@
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="F256" s="3" t="s">
-        <v>99</v>
+        <v>589</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
@@ -7306,44 +7294,44 @@
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>588</v>
+        <v>241</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>589</v>
+        <v>242</v>
       </c>
       <c r="F257" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F258" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="F258" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F259" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G259" s="2" t="s">
-        <v>334</v>
+        <v>84</v>
+      </c>
+      <c r="F259" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
@@ -7351,10 +7339,10 @@
         <v>73</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>101</v>
@@ -7365,10 +7353,10 @@
         <v>73</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>101</v>
@@ -7379,13 +7367,13 @@
         <v>73</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F262" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
@@ -7393,13 +7381,16 @@
         <v>73</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>79</v>
+        <v>623</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F263" s="4" t="s">
-        <v>100</v>
+        <v>624</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F263" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
@@ -7407,16 +7398,13 @@
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>623</v>
+        <v>447</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F264" s="5" t="s">
-        <v>101</v>
+        <v>448</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -7424,41 +7412,41 @@
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>477</v>
+        <v>638</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F266" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>639</v>
+      </c>
+      <c r="F266" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>638</v>
+        <v>735</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F267" s="5" t="s">
-        <v>101</v>
+        <v>736</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
@@ -7466,10 +7454,10 @@
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>738</v>
+        <v>80</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>739</v>
+        <v>88</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>99</v>
@@ -7480,27 +7468,30 @@
         <v>73</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>80</v>
+        <v>547</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F269" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+        <v>548</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>547</v>
+        <v>293</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F270" s="5" t="s">
-        <v>101</v>
+        <v>294</v>
+      </c>
+      <c r="F270" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="271" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7508,10 +7499,10 @@
         <v>73</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F271" s="16" t="s">
         <v>303</v>
@@ -7525,10 +7516,10 @@
         <v>73</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="F272" s="16" t="s">
         <v>303</v>
@@ -7537,38 +7528,35 @@
         <v>335</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F273" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G273" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>230</v>
+        <v>688</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F274" s="4" t="s">
-        <v>100</v>
+        <v>689</v>
+      </c>
+      <c r="F274" s="5" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="275" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7576,58 +7564,58 @@
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>690</v>
+        <v>81</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="F275" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>81</v>
+        <v>739</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>89</v>
+        <v>740</v>
       </c>
       <c r="F276" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>742</v>
+        <v>443</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="F277" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>444</v>
+      </c>
+      <c r="F277" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G277" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>443</v>
+        <v>640</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F278" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G278" s="2" t="s">
-        <v>377</v>
+        <v>641</v>
+      </c>
+      <c r="F278" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
@@ -7635,44 +7623,44 @@
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>640</v>
+        <v>506</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>641</v>
+        <v>507</v>
       </c>
       <c r="F279" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>506</v>
+        <v>772</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F280" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>773</v>
+      </c>
+      <c r="F280" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>775</v>
+        <v>245</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="F281" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G281" s="2" t="s">
-        <v>777</v>
+        <v>246</v>
+      </c>
+      <c r="F281" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
@@ -7680,13 +7668,13 @@
         <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>245</v>
+        <v>298</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F282" s="14" t="s">
-        <v>258</v>
+        <v>297</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
@@ -7694,13 +7682,13 @@
         <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>298</v>
+        <v>642</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F283" s="5" t="s">
-        <v>101</v>
+        <v>643</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
@@ -7708,13 +7696,13 @@
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>642</v>
+        <v>234</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F284" s="4" t="s">
-        <v>100</v>
+        <v>235</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
@@ -7722,10 +7710,10 @@
         <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>234</v>
+        <v>626</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>235</v>
+        <v>627</v>
       </c>
       <c r="F285" s="5" t="s">
         <v>101</v>
@@ -7736,13 +7724,13 @@
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>626</v>
+        <v>226</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F286" s="5" t="s">
-        <v>101</v>
+        <v>227</v>
+      </c>
+      <c r="F286" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -7750,13 +7738,13 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>226</v>
+        <v>523</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F287" s="12" t="s">
-        <v>250</v>
+        <v>524</v>
+      </c>
+      <c r="F287" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
@@ -7764,13 +7752,16 @@
         <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F288" s="14" t="s">
-        <v>258</v>
+        <v>522</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F288" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -7778,44 +7769,44 @@
         <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>521</v>
+        <v>224</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F289" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>224</v>
+        <v>644</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F290" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>645</v>
+      </c>
+      <c r="F290" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>644</v>
+        <v>583</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F291" s="20" t="s">
-        <v>100</v>
+        <v>585</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G291" s="2" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7823,81 +7814,81 @@
         <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F292" s="3" t="s">
-        <v>99</v>
+        <v>587</v>
+      </c>
+      <c r="F292" s="16" t="s">
+        <v>303</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A293" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A293" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B293" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="F293" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G293" s="2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A294" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B294" s="17" t="s">
+      <c r="B293" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C294" s="17" t="s">
+      <c r="C293" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D294" s="17"/>
-      <c r="E294" s="17"/>
-      <c r="F294" s="20" t="s">
+      <c r="D293" s="17"/>
+      <c r="E293" s="17"/>
+      <c r="F293" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G294" s="17"/>
-    </row>
-    <row r="295" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G293" s="17"/>
+    </row>
+    <row r="294" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A294" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F294" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>91</v>
+        <v>222</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>315</v>
+        <v>403</v>
       </c>
       <c r="F295" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>403</v>
+        <v>249</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>101</v>
@@ -7908,30 +7899,27 @@
         <v>90</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>247</v>
+        <v>797</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D297" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F297" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>798</v>
+      </c>
+      <c r="F297" s="25" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>800</v>
+        <v>351</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="F298" s="25" t="s">
-        <v>802</v>
+        <v>352</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.35">
@@ -7939,50 +7927,36 @@
         <v>90</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>351</v>
+        <v>563</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>352</v>
+        <v>564</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>565</v>
       </c>
       <c r="F299" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A300" s="2" t="s">
+    <row r="300" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A300" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B300" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A301" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B301" s="17" t="s">
+      <c r="B300" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C301" s="17" t="s">
+      <c r="C300" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D301" s="17" t="s">
+      <c r="D300" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E301" s="17"/>
-      <c r="F301" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G301" s="17"/>
+      <c r="E300" s="17"/>
+      <c r="F300" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G300" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B9A522-AC81-49EE-88D1-EB8CBF90E990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730C44AC-7D31-4302-9A0A-C633B8634610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="831">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2519,6 +2519,12 @@
   </si>
   <si>
     <t>BAU Imported Electricity, BAU Exported Electricity, Imported Electricity Price</t>
+  </si>
+  <si>
+    <t>BPM</t>
+  </si>
+  <si>
+    <t>Battery Pack Markup</t>
   </si>
 </sst>
 </file>
@@ -3330,7 +3336,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G300"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -7193,16 +7199,13 @@
         <v>73</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>633</v>
+        <v>829</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F250" s="5" t="s">
-        <v>101</v>
+        <v>830</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.35">
@@ -7210,10 +7213,13 @@
         <v>73</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>622</v>
+        <v>634</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>635</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>101</v>
@@ -7224,13 +7230,13 @@
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>814</v>
+        <v>621</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="F252" s="3" t="s">
-        <v>99</v>
+        <v>622</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
@@ -7238,10 +7244,10 @@
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>705</v>
+        <v>814</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>706</v>
+        <v>815</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>99</v>
@@ -7252,10 +7258,10 @@
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>636</v>
+        <v>705</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>637</v>
+        <v>706</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>99</v>
@@ -7266,10 +7272,10 @@
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>99</v>
@@ -7280,13 +7286,13 @@
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F256" s="4" t="s">
-        <v>100</v>
+        <v>609</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
@@ -7294,44 +7300,44 @@
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>241</v>
+        <v>588</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>242</v>
+        <v>589</v>
       </c>
       <c r="F257" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F258" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G258" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>76</v>
+        <v>285</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F259" s="5" t="s">
-        <v>101</v>
+        <v>286</v>
+      </c>
+      <c r="F259" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
@@ -7339,10 +7345,10 @@
         <v>73</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>101</v>
@@ -7353,10 +7359,10 @@
         <v>73</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>101</v>
@@ -7367,13 +7373,13 @@
         <v>73</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F262" s="4" t="s">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="F262" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
@@ -7381,16 +7387,13 @@
         <v>73</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>623</v>
+        <v>79</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D263" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F263" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
@@ -7398,13 +7401,16 @@
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>447</v>
+        <v>623</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F264" s="4" t="s">
-        <v>100</v>
+        <v>624</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -7412,41 +7418,41 @@
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>638</v>
+        <v>477</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F266" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+        <v>478</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>735</v>
+        <v>638</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="F267" s="3" t="s">
-        <v>99</v>
+        <v>639</v>
+      </c>
+      <c r="F267" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
@@ -7454,10 +7460,10 @@
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>80</v>
+        <v>735</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>88</v>
+        <v>736</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>99</v>
@@ -7468,30 +7474,27 @@
         <v>73</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>547</v>
+        <v>80</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F269" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>293</v>
+        <v>547</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F270" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G270" s="2" t="s">
-        <v>335</v>
+        <v>548</v>
+      </c>
+      <c r="F270" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="271" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7499,10 +7502,10 @@
         <v>73</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F271" s="16" t="s">
         <v>303</v>
@@ -7516,10 +7519,10 @@
         <v>73</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>239</v>
+        <v>295</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="F272" s="16" t="s">
         <v>303</v>
@@ -7528,35 +7531,38 @@
         <v>335</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F273" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="F273" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G273" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>688</v>
+        <v>230</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="F274" s="5" t="s">
-        <v>238</v>
+        <v>231</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="275" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7564,58 +7570,58 @@
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>81</v>
+        <v>688</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F275" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+        <v>689</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>739</v>
+        <v>81</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>740</v>
+        <v>89</v>
       </c>
       <c r="F276" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>443</v>
+        <v>739</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F277" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G277" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+        <v>740</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>640</v>
+        <v>443</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="F278" s="5" t="s">
-        <v>101</v>
+        <v>444</v>
+      </c>
+      <c r="F278" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G278" s="2" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
@@ -7623,44 +7629,44 @@
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>506</v>
+        <v>640</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>507</v>
+        <v>641</v>
       </c>
       <c r="F279" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>772</v>
+        <v>506</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F280" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G280" s="2" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+        <v>507</v>
+      </c>
+      <c r="F280" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>245</v>
+        <v>772</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F281" s="14" t="s">
-        <v>258</v>
+        <v>773</v>
+      </c>
+      <c r="F281" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G281" s="2" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
@@ -7668,13 +7674,13 @@
         <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F282" s="5" t="s">
-        <v>101</v>
+        <v>246</v>
+      </c>
+      <c r="F282" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
@@ -7682,13 +7688,13 @@
         <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>642</v>
+        <v>298</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F283" s="4" t="s">
-        <v>100</v>
+        <v>297</v>
+      </c>
+      <c r="F283" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
@@ -7696,13 +7702,13 @@
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>234</v>
+        <v>642</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F284" s="5" t="s">
-        <v>101</v>
+        <v>643</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
@@ -7710,10 +7716,10 @@
         <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>626</v>
+        <v>234</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>627</v>
+        <v>235</v>
       </c>
       <c r="F285" s="5" t="s">
         <v>101</v>
@@ -7724,13 +7730,13 @@
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>226</v>
+        <v>626</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F286" s="12" t="s">
-        <v>250</v>
+        <v>627</v>
+      </c>
+      <c r="F286" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -7738,13 +7744,13 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>523</v>
+        <v>226</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F287" s="14" t="s">
-        <v>258</v>
+        <v>227</v>
+      </c>
+      <c r="F287" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
@@ -7752,16 +7758,13 @@
         <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F288" s="5" t="s">
-        <v>101</v>
+        <v>524</v>
+      </c>
+      <c r="F288" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -7769,44 +7772,44 @@
         <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>224</v>
+        <v>521</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>225</v>
+        <v>522</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="F289" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>644</v>
+        <v>224</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F290" s="20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F291" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G291" s="2" t="s">
-        <v>586</v>
+        <v>645</v>
+      </c>
+      <c r="F291" s="20" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7814,81 +7817,81 @@
         <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G292" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A293" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B293" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="C293" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="F292" s="16" t="s">
+      <c r="F293" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="G292" s="2" t="s">
+      <c r="G293" s="2" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A293" s="17" t="s">
+    <row r="294" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A294" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B293" s="17" t="s">
+      <c r="B294" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C293" s="17" t="s">
+      <c r="C294" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D293" s="17"/>
-      <c r="E293" s="17"/>
-      <c r="F293" s="20" t="s">
+      <c r="D294" s="17"/>
+      <c r="E294" s="17"/>
+      <c r="F294" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G293" s="17"/>
-    </row>
-    <row r="294" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A294" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D294" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F294" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G294" s="17"/>
+    </row>
+    <row r="295" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>221</v>
+        <v>92</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>403</v>
+        <v>315</v>
       </c>
       <c r="F295" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>249</v>
+        <v>403</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>101</v>
@@ -7899,27 +7902,30 @@
         <v>90</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>797</v>
+        <v>247</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="F297" s="25" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F297" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>351</v>
+        <v>797</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F298" s="4" t="s">
-        <v>100</v>
+        <v>798</v>
+      </c>
+      <c r="F298" s="25" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.35">
@@ -7927,36 +7933,50 @@
         <v>90</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>563</v>
+        <v>351</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="D299" s="2" t="s">
-        <v>565</v>
+        <v>352</v>
       </c>
       <c r="F299" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A300" s="17" t="s">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A300" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B300" s="17" t="s">
+      <c r="B300" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A301" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B301" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C300" s="17" t="s">
+      <c r="C301" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D300" s="17" t="s">
+      <c r="D301" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E300" s="17"/>
-      <c r="F300" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G300" s="17"/>
+      <c r="E301" s="17"/>
+      <c r="F301" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G301" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730C44AC-7D31-4302-9A0A-C633B8634610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689CA091-282C-434F-9EC8-B18750BFFC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="833">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2525,6 +2525,12 @@
   </si>
   <si>
     <t>Battery Pack Markup</t>
+  </si>
+  <si>
+    <t>BPPM</t>
+  </si>
+  <si>
+    <t>Battery Pack Price Multiplier</t>
   </si>
 </sst>
 </file>
@@ -3336,7 +3342,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:G302"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -7230,13 +7236,13 @@
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>621</v>
+        <v>831</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="F252" s="5" t="s">
-        <v>101</v>
+        <v>832</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
@@ -7244,13 +7250,13 @@
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>814</v>
+        <v>621</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="F253" s="3" t="s">
-        <v>99</v>
+        <v>622</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
@@ -7258,10 +7264,10 @@
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>705</v>
+        <v>814</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>706</v>
+        <v>815</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>99</v>
@@ -7272,10 +7278,10 @@
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>636</v>
+        <v>705</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>637</v>
+        <v>706</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>99</v>
@@ -7286,10 +7292,10 @@
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>99</v>
@@ -7300,13 +7306,13 @@
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F257" s="4" t="s">
-        <v>100</v>
+        <v>609</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
@@ -7314,44 +7320,44 @@
         <v>73</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>241</v>
+        <v>588</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>242</v>
+        <v>589</v>
       </c>
       <c r="F258" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F259" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G259" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>76</v>
+        <v>285</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F260" s="5" t="s">
-        <v>101</v>
+        <v>286</v>
+      </c>
+      <c r="F260" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
@@ -7359,10 +7365,10 @@
         <v>73</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>101</v>
@@ -7373,10 +7379,10 @@
         <v>73</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>101</v>
@@ -7387,13 +7393,13 @@
         <v>73</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F263" s="4" t="s">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="F263" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
@@ -7401,16 +7407,13 @@
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>623</v>
+        <v>79</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F264" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -7418,13 +7421,16 @@
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>447</v>
+        <v>623</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F265" s="4" t="s">
-        <v>100</v>
+        <v>624</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
@@ -7432,41 +7438,41 @@
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>638</v>
+        <v>477</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F267" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+        <v>478</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>735</v>
+        <v>638</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="F268" s="3" t="s">
-        <v>99</v>
+        <v>639</v>
+      </c>
+      <c r="F268" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
@@ -7474,10 +7480,10 @@
         <v>73</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>80</v>
+        <v>735</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>88</v>
+        <v>736</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>99</v>
@@ -7488,30 +7494,27 @@
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>547</v>
+        <v>80</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F270" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>293</v>
+        <v>547</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F271" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G271" s="2" t="s">
-        <v>335</v>
+        <v>548</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="272" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7519,10 +7522,10 @@
         <v>73</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F272" s="16" t="s">
         <v>303</v>
@@ -7536,10 +7539,10 @@
         <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>239</v>
+        <v>295</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="F273" s="16" t="s">
         <v>303</v>
@@ -7548,35 +7551,38 @@
         <v>335</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F274" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="F274" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G274" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>688</v>
+        <v>230</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="F275" s="5" t="s">
-        <v>238</v>
+        <v>231</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7584,58 +7590,58 @@
         <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>81</v>
+        <v>688</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F276" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+        <v>689</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>739</v>
+        <v>81</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>740</v>
+        <v>89</v>
       </c>
       <c r="F277" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>443</v>
+        <v>739</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F278" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G278" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+        <v>740</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>640</v>
+        <v>443</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="F279" s="5" t="s">
-        <v>101</v>
+        <v>444</v>
+      </c>
+      <c r="F279" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
@@ -7643,44 +7649,44 @@
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>506</v>
+        <v>640</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>507</v>
+        <v>641</v>
       </c>
       <c r="F280" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>772</v>
+        <v>506</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F281" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G281" s="2" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+        <v>507</v>
+      </c>
+      <c r="F281" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>245</v>
+        <v>772</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F282" s="14" t="s">
-        <v>258</v>
+        <v>773</v>
+      </c>
+      <c r="F282" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
@@ -7688,13 +7694,13 @@
         <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F283" s="5" t="s">
-        <v>101</v>
+        <v>246</v>
+      </c>
+      <c r="F283" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
@@ -7702,13 +7708,13 @@
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>642</v>
+        <v>298</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F284" s="4" t="s">
-        <v>100</v>
+        <v>297</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
@@ -7716,13 +7722,13 @@
         <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>234</v>
+        <v>642</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F285" s="5" t="s">
-        <v>101</v>
+        <v>643</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
@@ -7730,10 +7736,10 @@
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>626</v>
+        <v>234</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>627</v>
+        <v>235</v>
       </c>
       <c r="F286" s="5" t="s">
         <v>101</v>
@@ -7744,13 +7750,13 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>226</v>
+        <v>626</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F287" s="12" t="s">
-        <v>250</v>
+        <v>627</v>
+      </c>
+      <c r="F287" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
@@ -7758,13 +7764,13 @@
         <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>523</v>
+        <v>226</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F288" s="14" t="s">
-        <v>258</v>
+        <v>227</v>
+      </c>
+      <c r="F288" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -7772,16 +7778,13 @@
         <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F289" s="5" t="s">
-        <v>101</v>
+        <v>524</v>
+      </c>
+      <c r="F289" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -7789,44 +7792,44 @@
         <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>224</v>
+        <v>521</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>225</v>
+        <v>522</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="F290" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>644</v>
+        <v>224</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F291" s="20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="F291" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F292" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G292" s="2" t="s">
-        <v>586</v>
+        <v>645</v>
+      </c>
+      <c r="F292" s="20" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7834,81 +7837,81 @@
         <v>73</v>
       </c>
       <c r="B293" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A294" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B294" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="C293" s="2" t="s">
+      <c r="C294" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="F293" s="16" t="s">
+      <c r="F294" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="G293" s="2" t="s">
+      <c r="G294" s="2" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A294" s="17" t="s">
+    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A295" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B294" s="17" t="s">
+      <c r="B295" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C294" s="17" t="s">
+      <c r="C295" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D294" s="17"/>
-      <c r="E294" s="17"/>
-      <c r="F294" s="20" t="s">
+      <c r="D295" s="17"/>
+      <c r="E295" s="17"/>
+      <c r="F295" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G294" s="17"/>
-    </row>
-    <row r="295" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A295" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F295" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G295" s="17"/>
+    </row>
+    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>221</v>
+        <v>92</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>403</v>
+        <v>315</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>249</v>
+        <v>403</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>101</v>
@@ -7919,27 +7922,30 @@
         <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>797</v>
+        <v>247</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="F298" s="25" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F298" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>351</v>
+        <v>797</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F299" s="4" t="s">
-        <v>100</v>
+        <v>798</v>
+      </c>
+      <c r="F299" s="25" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.35">
@@ -7947,36 +7953,50 @@
         <v>90</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>563</v>
+        <v>351</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>565</v>
+        <v>352</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A301" s="17" t="s">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A301" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B301" s="17" t="s">
+      <c r="B301" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A302" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B302" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C301" s="17" t="s">
+      <c r="C302" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D301" s="17" t="s">
+      <c r="D302" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E301" s="17"/>
-      <c r="F301" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G301" s="17"/>
+      <c r="E302" s="17"/>
+      <c r="F302" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G302" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E448F18-0DCE-4DF2-A042-1AAB7EF5E9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0106C665-AB98-46AA-99A6-AC85633E64FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="3750" windowWidth="25275" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4275" yWindow="-13455" windowWidth="17325" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -1537,12 +1537,6 @@
     <t>You wish to switch from the BAU plant retirement schedule to an alternative schedule you have specified in input data (rather than using the early retirement policy lever, which accelerates retirements and is additive to the BAU retirements)</t>
   </si>
   <si>
-    <t>IFStFS</t>
-  </si>
-  <si>
-    <t>Industrial Fuels Subject to Fuel Shifting</t>
-  </si>
-  <si>
     <t>You wish for the industrial fuel shifting policy lever to affect a different set of source (BAU) fuel types than the default set (which consists of the fossil fuels).</t>
   </si>
   <si>
@@ -2621,6 +2615,12 @@
   </si>
   <si>
     <t>CCS Retrofit Deployment Time</t>
+  </si>
+  <si>
+    <t>IFStE</t>
+  </si>
+  <si>
+    <t>Industrial Fuels Subject to Electrification</t>
   </si>
 </sst>
 </file>
@@ -3102,82 +3102,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>97</v>
       </c>
@@ -3185,32 +3185,32 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
         <v>244</v>
       </c>
@@ -3218,17 +3218,17 @@
         <v>247</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>99</v>
       </c>
@@ -3236,42 +3236,42 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>98</v>
       </c>
@@ -3279,84 +3279,84 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="15" t="s">
         <v>252</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="11" t="s">
         <v>140</v>
       </c>
@@ -3364,62 +3364,62 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3433,19 +3433,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G316"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.1796875" style="2" customWidth="1"/>
     <col min="4" max="4" width="67" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="2" customWidth="1"/>
     <col min="7" max="7" width="54" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="2"/>
+    <col min="8" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -3468,15 +3468,15 @@
         <v>306</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -3484,27 +3484,27 @@
         <v>97</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -3518,24 +3518,24 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>140</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="17" t="s">
         <v>4</v>
       </c>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="G7" s="17"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -3594,21 +3594,21 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -3625,21 +3625,21 @@
         <v>304</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -3670,24 +3670,24 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -3788,21 +3788,21 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
@@ -3895,21 +3895,21 @@
         <v>343</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="17" t="s">
         <v>9</v>
       </c>
@@ -4018,52 +4018,52 @@
       </c>
       <c r="G37" s="17"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="F39" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
@@ -4074,13 +4074,13 @@
         <v>404</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
@@ -4091,114 +4091,114 @@
         <v>397</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="F46" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F49" s="20" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>170</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="17" t="s">
         <v>170</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="17" t="s">
         <v>472</v>
       </c>
@@ -4247,10 +4247,10 @@
         <v>140</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>400</v>
       </c>
@@ -4267,24 +4267,24 @@
         <v>318</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>400</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>400</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>400</v>
       </c>
@@ -4335,24 +4335,24 @@
         <v>321</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>400</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>400</v>
       </c>
@@ -4386,41 +4386,41 @@
         <v>497</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>400</v>
       </c>
@@ -4437,24 +4437,24 @@
         <v>320</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>400</v>
       </c>
@@ -4468,24 +4468,24 @@
         <v>99</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2" t="s">
         <v>400</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="F66" s="22" t="s">
         <v>178</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="17" t="s">
         <v>400</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>452</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E67" s="17"/>
       <c r="F67" s="22" t="s">
@@ -4506,7 +4506,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>38</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>38</v>
       </c>
@@ -4534,21 +4534,21 @@
         <v>97</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>38</v>
       </c>
@@ -4562,21 +4562,21 @@
         <v>98</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="17" t="s">
         <v>38</v>
       </c>
@@ -4595,52 +4595,52 @@
         <v>374</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>772</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
@@ -4648,16 +4648,16 @@
         <v>179</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>43</v>
       </c>
@@ -4671,38 +4671,38 @@
         <v>97</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
@@ -4719,24 +4719,24 @@
         <v>308</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>43</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>43</v>
       </c>
@@ -4767,63 +4767,63 @@
         <v>310</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="F85" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>199</v>
@@ -4832,35 +4832,35 @@
         <v>97</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
@@ -4874,21 +4874,21 @@
         <v>97</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
@@ -4899,27 +4899,27 @@
         <v>52</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
@@ -4936,52 +4936,52 @@
         <v>500</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
@@ -4995,21 +4995,21 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>43</v>
       </c>
@@ -5020,13 +5020,13 @@
         <v>169</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>43</v>
       </c>
@@ -5043,24 +5043,24 @@
         <v>98</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
@@ -5077,66 +5077,66 @@
         <v>97</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
@@ -5147,13 +5147,13 @@
         <v>477</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
@@ -5170,130 +5170,130 @@
         <v>309</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>752</v>
-      </c>
       <c r="F111" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B112" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>753</v>
-      </c>
       <c r="F112" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>43</v>
       </c>
@@ -5338,58 +5338,58 @@
         <v>311</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>100</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F125" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
@@ -5403,21 +5403,21 @@
         <v>98</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>43</v>
       </c>
@@ -5434,52 +5434,52 @@
         <v>326</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="D129" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="F129" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="B131" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F131" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
@@ -5496,139 +5496,139 @@
         <v>98</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F133" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>722</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="17" t="s">
         <v>43</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>269</v>
       </c>
@@ -5660,13 +5660,13 @@
         <v>264</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>269</v>
       </c>
@@ -5677,13 +5677,13 @@
         <v>268</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>269</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>269</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>269</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>269</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="17" t="s">
         <v>269</v>
       </c>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="G149" s="17"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
@@ -5770,49 +5770,49 @@
         <v>97</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>55</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>55</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>55</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
@@ -5874,94 +5874,94 @@
         <v>99</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>55</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>55</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>55</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>55</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>55</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>55</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>55</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="172" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="17" t="s">
         <v>55</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>391</v>
       </c>
@@ -6125,24 +6125,24 @@
         <v>97</v>
       </c>
     </row>
-    <row r="174" spans="1:7" s="17" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="17" t="s">
+        <v>740</v>
+      </c>
+      <c r="B174" s="17" t="s">
+        <v>741</v>
+      </c>
+      <c r="C174" s="17" t="s">
         <v>742</v>
       </c>
-      <c r="B174" s="17" t="s">
+      <c r="D174" s="17" t="s">
         <v>743</v>
-      </c>
-      <c r="C174" s="17" t="s">
-        <v>744</v>
-      </c>
-      <c r="D174" s="17" t="s">
-        <v>745</v>
       </c>
       <c r="F174" s="19" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>344</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>344</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>344</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>344</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>344</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>344</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="181" spans="1:7" s="17" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="17" t="s">
         <v>344</v>
       </c>
@@ -6249,131 +6249,131 @@
         <v>362</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="D182" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="C182" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>812</v>
-      </c>
       <c r="F182" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="F183" s="16" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="F184" s="16" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="C187" s="2" t="s">
-        <v>795</v>
-      </c>
       <c r="D187" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="F187" s="12" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D188" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="F188" s="14" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D189" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>650</v>
       </c>
       <c r="F189" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>63</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
@@ -6401,21 +6401,21 @@
         <v>99</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="F192" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>63</v>
       </c>
@@ -6432,159 +6432,159 @@
         <v>332</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F194" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="F196" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>501</v>
+        <v>861</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>502</v>
+        <v>862</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>100</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>63</v>
       </c>
@@ -6598,27 +6598,27 @@
         <v>98</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="D205" s="2" t="s">
         <v>842</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>844</v>
       </c>
       <c r="F205" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>63</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>63</v>
       </c>
@@ -6649,35 +6649,35 @@
         <v>98</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F209" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>63</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>63</v>
       </c>
@@ -6705,21 +6705,21 @@
         <v>98</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F212" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>63</v>
       </c>
@@ -6733,15 +6733,15 @@
         <v>98</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="17" t="s">
         <v>63</v>
       </c>
       <c r="B214" s="17" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C214" s="17" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D214" s="17"/>
       <c r="E214" s="17"/>
@@ -6750,55 +6750,55 @@
       </c>
       <c r="G214" s="17"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D216" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>407</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>407</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>407</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>407</v>
       </c>
@@ -6854,18 +6854,18 @@
         <v>97</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B222" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C222" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="C222" s="2" t="s">
-        <v>600</v>
-      </c>
       <c r="D222" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>421</v>
@@ -6874,7 +6874,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>407</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>407</v>
       </c>
@@ -6902,24 +6902,24 @@
         <v>97</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F225" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>407</v>
       </c>
@@ -6934,24 +6934,24 @@
       </c>
       <c r="F226" s="3"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F227" s="6" t="s">
         <v>140</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>407</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>407</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>407</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>407</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>407</v>
       </c>
@@ -7024,21 +7024,21 @@
         <v>99</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>407</v>
       </c>
@@ -7052,24 +7052,24 @@
         <v>291</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="2" t="s">
         <v>407</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F235" s="19" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="17" t="s">
         <v>407</v>
       </c>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="G236" s="17"/>
     </row>
-    <row r="237" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>91</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>91</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>91</v>
       </c>
@@ -7131,7 +7131,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>91</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>91</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>91</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>91</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>91</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="17" t="s">
         <v>91</v>
       </c>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G245" s="17"/>
     </row>
-    <row r="246" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>68</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>68</v>
       </c>
@@ -7252,27 +7252,27 @@
         <v>140</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="F248" s="6" t="s">
         <v>140</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="17" t="s">
         <v>68</v>
       </c>
@@ -7291,35 +7291,35 @@
         <v>324</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>71</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>71</v>
       </c>
@@ -7347,21 +7347,21 @@
         <v>99</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F254" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>71</v>
       </c>
@@ -7375,35 +7375,35 @@
         <v>98</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F256" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>71</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="259" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>71</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="260" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>71</v>
       </c>
@@ -7448,49 +7448,49 @@
         <v>99</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>71</v>
       </c>
@@ -7504,7 +7504,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>71</v>
       </c>
@@ -7518,108 +7518,108 @@
         <v>99</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B266" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D266" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="C266" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>621</v>
-      </c>
       <c r="F266" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F267" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F272" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>71</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>71</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>71</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>71</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>71</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>71</v>
       </c>
@@ -7706,24 +7706,24 @@
         <v>98</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B279" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="D279" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="C279" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>611</v>
-      </c>
       <c r="F279" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>71</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>71</v>
       </c>
@@ -7751,35 +7751,35 @@
         <v>98</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F282" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>71</v>
       </c>
@@ -7793,21 +7793,21 @@
         <v>97</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F285" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>71</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>71</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>71</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>71</v>
       </c>
@@ -7875,21 +7875,21 @@
         <v>98</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F290" s="5" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>71</v>
       </c>
@@ -7903,21 +7903,21 @@
         <v>98</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>71</v>
       </c>
@@ -7934,21 +7934,21 @@
         <v>364</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F294" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>71</v>
       </c>
@@ -7962,24 +7962,24 @@
         <v>99</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="F296" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>71</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>71</v>
       </c>
@@ -8007,21 +8007,21 @@
         <v>99</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F299" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>71</v>
       </c>
@@ -8035,21 +8035,21 @@
         <v>99</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F301" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>71</v>
       </c>
@@ -8063,29 +8063,29 @@
         <v>244</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F303" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>220</v>
@@ -8094,7 +8094,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>71</v>
       </c>
@@ -8108,55 +8108,55 @@
         <v>99</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F306" s="20" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B307" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C307" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>571</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F308" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="17" t="s">
         <v>71</v>
       </c>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="G309" s="17"/>
     </row>
-    <row r="310" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
         <v>88</v>
       </c>
@@ -8190,7 +8190,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>88</v>
       </c>
@@ -8207,7 +8207,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A312" s="2" t="s">
         <v>88</v>
       </c>
@@ -8224,21 +8224,21 @@
         <v>99</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B313" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="F313" s="25" t="s">
         <v>790</v>
       </c>
-      <c r="C313" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="F313" s="25" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" s="2" t="s">
         <v>88</v>
       </c>
@@ -8252,24 +8252,24 @@
         <v>98</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B315" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D315" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="C315" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="D315" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="F315" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="316" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A316" s="17" t="s">
         <v>88</v>
       </c>
@@ -8297,13 +8297,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="52.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8311,7 +8311,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -8327,7 +8327,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>400</v>
       </c>
@@ -8351,7 +8351,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>472</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>269</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>391</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>344</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>407</v>
       </c>
@@ -8423,7 +8423,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>91</v>
       </c>
@@ -8431,7 +8431,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -8447,7 +8447,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>88</v>
       </c>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689CA091-282C-434F-9EC8-B18750BFFC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F5458D-FD54-4D41-8C5F-134816A8CA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="835">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2531,6 +2531,12 @@
   </si>
   <si>
     <t>Battery Pack Price Multiplier</t>
+  </si>
+  <si>
+    <t>UFDfGBS</t>
+  </si>
+  <si>
+    <t>Usage Factor Discount for Grid Battery Storage</t>
   </si>
 </sst>
 </file>
@@ -3342,7 +3348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G302"/>
+  <dimension ref="A1:G303"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -5427,101 +5433,101 @@
         <v>101</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="17" t="s">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B134" s="17" t="s">
+      <c r="B134" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B135" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="C134" s="17" t="s">
+      <c r="C135" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="D134" s="17" t="s">
+      <c r="D135" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="E134" s="17"/>
-      <c r="F134" s="21" t="s">
+      <c r="E135" s="17"/>
+      <c r="F135" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="G134" s="17" t="s">
+      <c r="G135" s="17" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A135" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>630</v>
+        <v>702</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>630</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>418</v>
+        <v>271</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>183</v>
+        <v>418</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>100</v>
+        <v>419</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
@@ -5529,69 +5535,69 @@
         <v>275</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="17" t="s">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A141" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B141" s="17" t="s">
+      <c r="B141" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="B142" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C141" s="17" t="s">
+      <c r="C142" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="D141" s="17"/>
-      <c r="E141" s="17"/>
-      <c r="F141" s="20" t="s">
+      <c r="D142" s="17"/>
+      <c r="E142" s="17"/>
+      <c r="F142" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G141" s="17"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A142" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G142" s="17"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>785</v>
+        <v>470</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+        <v>471</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>101</v>
@@ -5602,10 +5608,10 @@
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>101</v>
@@ -5616,16 +5622,13 @@
         <v>55</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>472</v>
+        <v>787</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="F146" s="3" t="s">
-        <v>99</v>
+        <v>790</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
@@ -5633,69 +5636,72 @@
         <v>55</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>380</v>
+        <v>472</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>381</v>
+        <v>473</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>474</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>56</v>
+        <v>380</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>268</v>
+        <v>381</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>313</v>
+        <v>56</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>776</v>
+        <v>313</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>777</v>
+        <v>314</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>628</v>
+        <v>776</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>629</v>
+        <v>777</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>101</v>
@@ -5706,13 +5712,10 @@
         <v>55</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>525</v>
+        <v>628</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>526</v>
+        <v>629</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>101</v>
@@ -5723,10 +5726,13 @@
         <v>55</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>791</v>
+        <v>525</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>778</v>
+        <v>792</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>526</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>101</v>
@@ -5737,13 +5743,13 @@
         <v>55</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>542</v>
+        <v>791</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>99</v>
+        <v>778</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
@@ -5751,61 +5757,58 @@
         <v>55</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>606</v>
+        <v>542</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F155" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>543</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>57</v>
+        <v>606</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+        <v>607</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>311</v>
+        <v>57</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>390</v>
+        <v>311</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F158" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>396</v>
+        <v>312</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5813,16 +5816,16 @@
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F159" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -5830,129 +5833,132 @@
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F160" s="16" t="s">
         <v>303</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>58</v>
+        <v>392</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+      <c r="F161" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>376</v>
+        <v>58</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>340</v>
+        <v>61</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F162" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B163" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C164" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="F163" s="3" t="s">
+      <c r="F164" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="164" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="17" t="s">
+    <row r="165" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A165" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B164" s="17" t="s">
+      <c r="B165" s="17" t="s">
         <v>441</v>
       </c>
-      <c r="C164" s="17" t="s">
+      <c r="C165" s="17" t="s">
         <v>442</v>
       </c>
-      <c r="F164" s="22" t="s">
+      <c r="F165" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G164" s="17" t="s">
+      <c r="G165" s="17" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A165" s="2" t="s">
+    <row r="166" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A166" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="B166" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C166" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D165" s="2" t="s">
+      <c r="D166" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="F165" s="3" t="s">
+      <c r="F166" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="166" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="17" t="s">
+    <row r="167" spans="1:7" s="17" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="17" t="s">
         <v>754</v>
       </c>
-      <c r="B166" s="17" t="s">
+      <c r="B167" s="17" t="s">
         <v>755</v>
       </c>
-      <c r="C166" s="17" t="s">
+      <c r="C167" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="D166" s="17" t="s">
+      <c r="D167" s="17" t="s">
         <v>757</v>
       </c>
-      <c r="F166" s="19" t="s">
+      <c r="F167" s="19" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A167" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
@@ -5960,13 +5966,13 @@
         <v>357</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F168" s="4" t="s">
-        <v>100</v>
+        <v>366</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
@@ -5974,27 +5980,24 @@
         <v>357</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>100</v>
@@ -6005,45 +6008,47 @@
         <v>357</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F172" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G172" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>370</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>807</v>
+        <v>364</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="F173" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="G173" s="2" t="s">
-        <v>809</v>
+        <v>374</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6051,64 +6056,62 @@
         <v>357</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="F174" s="6"/>
+      <c r="G174" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A175" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B175" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C174" s="2" t="s">
+      <c r="C175" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="F174" s="6" t="s">
+      <c r="F175" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G174" s="2" t="s">
+      <c r="G175" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="17" t="s">
+    <row r="176" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A176" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B175" s="17" t="s">
+      <c r="B176" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="C175" s="17" t="s">
+      <c r="C176" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="D175" s="17"/>
-      <c r="E175" s="17"/>
-      <c r="F175" s="20" t="s">
+      <c r="D176" s="17"/>
+      <c r="E176" s="17"/>
+      <c r="F176" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G175" s="17"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A176" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F176" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G176" s="17"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>518</v>
+        <v>206</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="F177" s="14" t="s">
-        <v>400</v>
+        <v>207</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6116,16 +6119,16 @@
         <v>63</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>661</v>
+        <v>518</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>662</v>
+        <v>519</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="F178" s="4" t="s">
-        <v>100</v>
+        <v>520</v>
+      </c>
+      <c r="F178" s="14" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6133,19 +6136,16 @@
         <v>63</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>197</v>
+        <v>661</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F179" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G179" s="2" t="s">
-        <v>339</v>
+        <v>662</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6153,13 +6153,19 @@
         <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>326</v>
+        <v>197</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>101</v>
+        <v>198</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F180" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6167,27 +6173,27 @@
         <v>63</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>64</v>
+        <v>326</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F181" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+        <v>327</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>496</v>
+        <v>64</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>101</v>
+        <v>67</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
@@ -6195,16 +6201,13 @@
         <v>63</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>65</v>
+        <v>496</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F183" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G183" s="2" t="s">
-        <v>345</v>
+        <v>497</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
@@ -6212,13 +6215,16 @@
         <v>63</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>561</v>
+        <v>65</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>101</v>
+        <v>68</v>
+      </c>
+      <c r="F184" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6226,13 +6232,13 @@
         <v>63</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>760</v>
+        <v>561</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="F185" s="4" t="s">
-        <v>100</v>
+        <v>562</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
@@ -6240,64 +6246,58 @@
         <v>63</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="F186" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>515</v>
+        <v>766</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F187" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G187" s="2" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+        <v>767</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>199</v>
+        <v>515</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F188" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>516</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>810</v>
+        <v>199</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="F189" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>813</v>
+        <v>200</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6305,44 +6305,50 @@
         <v>63</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>66</v>
+        <v>810</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>69</v>
+        <v>811</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F190" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+        <v>812</v>
+      </c>
+      <c r="F190" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F191" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F191" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>277</v>
+        <v>190</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F192" s="5" t="s">
-        <v>101</v>
+        <v>191</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6350,10 +6356,10 @@
         <v>63</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>101</v>
@@ -6364,13 +6370,13 @@
         <v>63</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F194" s="4" t="s">
-        <v>100</v>
+        <v>281</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6378,103 +6384,100 @@
         <v>63</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>566</v>
+        <v>279</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F195" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>476</v>
+        <v>566</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>567</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="17" t="s">
+    <row r="198" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A198" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B198" s="17" t="s">
+      <c r="B198" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A199" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B199" s="17" t="s">
         <v>494</v>
       </c>
-      <c r="C198" s="17" t="s">
+      <c r="C199" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="D198" s="17"/>
-      <c r="E198" s="17"/>
-      <c r="F198" s="20" t="s">
+      <c r="D199" s="17"/>
+      <c r="E199" s="17"/>
+      <c r="F199" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G198" s="17"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A199" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="F199" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G199" s="17"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>558</v>
+        <v>793</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>560</v>
+        <v>794</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>708</v>
+        <v>558</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>709</v>
+        <v>559</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>707</v>
+        <v>560</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>99</v>
@@ -6485,10 +6488,13 @@
         <v>420</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>428</v>
+        <v>708</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>429</v>
+        <v>709</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>707</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>99</v>
@@ -6499,10 +6505,10 @@
         <v>420</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>99</v>
@@ -6513,10 +6519,10 @@
         <v>420</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>99</v>
@@ -6527,44 +6533,44 @@
         <v>420</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>612</v>
+        <v>432</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>99</v>
@@ -6575,30 +6581,27 @@
         <v>420</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>529</v>
+        <v>422</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F209" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G209" s="2" t="s">
-        <v>531</v>
+        <v>424</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6606,48 +6609,48 @@
         <v>420</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>479</v>
+        <v>529</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="F210" s="3"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+      <c r="F210" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>527</v>
+        <v>479</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F211" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G211" s="2" t="s">
-        <v>532</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F211" s="3"/>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F212" s="3" t="s">
-        <v>99</v>
+        <v>528</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
@@ -6655,13 +6658,16 @@
         <v>420</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="F213" s="5" t="s">
-        <v>101</v>
+        <v>503</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
@@ -6669,10 +6675,10 @@
         <v>420</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>101</v>
@@ -6683,10 +6689,10 @@
         <v>420</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>423</v>
+        <v>466</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>425</v>
+        <v>467</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>101</v>
@@ -6697,10 +6703,10 @@
         <v>420</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>468</v>
+        <v>423</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>101</v>
@@ -6711,106 +6717,106 @@
         <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>540</v>
+        <v>468</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F217" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>469</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>426</v>
+        <v>540</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F218" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G218" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>541</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F219" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A220" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B220" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="C219" s="2" t="s">
+      <c r="C220" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="F219" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A220" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="B220" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="C220" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="D220" s="17"/>
-      <c r="E220" s="17"/>
       <c r="F220" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="G220" s="17"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A221" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F221" s="5" t="s">
-        <v>101</v>
-      </c>
+    </row>
+    <row r="221" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A221" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B221" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="C221" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="D221" s="17"/>
+      <c r="E221" s="17"/>
+      <c r="F221" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G221" s="17"/>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>304</v>
+        <v>209</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F222" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+      <c r="F222" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>211</v>
+        <v>304</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F223" s="5" t="s">
-        <v>101</v>
+        <v>305</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="224" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -6818,30 +6824,30 @@
         <v>93</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F224" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G224" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F225" s="5" t="s">
-        <v>101</v>
+        <v>214</v>
+      </c>
+      <c r="F225" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
@@ -6849,10 +6855,10 @@
         <v>93</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>101</v>
@@ -6863,128 +6869,128 @@
         <v>93</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>216</v>
+        <v>94</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A229" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B229" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C228" s="2" t="s">
+      <c r="C229" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F228" s="12" t="s">
+      <c r="F229" s="12" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A229" s="17" t="s">
+    <row r="230" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A230" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B229" s="17" t="s">
+      <c r="B230" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C229" s="17" t="s">
+      <c r="C230" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D229" s="17"/>
-      <c r="E229" s="17"/>
-      <c r="F229" s="20" t="s">
+      <c r="D230" s="17"/>
+      <c r="E230" s="17"/>
+      <c r="F230" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G229" s="17"/>
-    </row>
-    <row r="230" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A230" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F230" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G230" s="2" t="s">
-        <v>331</v>
-      </c>
+      <c r="G230" s="17"/>
     </row>
     <row r="231" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>192</v>
+        <v>71</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>741</v>
+        <v>192</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>742</v>
+        <v>194</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>142</v>
       </c>
       <c r="G232" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A233" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="F233" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G233" s="2" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A233" s="17" t="s">
+    <row r="234" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A234" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B233" s="17" t="s">
+      <c r="B234" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C233" s="17" t="s">
+      <c r="C234" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="D233" s="17"/>
-      <c r="E233" s="17"/>
-      <c r="F233" s="22" t="s">
+      <c r="D234" s="17"/>
+      <c r="E234" s="17"/>
+      <c r="F234" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G233" s="17" t="s">
+      <c r="G234" s="17" t="s">
         <v>336</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A234" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="F234" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
@@ -6992,13 +6998,13 @@
         <v>73</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>549</v>
+        <v>631</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F235" s="5" t="s">
-        <v>101</v>
+        <v>632</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
@@ -7006,13 +7012,13 @@
         <v>73</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>74</v>
+        <v>549</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F236" s="4" t="s">
-        <v>100</v>
+        <v>550</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -7020,41 +7026,41 @@
         <v>73</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>553</v>
+        <v>75</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>554</v>
+        <v>83</v>
       </c>
       <c r="F238" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>411</v>
+        <v>553</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F239" s="4" t="s">
-        <v>100</v>
+        <v>554</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
@@ -7062,10 +7068,10 @@
         <v>73</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>674</v>
+        <v>411</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>675</v>
+        <v>412</v>
       </c>
       <c r="F240" s="4" t="s">
         <v>100</v>
@@ -7076,13 +7082,13 @@
         <v>73</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>551</v>
+        <v>674</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="F241" s="5" t="s">
-        <v>101</v>
+        <v>675</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
@@ -7090,13 +7096,13 @@
         <v>73</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>283</v>
+        <v>551</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>99</v>
+        <v>552</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
@@ -7104,44 +7110,44 @@
         <v>73</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="244" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F244" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>795</v>
+        <v>236</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="F245" s="3" t="s">
-        <v>99</v>
+        <v>237</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
@@ -7149,13 +7155,13 @@
         <v>73</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>617</v>
+        <v>795</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="F246" s="5" t="s">
-        <v>101</v>
+        <v>796</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
@@ -7163,10 +7169,10 @@
         <v>73</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F247" s="5" t="s">
         <v>101</v>
@@ -7177,10 +7183,10 @@
         <v>73</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>232</v>
+        <v>619</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>233</v>
+        <v>620</v>
       </c>
       <c r="F248" s="5" t="s">
         <v>101</v>
@@ -7191,10 +7197,10 @@
         <v>73</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>101</v>
@@ -7205,13 +7211,13 @@
         <v>73</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>829</v>
+        <v>228</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="F250" s="4" t="s">
-        <v>100</v>
+        <v>229</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.35">
@@ -7219,16 +7225,13 @@
         <v>73</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>633</v>
+        <v>829</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F251" s="5" t="s">
-        <v>101</v>
+        <v>830</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
@@ -7236,13 +7239,16 @@
         <v>73</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>831</v>
+        <v>633</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="F252" s="4" t="s">
-        <v>100</v>
+        <v>634</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
@@ -7250,13 +7256,13 @@
         <v>73</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>621</v>
+        <v>831</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="F253" s="5" t="s">
-        <v>101</v>
+        <v>832</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
@@ -7264,13 +7270,13 @@
         <v>73</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>814</v>
+        <v>621</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="F254" s="3" t="s">
-        <v>99</v>
+        <v>622</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
@@ -7278,10 +7284,10 @@
         <v>73</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>705</v>
+        <v>814</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>706</v>
+        <v>815</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>99</v>
@@ -7292,10 +7298,10 @@
         <v>73</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>636</v>
+        <v>705</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>637</v>
+        <v>706</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>99</v>
@@ -7306,10 +7312,10 @@
         <v>73</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>99</v>
@@ -7320,13 +7326,13 @@
         <v>73</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F258" s="4" t="s">
-        <v>100</v>
+        <v>609</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
@@ -7334,44 +7340,44 @@
         <v>73</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>241</v>
+        <v>588</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>242</v>
+        <v>589</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F260" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>76</v>
+        <v>285</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F261" s="5" t="s">
-        <v>101</v>
+        <v>286</v>
+      </c>
+      <c r="F261" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
@@ -7379,10 +7385,10 @@
         <v>73</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>101</v>
@@ -7393,10 +7399,10 @@
         <v>73</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>101</v>
@@ -7407,13 +7413,13 @@
         <v>73</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F264" s="4" t="s">
-        <v>100</v>
+        <v>86</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
@@ -7421,16 +7427,13 @@
         <v>73</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>623</v>
+        <v>79</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F265" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
@@ -7438,13 +7441,16 @@
         <v>73</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>447</v>
+        <v>623</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F266" s="4" t="s">
-        <v>100</v>
+        <v>624</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F266" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
@@ -7452,41 +7458,41 @@
         <v>73</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>638</v>
+        <v>477</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+        <v>478</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>735</v>
+        <v>638</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="F269" s="3" t="s">
-        <v>99</v>
+        <v>639</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
@@ -7494,10 +7500,10 @@
         <v>73</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>80</v>
+        <v>735</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>88</v>
+        <v>736</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>99</v>
@@ -7508,30 +7514,27 @@
         <v>73</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>547</v>
+        <v>80</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>293</v>
+        <v>547</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F272" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G272" s="2" t="s">
-        <v>335</v>
+        <v>548</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -7539,10 +7542,10 @@
         <v>73</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F273" s="16" t="s">
         <v>303</v>
@@ -7556,10 +7559,10 @@
         <v>73</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>239</v>
+        <v>295</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="F274" s="16" t="s">
         <v>303</v>
@@ -7568,35 +7571,38 @@
         <v>335</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F275" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="F275" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>688</v>
+        <v>230</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="F276" s="5" t="s">
-        <v>238</v>
+        <v>231</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -7604,58 +7610,58 @@
         <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>81</v>
+        <v>688</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F277" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+        <v>689</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>739</v>
+        <v>81</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>740</v>
+        <v>89</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>443</v>
+        <v>739</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F279" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G279" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+        <v>740</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>640</v>
+        <v>443</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="F280" s="5" t="s">
-        <v>101</v>
+        <v>444</v>
+      </c>
+      <c r="F280" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
@@ -7663,44 +7669,44 @@
         <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>506</v>
+        <v>640</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>507</v>
+        <v>641</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>772</v>
+        <v>506</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F282" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="G282" s="2" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+        <v>507</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>245</v>
+        <v>772</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F283" s="14" t="s">
-        <v>258</v>
+        <v>773</v>
+      </c>
+      <c r="F283" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
@@ -7708,13 +7714,13 @@
         <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F284" s="5" t="s">
-        <v>101</v>
+        <v>246</v>
+      </c>
+      <c r="F284" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
@@ -7722,13 +7728,13 @@
         <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>642</v>
+        <v>298</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>100</v>
+        <v>297</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
@@ -7736,13 +7742,13 @@
         <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>234</v>
+        <v>642</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F286" s="5" t="s">
-        <v>101</v>
+        <v>643</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -7750,10 +7756,10 @@
         <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>626</v>
+        <v>234</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>627</v>
+        <v>235</v>
       </c>
       <c r="F287" s="5" t="s">
         <v>101</v>
@@ -7764,13 +7770,13 @@
         <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>226</v>
+        <v>626</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F288" s="12" t="s">
-        <v>250</v>
+        <v>627</v>
+      </c>
+      <c r="F288" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
@@ -7778,13 +7784,13 @@
         <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>523</v>
+        <v>226</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F289" s="14" t="s">
-        <v>258</v>
+        <v>227</v>
+      </c>
+      <c r="F289" s="12" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -7792,16 +7798,13 @@
         <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F290" s="5" t="s">
-        <v>101</v>
+        <v>524</v>
+      </c>
+      <c r="F290" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -7809,44 +7812,44 @@
         <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>224</v>
+        <v>521</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>225</v>
+        <v>522</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="F291" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>644</v>
+        <v>224</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F292" s="20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="F292" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G293" s="2" t="s">
-        <v>586</v>
+        <v>645</v>
+      </c>
+      <c r="F293" s="20" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -7854,81 +7857,81 @@
         <v>73</v>
       </c>
       <c r="B294" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G294" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A295" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="C295" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="F294" s="16" t="s">
+      <c r="F295" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="G294" s="2" t="s">
+      <c r="G295" s="2" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A295" s="17" t="s">
+    <row r="296" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A296" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B295" s="17" t="s">
+      <c r="B296" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C295" s="17" t="s">
+      <c r="C296" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D295" s="17"/>
-      <c r="E295" s="17"/>
-      <c r="F295" s="20" t="s">
+      <c r="D296" s="17"/>
+      <c r="E296" s="17"/>
+      <c r="F296" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G295" s="17"/>
-    </row>
-    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A296" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F296" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G296" s="17"/>
+    </row>
+    <row r="297" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>221</v>
+        <v>92</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>403</v>
+        <v>315</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>249</v>
+        <v>403</v>
       </c>
       <c r="F298" s="5" t="s">
         <v>101</v>
@@ -7939,27 +7942,30 @@
         <v>90</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>797</v>
+        <v>247</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="F299" s="25" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>351</v>
+        <v>797</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>100</v>
+        <v>798</v>
+      </c>
+      <c r="F300" s="25" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
@@ -7967,36 +7973,50 @@
         <v>90</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>563</v>
+        <v>351</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>565</v>
+        <v>352</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A302" s="17" t="s">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A302" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B302" s="17" t="s">
+      <c r="B302" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A303" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B303" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C302" s="17" t="s">
+      <c r="C303" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D302" s="17" t="s">
+      <c r="D303" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E302" s="17"/>
-      <c r="F302" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G302" s="17"/>
+      <c r="E303" s="17"/>
+      <c r="F303" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G303" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0106C665-AB98-46AA-99A6-AC85633E64FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269C63F9-B54A-4174-91B3-9FBC835E562E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4275" yWindow="-13455" windowWidth="17325" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="1260" windowWidth="21120" windowHeight="14655" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="931">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -970,12 +970,6 @@
     <t>You are modeling a region where power plant construction decisions are based on government mandates rather than being market-driven, and you are setting this policy lever to alter the BAU mandates</t>
   </si>
   <si>
-    <t>BAEPAbCiGC</t>
-  </si>
-  <si>
-    <t>Boolean Are Electricity Prices Affected by Changes in Generating Costs</t>
-  </si>
-  <si>
     <t>BSoAIGtAP</t>
   </si>
   <si>
@@ -1021,15 +1015,6 @@
     <t>Transportation Fuel Pollutant Emissions Intensity Improvement Rate, Electricity Fuel Pollutant Emissions Intensity Improvement Rate, Buildings Fuel Pollutant Emissions Intensity Improvement Rate, Industrial Fuel Pollutant Emissions Intensity Improvement Rate</t>
   </si>
   <si>
-    <t>BENCEfCT</t>
-  </si>
-  <si>
-    <t>Boolean Exempt Non CO2 Emissions from Carbon Tax</t>
-  </si>
-  <si>
-    <t>You want carbon pricing to only apply to CO2 emissions, exempting other GHGs (such as methane) and other climate-forcing pollutants (such as black carbon)</t>
-  </si>
-  <si>
     <t>You want to estimate induced foreign emissions</t>
   </si>
   <si>
@@ -1072,57 +1057,27 @@
     <t>Hydrogen Supply</t>
   </si>
   <si>
-    <t>BHPSbP</t>
-  </si>
-  <si>
     <t>EHPpUC</t>
   </si>
   <si>
-    <t>HPEbP</t>
-  </si>
-  <si>
     <t>HPEC</t>
   </si>
   <si>
     <t>HPPECbP</t>
   </si>
   <si>
-    <t>HPtFM</t>
-  </si>
-  <si>
-    <t>RHPF</t>
-  </si>
-  <si>
-    <t>BAU Hydrogen Production Shares by Pathway</t>
-  </si>
-  <si>
     <t>Electrolyzer Hydrogen Production per Unit Capacity</t>
   </si>
   <si>
-    <t>Hydrogen Production Efficiency by Pathway</t>
-  </si>
-  <si>
     <t>Hydrogen Production Equipment Costs</t>
   </si>
   <si>
     <t>Hydrogen Production Percent Excess Capacity by Pathway</t>
   </si>
   <si>
-    <t>Hydrogen Pathway to Fuel Mappings</t>
-  </si>
-  <si>
-    <t>Recipient Hydrogen Pathway Fractions</t>
-  </si>
-  <si>
     <t>Hydrogen Production Equipment CapEx, Hydrogen Production Equipment OpEx</t>
   </si>
   <si>
-    <t>You redefine one or more hydrogen production pathways</t>
-  </si>
-  <si>
-    <t>You wish for the hydrogen pathway shifting policy to shift hydrogen production to a pathway other than electrolysis</t>
-  </si>
-  <si>
     <t>PEIIR</t>
   </si>
   <si>
@@ -1378,9 +1333,6 @@
     <t>Start Year Components Energy Use</t>
   </si>
   <si>
-    <t>HOIbTP</t>
-  </si>
-  <si>
     <t>Health Outcome Incidence per Ton Pollutant</t>
   </si>
   <si>
@@ -1588,12 +1540,6 @@
     <t>You wish to include job break-outs by union status among your model outputs.</t>
   </si>
   <si>
-    <t>FoHObDT</t>
-  </si>
-  <si>
-    <t>Fraction of Health Outcomes by Demographic Trait</t>
-  </si>
-  <si>
     <t>You wish to include premature mortality break-outs by sex, race, or ethnicity among your model outputs.</t>
   </si>
   <si>
@@ -1960,12 +1906,6 @@
     <t>BAU Zero Emis Credit for Nuc Plants</t>
   </si>
   <si>
-    <t>EDWP</t>
-  </si>
-  <si>
-    <t>Electricity Dispatch Weibull Parameters</t>
-  </si>
-  <si>
     <t>MLfPPR</t>
   </si>
   <si>
@@ -2080,9 +2020,6 @@
     <t>Biomass with CCS Storage per MWh</t>
   </si>
   <si>
-    <t>Smoothing Time for CCS Capital Expenditures</t>
-  </si>
-  <si>
     <t>SoCTaSCbRIC</t>
   </si>
   <si>
@@ -2170,9 +2107,6 @@
     <t>Capacity Supply Curve</t>
   </si>
   <si>
-    <t>Electricity Dispatch Weibull Parameter A, Electricity Dispatch Weibull Parameter B</t>
-  </si>
-  <si>
     <t>GBCGpUNR</t>
   </si>
   <si>
@@ -2317,9 +2251,6 @@
     <t>You are modeling non-BAU subregional ZEV sales requirements (as opposed to a national ZEV sales standard)</t>
   </si>
   <si>
-    <t>STfECCE</t>
-  </si>
-  <si>
     <t>BUCMfNCR</t>
   </si>
   <si>
@@ -2431,12 +2362,6 @@
     <t>Elasticity of Industrial Equipment Energy Consumption with respect to Energy Cost</t>
   </si>
   <si>
-    <t>FYIESM</t>
-  </si>
-  <si>
-    <t>Final Year Industrial Equipment Shareweight Minimums</t>
-  </si>
-  <si>
     <t>IELC</t>
   </si>
   <si>
@@ -2467,9 +2392,6 @@
     <t>Weighted Average Cost of Capital by Industry, Risk Premium for Equity</t>
   </si>
   <si>
-    <t>RPFfFISCC</t>
-  </si>
-  <si>
     <t>Repayment Period for Financed Industry Sector Capital Costs</t>
   </si>
   <si>
@@ -2479,12 +2401,6 @@
     <t>BAU Clean Heat PTC Duration</t>
   </si>
   <si>
-    <t>BCHPR</t>
-  </si>
-  <si>
-    <t>BAU Clean Heat PTC Rate</t>
-  </si>
-  <si>
     <t>IFTQfS</t>
   </si>
   <si>
@@ -2621,6 +2537,294 @@
   </si>
   <si>
     <t>Industrial Fuels Subject to Electrification</t>
+  </si>
+  <si>
+    <t>FoCaAPMbDT</t>
+  </si>
+  <si>
+    <t>FoIPMbDT</t>
+  </si>
+  <si>
+    <t>Fraction of Child and Adult Premature Mortality by Demographic Trait</t>
+  </si>
+  <si>
+    <t>Fraction of Infant Premature Mortality by Demographic Trait</t>
+  </si>
+  <si>
+    <t>NoH</t>
+  </si>
+  <si>
+    <t>Number of Households</t>
+  </si>
+  <si>
+    <t>BDCL</t>
+  </si>
+  <si>
+    <t>BAU Data Center Load</t>
+  </si>
+  <si>
+    <t>HOIpTP</t>
+  </si>
+  <si>
+    <t>RPfFBSCC</t>
+  </si>
+  <si>
+    <t>BAEPAbCiPC</t>
+  </si>
+  <si>
+    <t>Boolean Are Electricity Prices Affected by Changes in Production Costs</t>
+  </si>
+  <si>
+    <t>FIoHP</t>
+  </si>
+  <si>
+    <t>Fuel Intensity of Hydrogen Production</t>
+  </si>
+  <si>
+    <t>BCHSR</t>
+  </si>
+  <si>
+    <t>BAU Clean Heat Subsidy Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is a clean-heat subsidy in your region. </t>
+  </si>
+  <si>
+    <t>RPfFISCC</t>
+  </si>
+  <si>
+    <t>DCLGA</t>
+  </si>
+  <si>
+    <t>Data Center Load Growth Assumptions</t>
+  </si>
+  <si>
+    <t>You wish to use a low- or high-growth forecast for data centers in your region.</t>
+  </si>
+  <si>
+    <t>ICwIwLF</t>
+  </si>
+  <si>
+    <t>Industry Category with Industry-wide Load Factor</t>
+  </si>
+  <si>
+    <t>You wish to use industry-specific load factors for any industry categories. In the U.S. model, we use industry-specific load factors for ag/forestry and refining.</t>
+  </si>
+  <si>
+    <t>elec/SHELF</t>
+  </si>
+  <si>
+    <t>ctrl-settings/ICwIwLF</t>
+  </si>
+  <si>
+    <t>MRV</t>
+  </si>
+  <si>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>Model Run Vintage</t>
+  </si>
+  <si>
+    <t>Modeled Vintage</t>
+  </si>
+  <si>
+    <t>BPMGBSA</t>
+  </si>
+  <si>
+    <t>BAU Policy Mandated Grid Battery Storage Additions</t>
+  </si>
+  <si>
+    <t>NSDoDC</t>
+  </si>
+  <si>
+    <t>Normalized Standard Deviation of Dispatch Costs</t>
+  </si>
+  <si>
+    <t>UFDfGBS</t>
+  </si>
+  <si>
+    <t>Usage Factor Discount for Grid Battery Storage</t>
+  </si>
+  <si>
+    <t>BPTbCP</t>
+  </si>
+  <si>
+    <t>BAU Pollutants Taxed by Carbon Pricing</t>
+  </si>
+  <si>
+    <t>PTbCP</t>
+  </si>
+  <si>
+    <t>Pollutants Taxed by Carbon Pricing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If there is a policy scenario with differing carbon pricing scheme than in the BAU. </t>
+  </si>
+  <si>
+    <t>BCoHSC</t>
+  </si>
+  <si>
+    <t>BAU Cost of Hydrogen Sector Capital</t>
+  </si>
+  <si>
+    <t>BSfHPbP</t>
+  </si>
+  <si>
+    <t>BAU Subsidy for Hydrogen Production by Pathway</t>
+  </si>
+  <si>
+    <t>FoHERbA</t>
+  </si>
+  <si>
+    <t>Fraction of Hydrogen Equipment Retiring by Age</t>
+  </si>
+  <si>
+    <t>HPLC</t>
+  </si>
+  <si>
+    <t>Hydrogen Production Logit Coefficient</t>
+  </si>
+  <si>
+    <t>HPS</t>
+  </si>
+  <si>
+    <t>Hydrogen Production Shareweights</t>
+  </si>
+  <si>
+    <t>HPSD</t>
+  </si>
+  <si>
+    <t>Hydrogen Production Subsidy Duration</t>
+  </si>
+  <si>
+    <t>If there is a hydrogen production subsidy in the region.</t>
+  </si>
+  <si>
+    <t>PHERP</t>
+  </si>
+  <si>
+    <t>Preexisting Hydrogen Equipment Retirement Profiles</t>
+  </si>
+  <si>
+    <t>RPfFHSCC</t>
+  </si>
+  <si>
+    <t>Repayment Period for Financed Hydrogen Sector Capital Costs</t>
+  </si>
+  <si>
+    <t>SYAHPC</t>
+  </si>
+  <si>
+    <t>Start Year Annual Hydrogen Production Capacity</t>
+  </si>
+  <si>
+    <t>SoHDTiGaLCbS</t>
+  </si>
+  <si>
+    <t>Start Year Hydrogen Demand That is Green and Low Carbon by Sector</t>
+  </si>
+  <si>
+    <t>SoHPCCbRIC</t>
+  </si>
+  <si>
+    <t>Share of Hydrogen Production Capital Costs by Recipient ISIC Code</t>
+  </si>
+  <si>
+    <t>WCoHPbP</t>
+  </si>
+  <si>
+    <t>Water Consumption of Hydrogen Production by Pathway</t>
+  </si>
+  <si>
+    <t>BDGPfPEP</t>
+  </si>
+  <si>
+    <t>Boolean Does Government Pay for Process Emissions Policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you wish to implement process emissions policies that are paid for by government or change the U.S. assumptions. </t>
+  </si>
+  <si>
+    <t>BIISRP</t>
+  </si>
+  <si>
+    <t>BAU Individual Industrial Site Retirement Profiles</t>
+  </si>
+  <si>
+    <t>EoIEPwEEI</t>
+  </si>
+  <si>
+    <t>Elasticity of Industrial Equipment Price with respect to Energy Efficiency Improvements</t>
+  </si>
+  <si>
+    <t>IES</t>
+  </si>
+  <si>
+    <t>Industrial Equipment Shareweights</t>
+  </si>
+  <si>
+    <t>IFTQfEERP</t>
+  </si>
+  <si>
+    <t>Industrial Fuel Types Qualifying for Early Equipment Retirement Policy</t>
+  </si>
+  <si>
+    <t>NIEAFSM</t>
+  </si>
+  <si>
+    <t>New Industrial Equipment Alternative Fuel Shifting Matrix</t>
+  </si>
+  <si>
+    <t>If applying fuel shifting policies other than a shift to hydrogen combustion (e.g., coal-to-gas policies).</t>
+  </si>
+  <si>
+    <t>PoONEUTiMEbIC</t>
+  </si>
+  <si>
+    <t>Percent of Other Nonprocess Energy Use That is Mobile Equipment by ISIC Code</t>
+  </si>
+  <si>
+    <t>SoICETAF</t>
+  </si>
+  <si>
+    <t>Share of Industry Capital Expenditures That Are Financed</t>
+  </si>
+  <si>
+    <t>WHRCC</t>
+  </si>
+  <si>
+    <t>WHRPbI</t>
+  </si>
+  <si>
+    <t>Waste Heat Recovery Potential by Industry</t>
+  </si>
+  <si>
+    <t>Waste Heat Recovery Capital Costs</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Vintage</t>
+  </si>
+  <si>
+    <t>ANVCV</t>
+  </si>
+  <si>
+    <t>Additional New Vehicles Calibration Variable</t>
+  </si>
+  <si>
+    <t>BPM</t>
+  </si>
+  <si>
+    <t>Battery Pack Markup</t>
+  </si>
+  <si>
+    <t>BPPM</t>
+  </si>
+  <si>
+    <t>Battery Pack Price Multiplier</t>
   </si>
 </sst>
 </file>
@@ -2729,7 +2933,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2790,6 +2994,52 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3102,82 +3352,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>97</v>
       </c>
@@ -3185,32 +3435,32 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
         <v>244</v>
       </c>
@@ -3218,17 +3468,17 @@
         <v>247</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>99</v>
       </c>
@@ -3236,42 +3486,42 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>98</v>
       </c>
@@ -3279,84 +3529,84 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>252</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>140</v>
       </c>
@@ -3364,62 +3614,62 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3432,20 +3682,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G316"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G348"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="67" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.81640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.54296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="54" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.81640625" style="2"/>
+    <col min="8" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -3459,7 +3709,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="F1" s="23" t="s">
         <v>96</v>
@@ -3468,15 +3718,15 @@
         <v>306</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -3484,4809 +3734,5279 @@
         <v>97</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>518</v>
+        <v>835</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>519</v>
+        <v>837</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>448</v>
+        <v>836</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>838</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>564</v>
+        <v>843</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>433</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="17" t="s">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B9" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C9" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G7" s="17"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>697</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>698</v>
+        <v>23</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>594</v>
+        <v>841</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>595</v>
+        <v>842</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>369</v>
+        <v>676</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>677</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>837</v>
+        <v>576</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>577</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>165</v>
+        <v>354</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>166</v>
+        <v>355</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+        <v>356</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>809</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+        <v>810</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>29</v>
+        <v>166</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>434</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>164</v>
+        <v>27</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>470</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>754</v>
+        <v>163</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>755</v>
+        <v>164</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>19</v>
+        <v>454</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>455</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>733</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>341</v>
+        <v>20</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>342</v>
+        <v>33</v>
       </c>
       <c r="F29" s="16" t="s">
         <v>291</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>562</v>
+        <v>21</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>835</v>
+        <v>34</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>437</v>
+        <v>22</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>442</v>
+        <v>336</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>490</v>
+        <v>844</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+        <v>807</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>237</v>
+        <v>422</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+        <v>423</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>474</v>
+        <v>427</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>475</v>
+        <v>428</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E36" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F39" s="12" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="17" t="s">
+    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>445</v>
-      </c>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17" t="s">
+      <c r="B40" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F40" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="17"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="116" x14ac:dyDescent="0.35">
+      <c r="G40" s="17"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>37</v>
+        <v>581</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>582</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>396</v>
+        <v>656</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>397</v>
+        <v>657</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>833</v>
+        <v>660</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+        <v>661</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>855</v>
+        <v>37</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+        <v>389</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>859</v>
+        <v>381</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+        <v>382</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>852</v>
+        <v>805</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>806</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>857</v>
+        <v>827</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>828</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>683</v>
+        <v>831</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>684</v>
+        <v>832</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="17" t="s">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="17" t="s">
-        <v>761</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>682</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B49" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>170</v>
+        <v>36</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>5</v>
+        <v>829</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>6</v>
+        <v>830</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" s="17" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>662</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B51" s="17" t="s">
-        <v>426</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="22" t="s">
+      <c r="B52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G51" s="17" t="s">
+      <c r="G53" s="17" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="17" t="s">
-        <v>472</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>432</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="22" t="s">
+    <row r="54" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>418</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G52" s="17" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="G54" s="17" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>423</v>
+        <v>845</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>424</v>
+        <v>846</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>329</v>
+        <v>521</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>330</v>
+        <v>522</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>245</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>246</v>
+        <v>409</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>700</v>
+        <v>245</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>701</v>
+        <v>246</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>494</v>
+        <v>679</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>495</v>
+        <v>680</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>260</v>
+        <v>478</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>261</v>
+        <v>479</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>554</v>
+        <v>260</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>555</v>
+        <v>261</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>762</v>
+        <v>536</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>763</v>
+        <v>537</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>176</v>
+        <v>739</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>177</v>
+        <v>740</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>559</v>
+        <v>176</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>561</v>
+        <v>177</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>402</v>
+        <v>853</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+        <v>854</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>830</v>
+        <v>541</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="F66" s="22" t="s">
+        <v>543</v>
+      </c>
+      <c r="F66" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="17" t="s">
-        <v>400</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>452</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>703</v>
-      </c>
-      <c r="E67" s="17"/>
-      <c r="F67" s="22" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F68" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="G67" s="17" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="2" t="s">
+      <c r="G68" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" s="26" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>385</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>435</v>
+      </c>
+      <c r="C69" s="26" t="s">
+        <v>436</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>682</v>
+      </c>
+      <c r="F69" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="G69" s="26" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" s="26" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="26" t="s">
+        <v>385</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>856</v>
+      </c>
+      <c r="C70" s="26" t="s">
+        <v>857</v>
+      </c>
+      <c r="E70" s="26" t="s">
+        <v>859</v>
+      </c>
+      <c r="F70" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="G70" s="26" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="26" t="s">
+        <v>385</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>861</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>863</v>
+      </c>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G71" s="26"/>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>862</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>864</v>
+      </c>
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G72" s="17"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B73" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F73" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A69" s="2" t="s">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F74" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70" s="2" t="s">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71" s="2" t="s">
+      <c r="B75" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B76" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F76" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A72" s="2" t="s">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="C73" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="D73" s="17"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="G73" s="17" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A74" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A75" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A77" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="B77" s="2" t="s">
-        <v>179</v>
+        <v>510</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>705</v>
+        <v>511</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A78" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="C78" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="G78" s="17" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>586</v>
+        <v>745</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>747</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>666</v>
+        <v>746</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>668</v>
+        <v>748</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>173</v>
+        <v>620</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F81" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+        <v>621</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>577</v>
+        <v>179</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>578</v>
+        <v>683</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+        <v>684</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>44</v>
+        <v>314</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>50</v>
+        <v>315</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>45</v>
+        <v>568</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F84" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>567</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>734</v>
+        <v>646</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="F85" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+        <v>647</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>756</v>
+        <v>173</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+      <c r="F86" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>671</v>
+        <v>559</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+        <v>560</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>656</v>
+        <v>44</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>848</v>
+        <v>45</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="F89" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>669</v>
+        <v>712</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+        <v>713</v>
+      </c>
+      <c r="F90" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>158</v>
+        <v>865</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>159</v>
+        <v>866</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>640</v>
+        <v>734</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>641</v>
+        <v>735</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>46</v>
+        <v>651</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>652</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>708</v>
+        <v>636</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>637</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>498</v>
+        <v>820</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+        <v>821</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>772</v>
+        <v>649</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>650</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>710</v>
+        <v>158</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>297</v>
+        <v>46</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>723</v>
+        <v>687</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>688</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>47</v>
+        <v>482</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+        <v>483</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>276</v>
+        <v>749</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F102" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>750</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>642</v>
+        <v>689</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>643</v>
+        <v>690</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>167</v>
+        <v>612</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+        <v>613</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>653</v>
+        <v>297</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>655</v>
+        <v>298</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>774</v>
+        <v>701</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+        <v>702</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>850</v>
+        <v>47</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>851</v>
+        <v>169</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>664</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>713</v>
+        <v>276</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>476</v>
+        <v>167</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>477</v>
+        <v>168</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>686</v>
+        <v>419</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>175</v>
+        <v>633</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+        <v>634</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B112" s="2" t="s">
-        <v>749</v>
+        <v>822</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>823</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+        <v>692</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>715</v>
+        <v>460</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>461</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>575</v>
+        <v>175</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>588</v>
+        <v>726</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+        <v>728</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+        <v>729</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>579</v>
+        <v>674</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>580</v>
+        <v>675</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>644</v>
+        <v>693</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>645</v>
+        <v>694</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>48</v>
+        <v>557</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+        <v>558</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>194</v>
+        <v>570</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>571</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>49</v>
+        <v>710</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>711</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>737</v>
+        <v>561</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>562</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>730</v>
+        <v>624</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>625</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>651</v>
+        <v>48</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="F125" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>562</v>
+        <v>867</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>868</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>199</v>
+        <v>49</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>663</v>
+        <v>715</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+        <v>716</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>583</v>
+        <v>708</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>584</v>
+        <v>709</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>723</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B131" s="2" t="s">
-        <v>649</v>
+        <v>631</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>650</v>
+        <v>632</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>695</v>
       </c>
       <c r="F131" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>441</v>
+        <v>185</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>661</v>
+        <v>544</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F133" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>545</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>634</v>
+        <v>199</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>644</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F136" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+        <v>566</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F137" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+        <v>630</v>
+      </c>
+      <c r="F137" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>581</v>
+        <v>424</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F138" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>718</v>
+        <v>641</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="F139" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>642</v>
+      </c>
+      <c r="F139" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>846</v>
+        <v>616</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>847</v>
+        <v>617</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>688</v>
+        <v>618</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="17" t="s">
+        <v>619</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B142" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="C142" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="D142" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="E142" s="17"/>
-      <c r="F142" s="21" t="s">
+      <c r="B142" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B148" s="31" t="s">
+        <v>869</v>
+      </c>
+      <c r="C148" s="31" t="s">
+        <v>870</v>
+      </c>
+      <c r="D148" s="30"/>
+      <c r="E148" s="30"/>
+      <c r="F148" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="G148" s="30"/>
+    </row>
+    <row r="149" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B149" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C149" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="D149" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="E149" s="17"/>
+      <c r="F149" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="G142" s="17" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A143" s="2" t="s">
+      <c r="G149" s="17" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B150" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C150" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D143" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="F143" s="4" t="s">
+      <c r="D150" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F150" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A144" s="2" t="s">
+    <row r="151" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B151" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D144" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="F144" s="4" t="s">
+      <c r="D151" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F151" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A145" s="2" t="s">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B152" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C152" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="F145" s="4" t="s">
+      <c r="F152" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A146" s="2" t="s">
+    <row r="153" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A147" s="2" t="s">
+      <c r="B153" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B154" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="F154" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A148" s="2" t="s">
+    <row r="155" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="B155" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C155" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F148" s="4" t="s">
+      <c r="F155" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="17" t="s">
+    <row r="156" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="B149" s="17" t="s">
+      <c r="B156" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C149" s="17" t="s">
+      <c r="C156" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="D149" s="17"/>
-      <c r="E149" s="17"/>
-      <c r="F149" s="20" t="s">
+      <c r="D156" s="17"/>
+      <c r="E156" s="17"/>
+      <c r="F156" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="G149" s="17"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A150" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A151" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A152" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A153" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A154" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A155" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A156" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G156" s="17"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>301</v>
+        <v>442</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>443</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>612</v>
+        <v>754</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>613</v>
+        <v>757</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>509</v>
+        <v>755</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>510</v>
+        <v>758</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>782</v>
+        <v>444</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+        <v>445</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>526</v>
+        <v>352</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>527</v>
+        <v>353</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A163" s="2" t="s">
+    <row r="163" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="F163" s="4" t="s">
+      <c r="B163" s="31" t="s">
+        <v>871</v>
+      </c>
+      <c r="C163" s="31" t="s">
+        <v>872</v>
+      </c>
+      <c r="F163" s="33" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F164" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>377</v>
+        <v>742</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F166" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>743</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>378</v>
+        <v>594</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F167" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G167" s="2" 